--- a/handover/유동성리뷰_담당자파일.xlsx
+++ b/handover/유동성리뷰_담당자파일.xlsx
@@ -379,7 +379,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">인 </t>
+      <t xml:space="preserve">인 과제 </t>
     </r>
     <r>
       <rPr>
@@ -396,7 +396,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">몫</t>
+      <t xml:space="preserve">개</t>
     </r>
     <r>
       <rPr>
@@ -430,7 +430,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">인 </t>
+      <t xml:space="preserve">인 과제 </t>
     </r>
     <r>
       <rPr>
@@ -447,7 +447,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">몫</t>
+      <t xml:space="preserve">개</t>
     </r>
     <r>
       <rPr>
@@ -456,7 +456,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. 1</t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -464,7 +464,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">몫 </t>
+      <t xml:space="preserve">과제 </t>
     </r>
     <r>
       <rPr>
@@ -473,7 +473,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">= </t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -481,7 +481,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">완전 정리 </t>
+      <t xml:space="preserve">개 </t>
     </r>
     <r>
       <rPr>
@@ -490,7 +490,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">= </t>
     </r>
     <r>
       <rPr>
@@ -498,7 +498,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">편 또는 짧은 정리 </t>
+      <t xml:space="preserve">긴 정리 </t>
     </r>
     <r>
       <rPr>
@@ -507,7 +507,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -515,7 +515,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">편</t>
+      <t xml:space="preserve">편 또는 짧은 정리 </t>
     </r>
     <r>
       <rPr>
@@ -524,7 +524,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">4</t>
     </r>
     <r>
       <rPr>
@@ -532,7 +532,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">같은 몫은 </t>
+      <t xml:space="preserve">편</t>
     </r>
     <r>
       <rPr>
@@ -541,7 +541,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">slot </t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -549,7 +549,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">열이 같다</t>
+      <t xml:space="preserve">같은 과제는 </t>
     </r>
     <r>
       <rPr>
@@ -558,7 +558,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">slot </t>
     </r>
     <r>
       <rPr>
@@ -566,7 +566,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">노란 칸</t>
+      <t xml:space="preserve">열이 같다</t>
     </r>
     <r>
       <rPr>
@@ -575,7 +575,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -583,7 +583,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">제출일</t>
+      <t xml:space="preserve">노란 칸</t>
     </r>
     <r>
       <rPr>
@@ -592,7 +592,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -600,7 +600,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">접수</t>
+      <t xml:space="preserve">제출일</t>
     </r>
     <r>
       <rPr>
@@ -617,7 +617,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">짝점검</t>
+      <t xml:space="preserve">접수</t>
     </r>
     <r>
       <rPr>
@@ -634,7 +634,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">반려사유</t>
+      <t xml:space="preserve">짝점검</t>
     </r>
     <r>
       <rPr>
@@ -643,7 +643,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -651,7 +651,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">을 원석이 채운다</t>
+      <t xml:space="preserve">반려사유</t>
     </r>
     <r>
       <rPr>
@@ -660,7 +660,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">)</t>
     </r>
     <r>
       <rPr>
@@ -668,7 +668,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">맨 위 회색 </t>
+      <t xml:space="preserve">을 원석이 채운다</t>
     </r>
     <r>
       <rPr>
@@ -677,7 +677,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">'</t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -685,7 +685,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">예시</t>
+      <t xml:space="preserve">맨 위 회색 </t>
     </r>
     <r>
       <rPr>
@@ -694,7 +694,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">' </t>
+      <t xml:space="preserve">'</t>
     </r>
     <r>
       <rPr>
@@ -702,7 +702,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">행을 따라 쓴다</t>
+      <t xml:space="preserve">예시</t>
     </r>
     <r>
       <rPr>
@@ -711,17 +711,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">' </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">진행현황</t>
+      <t xml:space="preserve">행을 따라 쓴다</t>
     </r>
     <r>
       <rPr>
@@ -730,15 +728,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">주차별배정의 노란 칸을 채우면 자동으로 계산된다</t>
+      <t xml:space="preserve">진행현황</t>
     </r>
     <r>
       <rPr>
@@ -747,7 +747,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
@@ -755,7 +755,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">수식</t>
+      <t xml:space="preserve">주차별배정의 노란 칸을 채우면 자동으로 계산된다</t>
     </r>
     <r>
       <rPr>
@@ -764,7 +764,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">). </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -772,7 +772,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">매주 수요일 보고에 이 숫자를 쓴다</t>
+      <t xml:space="preserve">수식</t>
     </r>
     <r>
       <rPr>
@@ -781,17 +781,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">). </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">분류틀</t>
+      <t xml:space="preserve">매주 수요일 보고에 이 숫자를 쓴다</t>
     </r>
     <r>
       <rPr>
@@ -800,15 +798,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">단계</t>
+      <t xml:space="preserve">분류틀</t>
     </r>
     <r>
       <rPr>
@@ -817,7 +817,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
@@ -825,7 +825,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">기능</t>
+      <t xml:space="preserve">단계</t>
     </r>
     <r>
       <rPr>
@@ -842,7 +842,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">시장 코드의 뜻과 </t>
+      <t xml:space="preserve">기능</t>
     </r>
     <r>
       <rPr>
@@ -851,7 +851,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">148</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -859,7 +859,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">편의 교차표</t>
+      <t xml:space="preserve">시장 코드의 뜻과 </t>
     </r>
     <r>
       <rPr>
@@ -868,7 +868,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">148</t>
     </r>
     <r>
       <rPr>
@@ -876,7 +876,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">수식</t>
+      <t xml:space="preserve">편의 교차표</t>
     </r>
     <r>
       <rPr>
@@ -885,17 +885,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">).</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">(</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">선별과정</t>
+      <t xml:space="preserve">수식</t>
     </r>
     <r>
       <rPr>
@@ -904,15 +902,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: 52,006</t>
-    </r>
+      <t xml:space="preserve">).</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">건에서 </t>
+      <t xml:space="preserve">선별과정</t>
     </r>
     <r>
       <rPr>
@@ -921,7 +921,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">148</t>
+      <t xml:space="preserve">: 52,006</t>
     </r>
     <r>
       <rPr>
@@ -929,7 +929,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">편이 되기까지</t>
+      <t xml:space="preserve">건에서 </t>
     </r>
     <r>
       <rPr>
@@ -938,7 +938,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(PRISMA). </t>
+      <t xml:space="preserve">148</t>
     </r>
     <r>
       <rPr>
@@ -946,7 +946,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">논문 </t>
+      <t xml:space="preserve">편이 되기까지</t>
     </r>
     <r>
       <rPr>
@@ -955,7 +955,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
+      <t xml:space="preserve">(PRISMA). </t>
     </r>
     <r>
       <rPr>
@@ -963,7 +963,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">장의 숫자</t>
+      <t xml:space="preserve">논문 </t>
     </r>
     <r>
       <rPr>
@@ -972,17 +972,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">3</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">전체</t>
+      <t xml:space="preserve">장의 숫자</t>
     </r>
     <r>
       <rPr>
@@ -991,15 +989,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">438: </t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">제목</t>
+      <t xml:space="preserve">전체</t>
     </r>
     <r>
       <rPr>
@@ -1008,7 +1008,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">438: </t>
     </r>
     <r>
       <rPr>
@@ -1016,7 +1016,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">초록 선별을 통과한 </t>
+      <t xml:space="preserve">제목</t>
     </r>
     <r>
       <rPr>
@@ -1025,7 +1025,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">438</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -1033,7 +1033,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">편과 각 편이 종합</t>
+      <t xml:space="preserve">초록 선별을 통과한 </t>
     </r>
     <r>
       <rPr>
@@ -1042,7 +1042,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
+      <t xml:space="preserve">438</t>
     </r>
     <r>
       <rPr>
@@ -1050,7 +1050,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">배경</t>
+      <t xml:space="preserve">편과 각 편이 종합</t>
     </r>
     <r>
       <rPr>
@@ -1067,7 +1067,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">증거지도 중 어디로 갔는지</t>
+      <t xml:space="preserve">배경</t>
     </r>
     <r>
       <rPr>
@@ -1076,20 +1076,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">노란 칸 입력 규칙</t>
-  </si>
-  <si>
+      <t xml:space="preserve">/</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">접수</t>
+      <t xml:space="preserve">증거지도 중 어디로 갔는지</t>
     </r>
     <r>
       <rPr>
@@ -1098,15 +1093,20 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: O(</t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">노란 칸 입력 규칙</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">통과</t>
+      <t xml:space="preserve">접수</t>
     </r>
     <r>
       <rPr>
@@ -1115,7 +1115,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) / </t>
+      <t xml:space="preserve">: O(</t>
     </r>
     <r>
       <rPr>
@@ -1123,7 +1123,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">반려 </t>
+      <t xml:space="preserve">통과</t>
     </r>
     <r>
       <rPr>
@@ -1132,7 +1132,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/ </t>
+      <t xml:space="preserve">) / </t>
     </r>
     <r>
       <rPr>
@@ -1140,7 +1140,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">미제출 중 하나</t>
+      <t xml:space="preserve">반려 </t>
     </r>
     <r>
       <rPr>
@@ -1149,7 +1149,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">/ </t>
     </r>
     <r>
       <rPr>
@@ -1157,7 +1157,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">짝점검</t>
+      <t xml:space="preserve">미제출 중 하나</t>
     </r>
     <r>
       <rPr>
@@ -1166,7 +1166,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: O / </t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -1174,7 +1174,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">수정필요</t>
+      <t xml:space="preserve">짝점검</t>
     </r>
     <r>
       <rPr>
@@ -1183,7 +1183,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">: O / </t>
     </r>
     <r>
       <rPr>
@@ -1191,7 +1191,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">반려사유는 짧게</t>
+      <t xml:space="preserve">수정필요</t>
     </r>
     <r>
       <rPr>
@@ -1200,7 +1200,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -1208,7 +1208,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">예</t>
+      <t xml:space="preserve">반려사유는 짧게</t>
     </r>
     <r>
       <rPr>
@@ -1217,7 +1217,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -1225,7 +1225,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">정의 원문 쪽수 없음</t>
+      <t xml:space="preserve">예</t>
     </r>
     <r>
       <rPr>
@@ -1234,17 +1234,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">).</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">: </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원문 상태 </t>
+      <t xml:space="preserve">정의 원문 쪽수 없음</t>
     </r>
     <r>
       <rPr>
@@ -1253,15 +1251,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
+      <t xml:space="preserve">).</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">도서관 전자저널</t>
+      <t xml:space="preserve">원문 상태 </t>
     </r>
     <r>
       <rPr>
@@ -1278,7 +1278,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">은 학교 도서관 로그인 후 </t>
+      <t xml:space="preserve">도서관 전자저널</t>
     </r>
     <r>
       <rPr>
@@ -1287,7 +1287,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DOI </t>
+      <t xml:space="preserve">'</t>
     </r>
     <r>
       <rPr>
@@ -1295,7 +1295,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">링크로 받는다</t>
+      <t xml:space="preserve">은 학교 도서관 로그인 후 </t>
     </r>
     <r>
       <rPr>
@@ -1304,7 +1304,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">DOI </t>
     </r>
     <r>
       <rPr>
@@ -1312,7 +1312,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">안 되면 상호대차</t>
+      <t xml:space="preserve">링크로 받는다</t>
     </r>
     <r>
       <rPr>
@@ -1321,17 +1321,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">. </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원문 상태 </t>
+      <t xml:space="preserve">안 되면 상호대차</t>
     </r>
     <r>
       <rPr>
@@ -1340,15 +1338,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">한국 학술지</t>
+      <t xml:space="preserve">원문 상태 </t>
     </r>
     <r>
       <rPr>
@@ -1365,7 +1365,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">는 </t>
+      <t xml:space="preserve">한국 학술지</t>
     </r>
     <r>
       <rPr>
@@ -1374,7 +1374,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">KCI</t>
+      <t xml:space="preserve">'</t>
     </r>
     <r>
       <rPr>
@@ -1382,7 +1382,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">에서 논문명 검색 → 원문보기</t>
+      <t xml:space="preserve">는 </t>
     </r>
     <r>
       <rPr>
@@ -1391,7 +1391,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">KCI</t>
     </r>
     <r>
       <rPr>
@@ -1399,7 +1399,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">안 되면 </t>
+      <t xml:space="preserve">에서 논문명 검색 → 원문보기</t>
     </r>
     <r>
       <rPr>
@@ -1408,17 +1408,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">RISS·DBpia.</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">. </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원문 상태 </t>
+      <t xml:space="preserve">안 되면 </t>
     </r>
     <r>
       <rPr>
@@ -1427,15 +1425,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">'</t>
-    </r>
+      <t xml:space="preserve">RISS·DBpia.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">받음</t>
+      <t xml:space="preserve">원문 상태 </t>
     </r>
     <r>
       <rPr>
@@ -1452,7 +1452,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">은 저장소 </t>
+      <t xml:space="preserve">받음</t>
     </r>
     <r>
       <rPr>
@@ -1461,7 +1461,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">papers/ </t>
+      <t xml:space="preserve">'</t>
     </r>
     <r>
       <rPr>
@@ -1469,7 +1469,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">폴더에 </t>
+      <t xml:space="preserve">은 저장소 </t>
     </r>
     <r>
       <rPr>
@@ -1478,7 +1478,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PDF</t>
+      <t xml:space="preserve">papers/ </t>
     </r>
     <r>
       <rPr>
@@ -1486,7 +1486,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가 있다</t>
+      <t xml:space="preserve">폴더에 </t>
     </r>
     <r>
       <rPr>
@@ -1495,7 +1495,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(pid </t>
+      <t xml:space="preserve">PDF</t>
     </r>
     <r>
       <rPr>
@@ -1503,7 +1503,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이름</t>
+      <t xml:space="preserve">가 있다</t>
     </r>
     <r>
       <rPr>
@@ -1512,20 +1512,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">).</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">숫자 출처</t>
-  </si>
-  <si>
+      <t xml:space="preserve">(pid </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">선별과정 시트의 수치는 저장소 </t>
+      <t xml:space="preserve">이름</t>
     </r>
     <r>
       <rPr>
@@ -1534,15 +1529,20 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">review/prisma_flow.md(2026-10-10 </t>
-    </r>
+      <t xml:space="preserve">).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">숫자 출처</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">검색 실행 결과</t>
+      <t xml:space="preserve">선별과정 시트의 수치는 저장소 </t>
     </r>
     <r>
       <rPr>
@@ -1551,7 +1551,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">review/prisma_flow.md(2026-10-10 </t>
     </r>
     <r>
       <rPr>
@@ -1559,7 +1559,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">에서 옮긴 값이다</t>
+      <t xml:space="preserve">검색 실행 결과</t>
     </r>
     <r>
       <rPr>
@@ -1568,79 +1568,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">pid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">주차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">담당</t>
-  </si>
-  <si>
-    <t xml:space="preserve">짝</t>
-  </si>
-  <si>
-    <t xml:space="preserve">연도</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제목</t>
-  </si>
-  <si>
-    <t xml:space="preserve">학술지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">단계</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기능</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시장</t>
-  </si>
-  <si>
-    <t xml:space="preserve">한국</t>
-  </si>
-  <si>
-    <t xml:space="preserve">원문 상태</t>
-  </si>
-  <si>
-    <t xml:space="preserve">원문 받는 법</t>
-  </si>
-  <si>
-    <t xml:space="preserve">비고</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정리 깊이</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">예시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이원석</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frequency domain analysis to detect common cycle in housing price and trading volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Housing and Urban Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.38100/jhuf.2021.6.2.53</t>
-  </si>
-  <si>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에서 옮긴 값이다</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1648,16 +1585,79 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">체결</t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">pid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">담당</t>
+  </si>
+  <si>
+    <t xml:space="preserve">짝</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연도</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">학술지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">단계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기능</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한국</t>
+  </si>
+  <si>
+    <t xml:space="preserve">원문 상태</t>
+  </si>
+  <si>
+    <t xml:space="preserve">원문 받는 법</t>
+  </si>
+  <si>
+    <t xml:space="preserve">비고</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정리 깊이</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">예시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이원석</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frequency domain analysis to detect common cycle in housing price and trading volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Housing and Urban Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.38100/jhuf.2021.6.2.53</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1665,7 +1665,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">S4 </t>
     </r>
     <r>
       <rPr>
@@ -1673,7 +1673,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">거래량</t>
+      <t xml:space="preserve">체결</t>
     </r>
     <r>
       <rPr>
@@ -1682,7 +1682,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -1690,7 +1690,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가격 발견</t>
+      <t xml:space="preserve">거래량</t>
     </r>
     <r>
       <rPr>
@@ -1699,10 +1699,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가격 발견</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1710,16 +1716,10 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">F3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">선행성</t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1727,7 +1727,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">F3 </t>
     </r>
     <r>
       <rPr>
@@ -1735,17 +1735,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">관계</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">비</t>
+      <t xml:space="preserve">선행성</t>
     </r>
     <r>
       <rPr>
@@ -1754,7 +1744,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MLS </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -1762,7 +1752,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">포털</t>
+      <t xml:space="preserve">관계</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비</t>
     </r>
     <r>
       <rPr>
@@ -1771,7 +1771,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">MLS </t>
     </r>
     <r>
       <rPr>
@@ -1779,26 +1779,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">중개</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">받음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p115.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정리 예시 완료</t>
+      <t xml:space="preserve">포털</t>
     </r>
     <r>
       <rPr>
@@ -1807,7 +1788,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(examples/example_Ma2021_p115.md). </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -1815,17 +1796,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원석이 원문 대조 검증</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">짧은</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W01</t>
+      <t xml:space="preserve">중개</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">받음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p115.pdf</t>
   </si>
   <si>
     <r>
@@ -1834,7 +1815,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">전원</t>
+      <t xml:space="preserve">정리 예시 완료</t>
     </r>
     <r>
       <rPr>
@@ -1843,7 +1824,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">(examples/example_Ma2021_p115.md). </t>
     </r>
     <r>
       <rPr>
@@ -1851,7 +1832,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">파일럿</t>
+      <t xml:space="preserve">원석이 원문 대조 검증</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">짧은</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전원</t>
     </r>
     <r>
       <rPr>
@@ -1860,22 +1860,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">전원 비교</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Factors Affecting the Days on Market of Residential Real Estate in Seoul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korean Association for Housing Policy Studies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.24957/hsr.2019.27.1.05</t>
-  </si>
-  <si>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일럿</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1883,16 +1877,22 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">매칭</t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">전원 비교</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factors Affecting the Days on Market of Residential Real Estate in Seoul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korean Association for Housing Policy Studies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.24957/hsr.2019.27.1.05</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1900,7 +1900,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">S3 </t>
     </r>
     <r>
       <rPr>
@@ -1908,7 +1908,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">매물 시간</t>
+      <t xml:space="preserve">매칭</t>
     </r>
     <r>
       <rPr>
@@ -1917,7 +1917,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -1925,7 +1925,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">호가 조정</t>
+      <t xml:space="preserve">매물 시간</t>
     </r>
     <r>
       <rPr>
@@ -1934,10 +1934,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">호가 조정</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1945,16 +1951,10 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">F1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정의</t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1962,7 +1962,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">F1 </t>
     </r>
     <r>
       <rPr>
@@ -1970,13 +1970,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">구축</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p023.pdf</t>
-  </si>
-  <si>
+      <t xml:space="preserve">정의</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1984,7 +1979,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">W1 </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -1992,8 +1987,13 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">파일럿 논문</t>
-    </r>
+      <t xml:space="preserve">구축</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p023.pdf</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2001,7 +2001,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(KCI </t>
+      <t xml:space="preserve">W1 </t>
     </r>
     <r>
       <rPr>
@@ -2009,7 +2009,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원문</t>
+      <t xml:space="preserve">파일럿 논문</t>
     </r>
     <r>
       <rPr>
@@ -2018,41 +2018,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">완전</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">박사</t>
-  </si>
-  <si>
-    <t xml:space="preserve">석사①</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Effect of Apartment Housing Characteristics on the Days On Market(DOM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Korean Association of Urban Policies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.21447/jup.2019.10.3.101</t>
-  </si>
-  <si>
+      <t xml:space="preserve">(KCI </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">한국 학술지</t>
+      <t xml:space="preserve">원문</t>
     </r>
     <r>
       <rPr>
@@ -2061,10 +2035,42 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(KCI·RISS·DBpia)</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">긴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">박사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">석사①</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Effect of Apartment Housing Characteristics on the Days On Market(DOM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Korean Association of Urban Policies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.21447/jup.2019.10.3.101</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한국 학술지</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2072,16 +2078,10 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">KCI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 원문 없음 → </t>
-    </r>
+      <t xml:space="preserve">(KCI·RISS·DBpia)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2089,7 +2089,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DBpia·RISS(</t>
+      <t xml:space="preserve">KCI</t>
     </r>
     <r>
       <rPr>
@@ -2097,7 +2097,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">학교 계정</t>
+      <t xml:space="preserve">에 원문 없음 → </t>
     </r>
     <r>
       <rPr>
@@ -2106,7 +2106,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) </t>
+      <t xml:space="preserve">DBpia·RISS(</t>
     </r>
     <r>
       <rPr>
@@ -2114,34 +2114,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">또는 학회 홈페이지</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Determinants of Time to Close in Housing Transactions: Evidence from Survival Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.24957/hsr.2026.34.2.101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">학부④</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Impact of Asking Price and Sales Volume on the Real Transaction Price of Apartment using Machine Learning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Journal of Korean Institute of Information Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.14801/jkiit.2023.21.10.37</t>
-  </si>
-  <si>
+      <t xml:space="preserve">학교 계정</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2149,7 +2123,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S2 </t>
+      <t xml:space="preserve">) </t>
     </r>
     <r>
       <rPr>
@@ -2157,8 +2131,34 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">공급</t>
-    </r>
+      <t xml:space="preserve">또는 학회 홈페이지</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Determinants of Time to Close in Housing Transactions: Evidence from Survival Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.24957/hsr.2026.34.2.101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">학부④</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Impact of Asking Price and Sales Volume on the Real Transaction Price of Apartment using Machine Learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Journal of Korean Institute of Information Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.14801/jkiit.2023.21.10.37</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2166,7 +2166,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">S2 </t>
     </r>
     <r>
       <rPr>
@@ -2174,43 +2174,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">호가 설정</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">석사②</t>
-  </si>
-  <si>
-    <t xml:space="preserve">학부①</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does Online Apartment Listing Volume Lead Price Changes?: The Role of Transaction Volume and a Comparison of Sale and Jeonse Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.24957/hsr.2026.34.3.267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">학부③</t>
-  </si>
-  <si>
-    <t xml:space="preserve">학부②</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applications and Improvements of Real Estate Transaction Volume Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">국토연구</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.15793/kspr.2009.62..006</t>
-  </si>
-  <si>
+      <t xml:space="preserve">공급</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2218,7 +2183,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">F2 </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -2226,74 +2191,41 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">측정 쟁점</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p074.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do Housing Trading Volume Explain Housing Prices or the Converse?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.15793/kspr.2011.69..001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p077.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Relationship between Asymmetric Volatility and Trading Volume in the Korean Housing Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">대한경영학회지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.18032/kaaba.2017.30.11.1935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Causality and Predictability of Price-Volume in Housing Market - Evidence from Seoul and Busan Housing Markets -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH Urban Research &amp; Insight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.26700/shuri.2018.12.8.3.51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intervention Analysis of Apartment Trading Volume in Seoul, Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Real Estate Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.30902/jrea.2018.4.1.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p099.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Typology of the Busan Housing Market Considering Price Differentiation and Transaction Liquidity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korea Real Estate Society</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.37407/kres.2026.44.3.315</t>
+      <t xml:space="preserve">호가 설정</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">석사②</t>
+  </si>
+  <si>
+    <t xml:space="preserve">학부①</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does Online Apartment Listing Volume Lead Price Changes?: The Role of Transaction Volume and a Comparison of Sale and Jeonse Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.24957/hsr.2026.34.3.267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">학부③</t>
+  </si>
+  <si>
+    <t xml:space="preserve">학부②</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applications and Improvements of Real Estate Transaction Volume Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">국토연구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.15793/kspr.2009.62..006</t>
   </si>
   <si>
     <r>
@@ -2303,7 +2235,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S5 </t>
+      <t xml:space="preserve">F2 </t>
     </r>
     <r>
       <rPr>
@@ -2311,8 +2243,76 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">집계 상태</t>
-    </r>
+      <t xml:space="preserve">측정 쟁점</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p074.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do Housing Trading Volume Explain Housing Prices or the Converse?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.15793/kspr.2011.69..001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p077.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Relationship between Asymmetric Volatility and Trading Volume in the Korean Housing Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대한경영학회지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.18032/kaaba.2017.30.11.1935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Causality and Predictability of Price-Volume in Housing Market - Evidence from Seoul and Busan Housing Markets -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH Urban Research &amp; Insight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.26700/shuri.2018.12.8.3.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intervention Analysis of Apartment Trading Volume in Seoul, Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Real Estate Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.30902/jrea.2018.4.1.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p099.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Typology of the Busan Housing Market Considering Price Differentiation and Transaction Liquidity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korea Real Estate Society</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.37407/kres.2026.44.3.315</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2320,7 +2320,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">S5 </t>
     </r>
     <r>
       <rPr>
@@ -2328,40 +2328,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">지수</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apartment Transaction Volume and Price Volatility: Construction and Application of a Transaction-Volume-Based Price Uncertainty Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Housing Finance Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.52344/hfr.2026.10.1.133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p129.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Duration of Marketing Time of Residential Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00463</t>
-  </si>
-  <si>
+      <t xml:space="preserve">집계 상태</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2369,7 +2337,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MLS </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -2377,21 +2345,40 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">시장</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">도서관 전자저널</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가천대 도서관 로그인 후 </t>
-    </r>
+      <t xml:space="preserve">지수</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartment Transaction Volume and Price Volatility: Construction and Application of a Transaction-Volume-Based Price Uncertainty Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Housing Finance Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.52344/hfr.2026.10.1.133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p129.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Duration of Marketing Time of Residential Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00463</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2399,7 +2386,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DOI </t>
+      <t xml:space="preserve">MLS </t>
     </r>
     <r>
       <rPr>
@@ -2407,7 +2394,20 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">링크로 접속</t>
+      <t xml:space="preserve">시장</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">도서관 전자저널</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가천대 도서관 로그인 후 </t>
     </r>
     <r>
       <rPr>
@@ -2416,7 +2416,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">DOI </t>
     </r>
     <r>
       <rPr>
@@ -2424,55 +2424,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">구독 안 되면 상호대차 신청</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Measuring Residential Real Estate Liquidity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquidating Real Estate Assets Quickly: What Affects the Probability of a Quick Sale?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Real Estate Practice and Education</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10835547.2010.12091669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross sectional Analysis of time on Market indicators for an Australian City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacific Rim Property Research Journal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/14445921.2012.11104370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A study on the impact of changes in consumer sentiment on the housing market in Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Journal of Urban Sciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/12265934.2016.1239548</t>
-  </si>
-  <si>
+      <t xml:space="preserve">링크로 접속</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2480,7 +2433,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S1 </t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -2488,8 +2441,55 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">수요</t>
-    </r>
+      <t xml:space="preserve">구독 안 되면 상호대차 신청</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measuring Residential Real Estate Liquidity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidating Real Estate Assets Quickly: What Affects the Probability of a Quick Sale?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Real Estate Practice and Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10835547.2010.12091669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross sectional Analysis of time on Market indicators for an Australian City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacific Rim Property Research Journal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/14445921.2012.11104370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A study on the impact of changes in consumer sentiment on the housing market in Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Journal of Urban Sciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/12265934.2016.1239548</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2497,7 +2497,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">S1 </t>
     </r>
     <r>
       <rPr>
@@ -2505,215 +2505,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">관심</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relationship Among News Coverage, Consumers’ Sentiment, Prices, and Trading Volume in Housing Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.24957/hsr.2017.25.3.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p092.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Effects of News Big Data and Google Information Search on Apartment Transaction Volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential Environment Institute Of Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.22313/reik.2018.16.2.411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p094.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empirical Analyses of Factors Shaping the Relationship between Housing Price and Trading Volume based on Bounded Rationality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.15793/kspr.2018.97..001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p096.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Impact of the Trading Volume on Prices &amp; Prices Volatility of Housing Market in Seoul and the Whole Country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공공정책연구</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.37103/kapp.21.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer Sentiment in On-line Community and the Variation of Real Estate Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.22313/reik.2019.17.4.31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p103.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Dynamic Causal Relationship between Housing Price and Housing Trading Volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.22313/reik.2020.18.1.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p106.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Interaction of Apartment Price and Transaction Volumein Seoul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부동산학보</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.31303/krear.2020.83.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Behavioral Economic Analysis of Housing Transaction Volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부동산학연구</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.19172/kreaa.26.3.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Big Data Time Series Analysis of the Relationship Between News Coverage, Apartment Price and Trading Volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korea Association Of Real Estate Law</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.32989/rel.2020.24.2.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Monthly Effect of Apartment Price and Transaction Volume: Focusing on New Cities in the Metropolitan Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of the Korea Academia-Industrial cooperation Society</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.5762/kais.2022.23.3.273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effects of Consumer Sentiment, Interest Rate, and Transaction Volume on Housing Price Using the BVAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Journal of Humanities and Social sciences 21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.22143/hss21.14.2.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Causality of Housing Price and Trading by Cyclical Variation: Focused on Housing market of Seoul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">대한부동산학회지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.37407/kres.2024.42.1.211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic Relationship between Housing Sales Price and Transaction Volume by Housing Type in the Metropolitan Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Journal of the Korea Contents Association</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.5392/jkca.2024.24.01.621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate News Data by Living District in Seoul Trend Analysis Research Through Topic Modeling and Sentiment Analysis: Focusing on Apartment and Non-Apartment Transaction Volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정보과학회 컴퓨팅의 실제 논문지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.5626/ktcp.2026.32.3.89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Censored Sample Bias, Macroeconomic Factors, and Time on Market of Residential Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Real Estate Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10835547.1994.12090750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exploring Spatial Effects on Urban Housing Duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environment and Planning A Economy and Space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1068/a35170</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">비</t>
+      <t xml:space="preserve">수요</t>
     </r>
     <r>
       <rPr>
@@ -2722,7 +2514,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MLS </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -2730,7 +2522,215 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">포털</t>
+      <t xml:space="preserve">관심</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relationship Among News Coverage, Consumers’ Sentiment, Prices, and Trading Volume in Housing Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.24957/hsr.2017.25.3.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p092.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Effects of News Big Data and Google Information Search on Apartment Transaction Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential Environment Institute Of Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.22313/reik.2018.16.2.411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p094.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empirical Analyses of Factors Shaping the Relationship between Housing Price and Trading Volume based on Bounded Rationality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.15793/kspr.2018.97..001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p096.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Impact of the Trading Volume on Prices &amp; Prices Volatility of Housing Market in Seoul and the Whole Country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공공정책연구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.37103/kapp.21.3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer Sentiment in On-line Community and the Variation of Real Estate Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.22313/reik.2019.17.4.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p103.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Dynamic Causal Relationship between Housing Price and Housing Trading Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.22313/reik.2020.18.1.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p106.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Interaction of Apartment Price and Transaction Volumein Seoul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부동산학보</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.31303/krear.2020.83.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behavioral Economic Analysis of Housing Transaction Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부동산학연구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.19172/kreaa.26.3.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big Data Time Series Analysis of the Relationship Between News Coverage, Apartment Price and Trading Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korea Association Of Real Estate Law</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.32989/rel.2020.24.2.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Monthly Effect of Apartment Price and Transaction Volume: Focusing on New Cities in the Metropolitan Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of the Korea Academia-Industrial cooperation Society</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.5762/kais.2022.23.3.273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effects of Consumer Sentiment, Interest Rate, and Transaction Volume on Housing Price Using the BVAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Journal of Humanities and Social sciences 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.22143/hss21.14.2.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Causality of Housing Price and Trading by Cyclical Variation: Focused on Housing market of Seoul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대한부동산학회지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.37407/kres.2024.42.1.211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamic Relationship between Housing Sales Price and Transaction Volume by Housing Type in the Metropolitan Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Journal of the Korea Contents Association</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.5392/jkca.2024.24.01.621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate News Data by Living District in Seoul Trend Analysis Research Through Topic Modeling and Sentiment Analysis: Focusing on Apartment and Non-Apartment Transaction Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정보과학회 컴퓨팅의 실제 논문지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.5626/ktcp.2026.32.3.89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Censored Sample Bias, Macroeconomic Factors, and Time on Market of Residential Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Real Estate Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10835547.1994.12090750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exploring Spatial Effects on Urban Housing Duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Environment and Planning A Economy and Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1068/a35170</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비</t>
     </r>
     <r>
       <rPr>
@@ -2739,7 +2739,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">MLS </t>
     </r>
     <r>
       <rPr>
@@ -2747,7 +2747,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">중개 </t>
+      <t xml:space="preserve">포털</t>
     </r>
     <r>
       <rPr>
@@ -2756,7 +2756,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -2764,7 +2764,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">확인</t>
+      <t xml:space="preserve">중개 </t>
     </r>
     <r>
       <rPr>
@@ -2773,43 +2773,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelling a property's time to sale by inflating its previous selling price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of the Operational Research Society</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1057/jors.2011.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marketing Time and Sales Price of Residential Properties in Akure, Nigeria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of economics and sustainable development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A hybrid neural network for predicting Days on Market a measure of liquidity in real estate industry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Knowledge-Based Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.knosys.2020.106417</t>
-  </si>
-  <si>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2817,16 +2790,43 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MLS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시장 </t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelling a property's time to sale by inflating its previous selling price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of the Operational Research Society</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1057/jors.2011.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing Time and Sales Price of Residential Properties in Akure, Nigeria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of economics and sustainable development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A hybrid neural network for predicting Days on Market a measure of liquidity in real estate industry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knowledge-Based Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.knosys.2020.106417</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2834,7 +2834,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">MLS </t>
     </r>
     <r>
       <rPr>
@@ -2842,7 +2842,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">확인</t>
+      <t xml:space="preserve">시장 </t>
     </r>
     <r>
       <rPr>
@@ -2851,155 +2851,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key determinants of time on the market: an analysis of residential housing market in Sri Lanka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Journal of Housing Markets and Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/ijhma-06-2020-0071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Impacts of Property Features on Time on Market of Real Estate Assets in Lagos Metropolis, Nigeria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIOSUN Journal of Engineering and Environmental Sciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.36108/ujees/2202.40.0210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p032.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Repeat Time-On-The-Market Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Urban Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.jue.2019.04.005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submarket Dynamics of Time to Sale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/j.1540-6229.2006.00171.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Probability of Sale for Residential Real Estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Housing Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10835547.2007.12091978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spatial Heterogeneity in Listing Duration: The Influence of Relative Location to Marketability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10835547.2009.12092005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Are homes hot or cold potatoes? The distribution of marketing time in the housing market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regional Science and Urban Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2011.08.010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days on market and home sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The RAND Journal of Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1756-2171.12022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Probability of Sale and Price Premiums in Withdrawn Auctioned Properties*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urban Studies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1177/0042098014529341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">경매 시장</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p016.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does Time-on-Market Measurement Matter?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Journal of Real Estate Finance and Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-013-9450-z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For sale… but for how long? a methodological proposal for estimating time-on-the-market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Journal of Strategic Property Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.3846/1648715x.2015.1072746</t>
-  </si>
-  <si>
+      <t xml:space="preserve">(</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가천대 도서관 로그인 후 </t>
+      <t xml:space="preserve">확인</t>
     </r>
     <r>
       <rPr>
@@ -3008,25 +2868,155 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DOI </t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key determinants of time on the market: an analysis of residential housing market in Sri Lanka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Journal of Housing Markets and Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/ijhma-06-2020-0071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Impacts of Property Features on Time on Market of Real Estate Assets in Lagos Metropolis, Nigeria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIOSUN Journal of Engineering and Environmental Sciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.36108/ujees/2202.40.0210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p032.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Repeat Time-On-The-Market Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Urban Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.jue.2019.04.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submarket Dynamics of Time to Sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/j.1540-6229.2006.00171.x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Probability of Sale for Residential Real Estate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Housing Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10835547.2007.12091978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spatial Heterogeneity in Listing Duration: The Influence of Relative Location to Marketability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10835547.2009.12092005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are homes hot or cold potatoes? The distribution of marketing time in the housing market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regional Science and Urban Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2011.08.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days on market and home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The RAND Journal of Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1756-2171.12022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Probability of Sale and Price Premiums in Withdrawn Auctioned Properties*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urban Studies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1177/0042098014529341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">경매 시장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p016.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does Time-on-Market Measurement Matter?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Journal of Real Estate Finance and Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-013-9450-z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For sale… but for how long? a methodological proposal for estimating time-on-the-market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Journal of Strategic Property Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.3846/1648715x.2015.1072746</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">링크</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">무료 링크가 다른 논문</t>
+      <t xml:space="preserve">가천대 도서관 로그인 후 </t>
     </r>
     <r>
       <rPr>
@@ -3035,7 +3025,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">DOI </t>
     </r>
     <r>
       <rPr>
@@ -3043,7 +3033,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">임대료 설정 논문</t>
+      <t xml:space="preserve">링크</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무료 링크가 다른 논문</t>
     </r>
     <r>
       <rPr>
@@ -3052,7 +3052,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -3060,35 +3060,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">으로 연결됨 → 도서관 전자저널로 받을 것</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Fire Sales" in Housing Market: Is the House-Search Process Similar to a Theme Park Visit?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Real Estate Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.53383/100144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p010.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제목 정정</t>
+      <t xml:space="preserve">임대료 설정 논문</t>
     </r>
     <r>
       <rPr>
@@ -3097,7 +3069,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: Crossref </t>
+      <t xml:space="preserve">)</t>
     </r>
     <r>
       <rPr>
@@ -3105,7 +3077,35 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">제목 결손</t>
+      <t xml:space="preserve">으로 연결됨 → 도서관 전자저널로 받을 것</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Fire Sales" in Housing Market: Is the House-Search Process Similar to a Theme Park Visit?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Real Estate Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.53383/100144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p010.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제목 정정</t>
     </r>
     <r>
       <rPr>
@@ -3114,7 +3114,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve">: Crossref </t>
     </r>
     <r>
       <rPr>
@@ -3122,128 +3122,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원문으로 확인</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Effect of Relisting on House Selling Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of real estate finance and economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-015-9503-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Spatiotemporal Solution for the Simultaneous Sale Price and Time‐on‐the‐Market Problem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Measuring the influence of space and time effects on time on the market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1177/0042098015596923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The influence of house, seller, and locational factors on the probability of sale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Housing Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2018.09.009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solving Old Puzzles with New Tricks: Addressing Endogeneity and Nonlinearity in Time-on-Market Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/08965803.2020.1844476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average time to sell a property and credit conditions: Evidence from the Italian housing market survey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulletin of Economic Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/boer.12284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time on the Market and Probability of Sale Using a Generalized Geometric Hazard Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Econometric Methods</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1515/jem-2020-0017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modeling home property listings’ time-on-market duration and listing outcome using copula-based competing risk method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Transport and Land Use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.5198/jtlu.2024.2447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p033.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apartment prices, the business cycle and time on market: Evidence from Bucharest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.3846/ijspm.2025.23319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquidity in housing markets: the effect of news sentiment on time on market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of European Real Estate Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/jerer-12-2025-0098</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">무료 원문</t>
+      <t xml:space="preserve">제목 결손</t>
     </r>
     <r>
       <rPr>
@@ -3252,7 +3131,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -3260,7 +3139,128 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">직접 받기</t>
+      <t xml:space="preserve">원문으로 확인</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Effect of Relisting on House Selling Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of real estate finance and economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-015-9503-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Spatiotemporal Solution for the Simultaneous Sale Price and Time‐on‐the‐Market Problem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measuring the influence of space and time effects on time on the market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1177/0042098015596923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The influence of house, seller, and locational factors on the probability of sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Housing Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2018.09.009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solving Old Puzzles with New Tricks: Addressing Endogeneity and Nonlinearity in Time-on-Market Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/08965803.2020.1844476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average time to sell a property and credit conditions: Evidence from the Italian housing market survey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulletin of Economic Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/boer.12284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time on the Market and Probability of Sale Using a Generalized Geometric Hazard Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Econometric Methods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1515/jem-2020-0017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modeling home property listings’ time-on-market duration and listing outcome using copula-based competing risk method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Transport and Land Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.5198/jtlu.2024.2447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p033.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartment prices, the business cycle and time on market: Evidence from Bucharest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.3846/ijspm.2025.23319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidity in housing markets: the effect of news sentiment on time on market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of European Real Estate Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/jerer-12-2025-0098</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무료 원문</t>
     </r>
     <r>
       <rPr>
@@ -3269,98 +3269,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.emerald.com/jerer/article-pdf/doi/10.1108/JERER-12-2025-0098/11860165/jerer-12-2025-0098en.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Understanding Housing Market Dynamics through a Joint Model of Time-on-Market Duration and Listing Outcome of Residential Property Listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of urban planning and development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1061/jupddm.upeng-5857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Listing Price, Time on Market, and Ultimate Selling Price: Causes and Effects of Listing Price Changes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asymmetric information and list-price reductions in the housing market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2013.03.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Effect of Listing Price Changes on the Selling Price of Single-Family Residential Homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-016-9558-z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signaling effects of recurrent list‐price reductions on the likelihood of house sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Journal of Financial Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/jfir.12308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/jfir.12308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An Investigation of the Major Influences of Residential Liquidity: A Multivariate Approach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bargaining over residential real estate: evidence from England</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.jue.2004.05.004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p039.pdf</t>
-  </si>
-  <si>
+      <t xml:space="preserve">(</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">받은 파일은 워킹페이퍼</t>
+      <t xml:space="preserve">직접 받기</t>
     </r>
     <r>
       <rPr>
@@ -3369,15 +3286,98 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.emerald.com/jerer/article-pdf/doi/10.1108/JERER-12-2025-0098/11860165/jerer-12-2025-0098en.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Understanding Housing Market Dynamics through a Joint Model of Time-on-Market Duration and Listing Outcome of Residential Property Listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of urban planning and development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1061/jupddm.upeng-5857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listing Price, Time on Market, and Ultimate Selling Price: Causes and Effects of Listing Price Changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asymmetric information and list-price reductions in the housing market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2013.03.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Effect of Listing Price Changes on the Selling Price of Single-Family Residential Homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-016-9558-z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signaling effects of recurrent list‐price reductions on the likelihood of house sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Journal of Financial Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/jfir.12308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/jfir.12308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An Investigation of the Major Influences of Residential Liquidity: A Multivariate Approach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bargaining over residential real estate: evidence from England</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.jue.2004.05.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p039.pdf</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">저자 공개본일 수 있음</t>
+      <t xml:space="preserve">받은 파일은 워킹페이퍼</t>
     </r>
     <r>
       <rPr>
@@ -3386,7 +3386,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -3394,7 +3394,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">인용</t>
+      <t xml:space="preserve">저자 공개본일 수 있음</t>
     </r>
     <r>
       <rPr>
@@ -3403,7 +3403,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -3411,365 +3411,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">쪽수는 게재본으로 확인</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Measuring price expectations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/17539260910978481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bidding Conventions and the Degree of Overpricing in the Market for Houses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1177/0042098010363496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparing alternative house price indices: evidence from asking prices in Malta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/17538271311306048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Comparative Analysis Of Asking And Traded Price Indices In Different Floor Area Subsegments Of The Residential Property Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate Management and Valuation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1515/remav-2015-0021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p048.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic and Static Asking Prices in the Sydney Housing Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economic Record</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1475-4932.12242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p049.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A More Timely House Price Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review of Economics and Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1162/rest_a_00634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can list prices accurately capture housing price trends? Insights from extreme markets conditions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finance Research Letters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.frl.2018.10.004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">House price index based on online listing information: The case of China</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2020.101715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Early Real Estate Indicators during the COVID-19 Crisis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Official Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.2478/jos-2022-0017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p056.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Web-scraping housing prices in real-time: The Covid-19 crisis in the UK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2022.101906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p060.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List prices and “hot” real estate markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.70013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Inventory–Sales Relationship in the Market for New Single‐Family Homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/j.1080-8620.2004.00106.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Running hot and cold in the urban home-ownership market: The experience of Japan?s major cities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Housing and the Built Environment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s10901-005-6762-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Housing Supply Absorption Rate Equation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-020-09815-z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p112.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquidity Imbalance in the Residential Real Estate Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10527001.2020.1776513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimating House Price Indexes in the Presence of Seller Reservation Prices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1162/003465306775565783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bidding Wars for Houses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/reec.12015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Properties that Sell at or above Listing Price: Strategic Pricing, Better Broker or Just Dumb Luck?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-019-09714-y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine Learning Insights: Exploring Key Factors Influencing Sale-to-List Ratio—Insights from SVM Classification and Recursive Feature Selection in the US Real Estate Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.3390/buildings14051471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic hierarchical network-based framework for constructing a predictive index of offer–listing price differences in real estate E-commerce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electronic Commerce Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s10660-026-10107-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incorporating the Number of Existing Home Sales into a Structural Model of the Market for Owner-Occupied Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1006/jhec.1995.1005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price spreads and residential housing market liquidity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/bf01099111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://libres.uncg.edu/ir/uncg/f/D_Winkler_Price_1995.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrating Real Estate Market Conditions into Home Price Forecasting Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10835547.2012.12092059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To Sell or Not to Sell: Measuring the Heat of the Housing Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/reec.12003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can Tightness in the Housing Market Help Predict Subsequent Home Price Appreciation? Evidence from the United States and the Netherlands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expectation, volatility and liquidity in the housing market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/00036846.2015.1023943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does liquidity affect housing market performance? An empirical study with spatial panel approach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Land Use Policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.landusepol.2016.05.008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market depth in the UK housing market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economic Research-Ekonomska Istraživanja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/1331677x.2018.1429289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.tandfonline.com/doi/pdf/10.1080/1331677X.2018.1429289?needAccess=true</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hot and cold seasons in Texas housing markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/ijhma-02-2020-0017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://scholarsphere.psu.edu/resources/8b45d64c-36f4-4294-a0a6-50926994da05/downloads/15638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquidity and prices: a cluster analysis of the German residential real estate market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Business Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11573-020-00990-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p111.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time‐varying impacts of expectations on housing markets across hot and cold phases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/infi.12408</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">복수</t>
+      <t xml:space="preserve">인용</t>
     </r>
     <r>
       <rPr>
@@ -3778,7 +3420,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -3786,7 +3428,365 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">불명 </t>
+      <t xml:space="preserve">쪽수는 게재본으로 확인</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measuring price expectations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/17539260910978481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bidding Conventions and the Degree of Overpricing in the Market for Houses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1177/0042098010363496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparing alternative house price indices: evidence from asking prices in Malta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/17538271311306048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Comparative Analysis Of Asking And Traded Price Indices In Different Floor Area Subsegments Of The Residential Property Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate Management and Valuation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1515/remav-2015-0021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p048.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamic and Static Asking Prices in the Sydney Housing Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economic Record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1475-4932.12242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p049.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A More Timely House Price Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review of Economics and Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1162/rest_a_00634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Can list prices accurately capture housing price trends? Insights from extreme markets conditions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finance Research Letters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.frl.2018.10.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House price index based on online listing information: The case of China</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2020.101715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Early Real Estate Indicators during the COVID-19 Crisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Official Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.2478/jos-2022-0017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p056.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web-scraping housing prices in real-time: The Covid-19 crisis in the UK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2022.101906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p060.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List prices and “hot” real estate markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.70013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Inventory–Sales Relationship in the Market for New Single‐Family Homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/j.1080-8620.2004.00106.x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Running hot and cold in the urban home-ownership market: The experience of Japan?s major cities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Housing and the Built Environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s10901-005-6762-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Housing Supply Absorption Rate Equation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-020-09815-z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p112.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidity Imbalance in the Residential Real Estate Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10527001.2020.1776513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimating House Price Indexes in the Presence of Seller Reservation Prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1162/003465306775565783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bidding Wars for Houses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/reec.12015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Properties that Sell at or above Listing Price: Strategic Pricing, Better Broker or Just Dumb Luck?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-019-09714-y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machine Learning Insights: Exploring Key Factors Influencing Sale-to-List Ratio—Insights from SVM Classification and Recursive Feature Selection in the US Real Estate Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.3390/buildings14051471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamic hierarchical network-based framework for constructing a predictive index of offer–listing price differences in real estate E-commerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electronic Commerce Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s10660-026-10107-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incorporating the Number of Existing Home Sales into a Structural Model of the Market for Owner-Occupied Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1006/jhec.1995.1005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price spreads and residential housing market liquidity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/bf01099111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://libres.uncg.edu/ir/uncg/f/D_Winkler_Price_1995.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrating Real Estate Market Conditions into Home Price Forecasting Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10835547.2012.12092059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To Sell or Not to Sell: Measuring the Heat of the Housing Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/reec.12003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Can Tightness in the Housing Market Help Predict Subsequent Home Price Appreciation? Evidence from the United States and the Netherlands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expectation, volatility and liquidity in the housing market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/00036846.2015.1023943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does liquidity affect housing market performance? An empirical study with spatial panel approach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land Use Policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.landusepol.2016.05.008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market depth in the UK housing market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economic Research-Ekonomska Istraživanja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/1331677x.2018.1429289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.tandfonline.com/doi/pdf/10.1080/1331677X.2018.1429289?needAccess=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hot and cold seasons in Texas housing markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/ijhma-02-2020-0017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://scholarsphere.psu.edu/resources/8b45d64c-36f4-4294-a0a6-50926994da05/downloads/15638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidity and prices: a cluster analysis of the German residential real estate market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Business Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11573-020-00990-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p111.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time‐varying impacts of expectations on housing markets across hot and cold phases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/infi.12408</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">복수</t>
     </r>
     <r>
       <rPr>
@@ -3795,7 +3795,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
@@ -3803,7 +3803,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">확인</t>
+      <t xml:space="preserve">불명 </t>
     </r>
     <r>
       <rPr>
@@ -3812,614 +3812,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Local Constant-Quality Housing Market Liquidity Indices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2024.103997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frozen Markets, Falling Prices: Illiquidity and Bounded Price Discovery in U.S. Neighborhood Housing Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-026-10080-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">House Search Duration in Hot and Cold Residential Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/j.1540-6229.2012.00329.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List price and sale price variation across the housing market cycle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/17538271011049731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List price and sales prices of residential properties during booms and busts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2013.01.003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">House prices at different stages of the buying/selling process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2016.04.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p050.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interpretation and measurement of the spread between asking and selling prices in the Italian residential market [Interpretazione e misura dello spread tra prezzi richiesti e prezzi di vendita nel mercato residenziale italiano]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valori e Valutazioni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.48264/vvsiev-20223102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p059.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forecasting Connecticut home sales in a BVAR framework using coincident and leading indexes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/bf00217392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Using Leading Indicators to Forecast U.S. Home Sales in a Bayesian Vector Autoregressive Framework</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1023/a:1007718725609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testing Alternative Theories of the Property Price-Trading Volume Correlation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10835547.2002.12091081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trading Volume and Price Dispersion in Housing Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Property Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/09599910802696615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transaction Volume and Price Dispersion in the Presale and Spot Real Estate Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-008-9161-z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Housing Price Dynamics in Time and Space: Predictability, Liquidity and Investor Returns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-009-9207-x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://link.springer.com/content/pdf/10.1007/s11146-009-9207-x.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Could We Have Predicted the Recent Downturn in Home Sales in the Four U.S. Census Regions?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10835547.2010.12092026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Economic Impact of Anticipated House Price Changes—Evidence from Home Sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/j.1540-6229.2010.00292.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trading Volume-Induced Spatial Autocorrelation in Real Estate Prices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-012-9375-y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://link.springer.com/content/pdf/10.1007/s11146-012-9375-y.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Housing prices and transaction volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2013.02.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p081.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price and transaction volume in the Dutch housing market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2012.07.002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p082.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Relationship between Trading Volume and Purchase Price Index Volatility in Apartment Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Business Administration Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.17092/jibr.2013.10.1.159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ripple effect in house prices and trading volume in the UK housing market: New viewpoint and evidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economic Modelling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.econmod.2014.03.026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anticipated vs. unanticipated house price movements and transaction volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2015.04.003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p086.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Sales Pair Counts: The&lt;i&gt;Organic&lt;/i&gt;Metric for Trading Volume in Housing Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INFORMATION CONTENT OF TRANSACTION VOLUME: THE HOUSING MARKET IN THE UNITED KINGDOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.3846/ijspm.2018.5219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://journals.vgtu.lt/index.php/IJSPM/article/download/5219/4510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The cause and outcomes of the ripple effect: housing prices and transaction volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The annals of regional science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s00168-018-0870-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Features of the ripple effect in the US regional housing markets: a viewpoint of nonsynchronous trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/12265934.2021.1925142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forecasting trading volume in local housing markets through a time-series model and a deep learning algorithm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Construction &amp; Architectural Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/ecam-10-2020-0850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Housing market spillovers through the lens of transaction volume: A new spillover index approach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Empirical Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.jempfin.2021.10.003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p116.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">House price seasonality, market activity, and the December discount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/1540-6229.12463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sale to list ratio, for-sale inventory, sale count, and housing value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/ijhma-08-2023-0113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spatial and temporal diffusion of property prices and sales across British regions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/ijhma-09-2023-0118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From Causes to Forecasts: Granger Causality and Machine Learning Predictions of Housing Sales in Türkiye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Istanbul Journal of Economics / İstanbul İktisat Dergisi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.26650/istjecon2025-1707729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Housing Market Spillovers in China via Trading Volume: A Comparison of Two Spillover Indexes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financial Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/fire.70004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From prediction to explanation for price–volume dynamics in real estate market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interface Focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1098/rsfs.2025.0069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p130.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fundamentals and Market Sentiment in Housing Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Housing Theory and Society</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/14036096.2016.1196240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://ira.lib.polyu.edu.hk/bitstream/10397/95907/1/Hui_Fundamentals_And_Market.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forecasting Short-Term Housing Transaction Volumes using Time-Series and Internet Search Queries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KSCE Journal of Civil Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s12205-019-1926-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Housing Prices and Transaction Volumes in Taiwan Region’s Six Major Cities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Financial Risk Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.4236/jfrm.2026.152007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p132.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forecasting Residential Real Estate Price Changes from Online Search Activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10835547.2013.12091364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intercity Information Diffusion and Price Discovery in Housing Markets: Evidence from Google Searches</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-014-9493-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online Information Search, Market Fundamentals and Apartment Real Estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-015-9496-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sentiment-based predictions of housing market turning points with Google trends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/ijhma-12-2014-0058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internet Search Behavior, Liquidity and Prices in the Housing Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p137.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home is where the ad is: online interest proxies housing demand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPJ Data Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1140/epjds/s13688-018-0176-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p138.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;i&gt;FEAR Index&lt;/i&gt;, city characteristics, and housing returns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Search Queries, Foreclosures, and House Prices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-020-09789-y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p140.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segmented Housing Search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Economic Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1257/aer.20141772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use of Google Trends to Predict the Real Estate Market: Evidence from the United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.53383/100332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p142.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Local Experiences, Search, and Spillovers in the Housing Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Journal of Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/jofi.13208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/jofi.13208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predicting Housing Price Trends in Poland: Online Social Engagement - Google Trends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.2478/remav-2023-0032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p144.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Housing search activity and quantiles-based predictability of housing price movements in the USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/ijhma-12-2023-0166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From digital search to deed: forecasting UK housing purchases in Spain using Google Trends across the Brexit divide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/jerer-07-2025-0060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">House hunting high and low: Constructing a Housing Search Index for Portugal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2026.102163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">배정일</t>
-  </si>
-  <si>
-    <t xml:space="preserve">마감</t>
-  </si>
-  <si>
-    <t xml:space="preserve">종류</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제출일</t>
-  </si>
-  <si>
-    <t xml:space="preserve">접수</t>
-  </si>
-  <si>
-    <t xml:space="preserve">짝점검</t>
-  </si>
-  <si>
-    <t xml:space="preserve">반려사유</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-17</t>
-  </si>
-  <si>
+      <t xml:space="preserve">(</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">예시</t>
+      <t xml:space="preserve">확인</t>
     </r>
     <r>
       <rPr>
@@ -4428,15 +3829,614 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local Constant-Quality Housing Market Liquidity Indices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2024.103997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frozen Markets, Falling Prices: Illiquidity and Bounded Price Discovery in U.S. Neighborhood Housing Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-026-10080-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House Search Duration in Hot and Cold Residential Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/j.1540-6229.2012.00329.x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List price and sale price variation across the housing market cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/17538271011049731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List price and sales prices of residential properties during booms and busts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2013.01.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House prices at different stages of the buying/selling process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2016.04.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p050.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpretation and measurement of the spread between asking and selling prices in the Italian residential market [Interpretazione e misura dello spread tra prezzi richiesti e prezzi di vendita nel mercato residenziale italiano]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valori e Valutazioni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.48264/vvsiev-20223102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p059.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecasting Connecticut home sales in a BVAR framework using coincident and leading indexes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/bf00217392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using Leading Indicators to Forecast U.S. Home Sales in a Bayesian Vector Autoregressive Framework</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1023/a:1007718725609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing Alternative Theories of the Property Price-Trading Volume Correlation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10835547.2002.12091081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trading Volume and Price Dispersion in Housing Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Property Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/09599910802696615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transaction Volume and Price Dispersion in the Presale and Spot Real Estate Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-008-9161-z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Housing Price Dynamics in Time and Space: Predictability, Liquidity and Investor Returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-009-9207-x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://link.springer.com/content/pdf/10.1007/s11146-009-9207-x.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Could We Have Predicted the Recent Downturn in Home Sales in the Four U.S. Census Regions?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10835547.2010.12092026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Economic Impact of Anticipated House Price Changes—Evidence from Home Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/j.1540-6229.2010.00292.x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trading Volume-Induced Spatial Autocorrelation in Real Estate Prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-012-9375-y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://link.springer.com/content/pdf/10.1007/s11146-012-9375-y.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Housing prices and transaction volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2013.02.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p081.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price and transaction volume in the Dutch housing market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2012.07.002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p082.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Relationship between Trading Volume and Purchase Price Index Volatility in Apartment Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Business Administration Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.17092/jibr.2013.10.1.159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ripple effect in house prices and trading volume in the UK housing market: New viewpoint and evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economic Modelling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.econmod.2014.03.026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anticipated vs. unanticipated house price movements and transaction volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2015.04.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p086.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home Sales Pair Counts: The&lt;i&gt;Organic&lt;/i&gt;Metric for Trading Volume in Housing Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFORMATION CONTENT OF TRANSACTION VOLUME: THE HOUSING MARKET IN THE UNITED KINGDOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.3846/ijspm.2018.5219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://journals.vgtu.lt/index.php/IJSPM/article/download/5219/4510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The cause and outcomes of the ripple effect: housing prices and transaction volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The annals of regional science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s00168-018-0870-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Features of the ripple effect in the US regional housing markets: a viewpoint of nonsynchronous trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/12265934.2021.1925142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecasting trading volume in local housing markets through a time-series model and a deep learning algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Construction &amp; Architectural Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/ecam-10-2020-0850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Housing market spillovers through the lens of transaction volume: A new spillover index approach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Empirical Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.jempfin.2021.10.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p116.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House price seasonality, market activity, and the December discount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/1540-6229.12463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sale to list ratio, for-sale inventory, sale count, and housing value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/ijhma-08-2023-0113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spatial and temporal diffusion of property prices and sales across British regions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/ijhma-09-2023-0118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Causes to Forecasts: Granger Causality and Machine Learning Predictions of Housing Sales in Türkiye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Istanbul Journal of Economics / İstanbul İktisat Dergisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.26650/istjecon2025-1707729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Housing Market Spillovers in China via Trading Volume: A Comparison of Two Spillover Indexes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financial Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/fire.70004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From prediction to explanation for price–volume dynamics in real estate market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interface Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1098/rsfs.2025.0069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p130.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundamentals and Market Sentiment in Housing Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Housing Theory and Society</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/14036096.2016.1196240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://ira.lib.polyu.edu.hk/bitstream/10397/95907/1/Hui_Fundamentals_And_Market.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecasting Short-Term Housing Transaction Volumes using Time-Series and Internet Search Queries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KSCE Journal of Civil Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s12205-019-1926-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Housing Prices and Transaction Volumes in Taiwan Region’s Six Major Cities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Financial Risk Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.4236/jfrm.2026.152007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p132.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecasting Residential Real Estate Price Changes from Online Search Activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10835547.2013.12091364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intercity Information Diffusion and Price Discovery in Housing Markets: Evidence from Google Searches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-014-9493-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online Information Search, Market Fundamentals and Apartment Real Estate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-015-9496-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentiment-based predictions of housing market turning points with Google trends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/ijhma-12-2014-0058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet Search Behavior, Liquidity and Prices in the Housing Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p137.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home is where the ad is: online interest proxies housing demand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPJ Data Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1140/epjds/s13688-018-0176-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p138.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;i&gt;FEAR Index&lt;/i&gt;, city characteristics, and housing returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Search Queries, Foreclosures, and House Prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-020-09789-y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p140.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segmented Housing Search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">American Economic Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1257/aer.20141772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use of Google Trends to Predict the Real Estate Market: Evidence from the United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.53383/100332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p142.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local Experiences, Search, and Spillovers in the Housing Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Journal of Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/jofi.13208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/jofi.13208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predicting Housing Price Trends in Poland: Online Social Engagement - Google Trends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.2478/remav-2023-0032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p144.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Housing search activity and quantiles-based predictability of housing price movements in the USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/ijhma-12-2023-0166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From digital search to deed: forecasting UK housing purchases in Spain using Google Trends across the Brexit divide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/jerer-07-2025-0060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House hunting high and low: Constructing a Housing Search Index for Portugal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2026.102163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">배정일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마감</t>
+  </si>
+  <si>
+    <t xml:space="preserve">종류</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제출일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">접수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">짝점검</t>
+  </si>
+  <si>
+    <t xml:space="preserve">반려사유</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-17</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">완전</t>
+      <t xml:space="preserve">예시</t>
     </r>
     <r>
       <rPr>
@@ -4445,7 +4445,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -4453,7 +4453,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">짧은 둘 다</t>
+      <t xml:space="preserve">긴</t>
     </r>
     <r>
       <rPr>
@@ -4462,38 +4462,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">S4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">주택도시금융연구</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.38100/jhuf.2021.6.2.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-23</t>
-  </si>
-  <si>
+      <t xml:space="preserve">·</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">파일럿</t>
+      <t xml:space="preserve">짧은 둘 다</t>
     </r>
     <r>
       <rPr>
@@ -4502,15 +4479,38 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주택도시금융연구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.38100/jhuf.2021.6.2.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-23</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">전원 같은 논문</t>
+      <t xml:space="preserve">파일럿</t>
     </r>
     <r>
       <rPr>
@@ -4519,26 +4519,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">S3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.24957/hsr.2019.27.1.05</t>
-  </si>
-  <si>
+      <t xml:space="preserve">(</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">전원 비교</t>
+      <t xml:space="preserve">전원 같은 논문</t>
     </r>
     <r>
       <rPr>
@@ -4547,15 +4536,26 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.24957/hsr.2019.27.1.05</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원석</t>
+      <t xml:space="preserve">전원 비교</t>
     </r>
     <r>
       <rPr>
@@ -4564,6 +4564,23 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">)</t>
     </r>
   </si>
@@ -4574,7 +4591,7 @@
     <t xml:space="preserve">2026-10-30</t>
   </si>
   <si>
-    <t xml:space="preserve">완전 정리</t>
+    <t xml:space="preserve">긴 정리</t>
   </si>
   <si>
     <t xml:space="preserve">10.21447/jup.2019.10.3.101</t>
@@ -17102,7 +17119,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
         <v>33</v>
       </c>

--- a/handover/유동성리뷰_담당자파일.xlsx
+++ b/handover/유동성리뷰_담당자파일.xlsx
@@ -245,7 +245,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">① 수요일</t>
+      <t xml:space="preserve">① 수요일 모임 날</t>
     </r>
     <r>
       <rPr>
@@ -254,7 +254,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: </t>
+      <t xml:space="preserve">(W1</t>
     </r>
     <r>
       <rPr>
@@ -262,7 +262,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">그 주 논문 원문을 구해 단톡방</t>
+      <t xml:space="preserve">만 </t>
     </r>
     <r>
       <rPr>
@@ -271,7 +271,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">10/19 </t>
     </r>
     <r>
       <rPr>
@@ -279,7 +279,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">드라이브에 올린다</t>
+      <t xml:space="preserve">월</t>
     </r>
     <r>
       <rPr>
@@ -288,7 +288,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">): </t>
     </r>
     <r>
       <rPr>
@@ -296,7 +296,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원문 상태가 </t>
+      <t xml:space="preserve">그 주 논문 원문을 구해 단톡방</t>
     </r>
     <r>
       <rPr>
@@ -305,7 +305,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">'</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -313,7 +313,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">받음</t>
+      <t xml:space="preserve">드라이브에 올린다</t>
     </r>
     <r>
       <rPr>
@@ -322,7 +322,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">'</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -330,7 +330,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이 아닌 것</t>
+      <t xml:space="preserve">원문 상태가 </t>
     </r>
     <r>
       <rPr>
@@ -339,7 +339,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">). ② </t>
+      <t xml:space="preserve">'</t>
     </r>
     <r>
       <rPr>
@@ -347,7 +347,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">화요일 </t>
+      <t xml:space="preserve">받음</t>
     </r>
     <r>
       <rPr>
@@ -356,7 +356,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">18:00 </t>
+      <t xml:space="preserve">'</t>
     </r>
     <r>
       <rPr>
@@ -364,7 +364,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">마감 후</t>
+      <t xml:space="preserve">이 아닌 것</t>
     </r>
     <r>
       <rPr>
@@ -373,7 +373,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: </t>
+      <t xml:space="preserve">). ② </t>
     </r>
     <r>
       <rPr>
@@ -381,7 +381,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">워드</t>
+      <t xml:space="preserve">화요일 </t>
     </r>
     <r>
       <rPr>
@@ -390,7 +390,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">18:00 </t>
     </r>
     <r>
       <rPr>
@@ -398,7 +398,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">시트가 들어왔는지</t>
+      <t xml:space="preserve">마감 후</t>
     </r>
     <r>
       <rPr>
@@ -407,7 +407,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
@@ -415,7 +415,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">빈칸</t>
+      <t xml:space="preserve">워드</t>
     </r>
     <r>
       <rPr>
@@ -432,7 +432,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">쪽수 누락이 없는지만 본다</t>
+      <t xml:space="preserve">시트가 들어왔는지</t>
     </r>
     <r>
       <rPr>
@@ -441,7 +441,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -449,7 +449,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">내용이 맞는지는 판단하지 않는다</t>
+      <t xml:space="preserve">빈칸</t>
     </r>
     <r>
       <rPr>
@@ -458,7 +458,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. ③ </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -466,7 +466,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">주차별배정의 노란 칸을 채운다</t>
+      <t xml:space="preserve">쪽수 누락이 없는지만 본다</t>
     </r>
     <r>
       <rPr>
@@ -475,7 +475,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. ④ </t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -483,7 +483,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">본인 배정 논문도 정리한다</t>
+      <t xml:space="preserve">내용이 맞는지는 판단하지 않는다</t>
     </r>
     <r>
       <rPr>
@@ -492,17 +492,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">. ③ </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">내용 대조는 </t>
+      <t xml:space="preserve">주차별배정의 노란 칸을 채운다</t>
     </r>
     <r>
       <rPr>
@@ -511,7 +509,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Claude</t>
+      <t xml:space="preserve">. ④ </t>
     </r>
     <r>
       <rPr>
@@ -519,7 +517,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가 한다</t>
+      <t xml:space="preserve">본인 배정 논문도 정리한다</t>
     </r>
     <r>
       <rPr>
@@ -528,15 +526,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: Claude</t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가 원문으로 따로 정리해 둔 것</t>
+      <t xml:space="preserve">내용 대조는 </t>
     </r>
     <r>
       <rPr>
@@ -545,7 +545,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(1</t>
+      <t xml:space="preserve">Claude</t>
     </r>
     <r>
       <rPr>
@@ -553,7 +553,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">차 추출</t>
+      <t xml:space="preserve">가 한다</t>
     </r>
     <r>
       <rPr>
@@ -562,7 +562,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">: Claude</t>
     </r>
     <r>
       <rPr>
@@ -570,7 +570,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">과 학생 정리</t>
+      <t xml:space="preserve">가 원문으로 따로 정리해 둔 것</t>
     </r>
     <r>
       <rPr>
@@ -579,7 +579,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(2</t>
+      <t xml:space="preserve">(1</t>
     </r>
     <r>
       <rPr>
@@ -604,7 +604,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">를 맞춘 대조표를 매주 만들고</t>
+      <t xml:space="preserve">과 학생 정리</t>
     </r>
     <r>
       <rPr>
@@ -613,7 +613,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve">(2</t>
     </r>
     <r>
       <rPr>
@@ -621,7 +621,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">다른 곳은 교수가 판정한다</t>
+      <t xml:space="preserve">차 추출</t>
     </r>
     <r>
       <rPr>
@@ -630,7 +630,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">)</t>
     </r>
     <r>
       <rPr>
@@ -638,7 +638,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원석은 </t>
+      <t xml:space="preserve">를 맞춘 대조표를 매주 만들고</t>
     </r>
     <r>
       <rPr>
@@ -647,7 +647,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Claude </t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -655,7 +655,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">정리를 보지 않는다</t>
+      <t xml:space="preserve">다른 곳은 교수가 판정한다</t>
     </r>
     <r>
       <rPr>
@@ -664,20 +664,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">시트 안내</t>
-  </si>
-  <si>
+      <t xml:space="preserve">. </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">사람별일정</t>
+      <t xml:space="preserve">원석은 </t>
     </r>
     <r>
       <rPr>
@@ -686,7 +681,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: 8</t>
+      <t xml:space="preserve">Claude </t>
     </r>
     <r>
       <rPr>
@@ -694,7 +689,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">명이 몇 주차에 무엇을 하는지 한눈에 보는 표</t>
+      <t xml:space="preserve">정리를 보지 않는다</t>
     </r>
     <r>
       <rPr>
@@ -703,15 +698,20 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">시트 안내</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가장 먼저 볼 시트</t>
+      <t xml:space="preserve">사람별일정</t>
     </r>
     <r>
       <rPr>
@@ -720,17 +720,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">: 8</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">종합</t>
+      <t xml:space="preserve">명이 몇 주차에 무엇을 하는지 한눈에 보는 표</t>
     </r>
     <r>
       <rPr>
@@ -739,7 +737,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">148: </t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -747,7 +745,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이번 리뷰에서 정리할 논문 전체</t>
+      <t xml:space="preserve">가장 먼저 볼 시트</t>
     </r>
     <r>
       <rPr>
@@ -756,15 +754,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">교수 승인 </t>
+      <t xml:space="preserve">종합</t>
     </r>
     <r>
       <rPr>
@@ -773,7 +773,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">10/11). </t>
+      <t xml:space="preserve">148: </t>
     </r>
     <r>
       <rPr>
@@ -781,7 +781,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">주차</t>
+      <t xml:space="preserve">이번 리뷰에서 정리할 논문 전체</t>
     </r>
     <r>
       <rPr>
@@ -790,7 +790,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -798,7 +798,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">담당</t>
+      <t xml:space="preserve">교수 승인 </t>
     </r>
     <r>
       <rPr>
@@ -807,7 +807,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">10/11). </t>
     </r>
     <r>
       <rPr>
@@ -815,7 +815,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원문 받는 법이 함께 있다</t>
+      <t xml:space="preserve">주차</t>
     </r>
     <r>
       <rPr>
@@ -824,7 +824,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. p115·p033</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -832,7 +832,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">은 정리 예시라 배정하지 않는다</t>
+      <t xml:space="preserve">담당</t>
     </r>
     <r>
       <rPr>
@@ -841,17 +841,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">·</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">주차별배정</t>
+      <t xml:space="preserve">원문 받는 법이 함께 있다</t>
     </r>
     <r>
       <rPr>
@@ -860,7 +858,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: </t>
+      <t xml:space="preserve">. p115·p033</t>
     </r>
     <r>
       <rPr>
@@ -868,7 +866,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">매주 누가 어떤 논문을 하는지</t>
+      <t xml:space="preserve">은 정리 예시라 배정하지 않는다</t>
     </r>
     <r>
       <rPr>
@@ -877,15 +875,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. W1~W5</t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">는 </t>
+      <t xml:space="preserve">주차별배정</t>
     </r>
     <r>
       <rPr>
@@ -894,7 +894,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
@@ -902,7 +902,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">인 </t>
+      <t xml:space="preserve">매주 누가 어떤 논문을 하는지</t>
     </r>
     <r>
       <rPr>
@@ -911,7 +911,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">. W1~W5</t>
     </r>
     <r>
       <rPr>
@@ -919,7 +919,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">편</t>
+      <t xml:space="preserve">는 </t>
     </r>
     <r>
       <rPr>
@@ -928,7 +928,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, W6</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -936,7 +936,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">부터 </t>
+      <t xml:space="preserve">인 </t>
     </r>
     <r>
       <rPr>
@@ -953,7 +953,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">인 </t>
+      <t xml:space="preserve">편</t>
     </r>
     <r>
       <rPr>
@@ -962,7 +962,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">, W6</t>
     </r>
     <r>
       <rPr>
@@ -970,7 +970,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">편</t>
+      <t xml:space="preserve">부터 </t>
     </r>
     <r>
       <rPr>
@@ -979,7 +979,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -987,7 +987,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">수요일 배정</t>
+      <t xml:space="preserve">인 </t>
     </r>
     <r>
       <rPr>
@@ -996,7 +996,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -1004,7 +1004,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">다음 주 화요일 </t>
+      <t xml:space="preserve">편</t>
     </r>
     <r>
       <rPr>
@@ -1013,7 +1013,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">18:00 </t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -1021,7 +1021,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">마감</t>
+      <t xml:space="preserve">매주 수요일 모임에서 배정</t>
     </r>
     <r>
       <rPr>
@@ -1030,7 +1030,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -1038,7 +1038,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">노란 칸</t>
+      <t xml:space="preserve">다음 모임 전날 화요일 </t>
     </r>
     <r>
       <rPr>
@@ -1047,7 +1047,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">18:00 </t>
     </r>
     <r>
       <rPr>
@@ -1055,7 +1055,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원문 배포</t>
+      <t xml:space="preserve">마감</t>
     </r>
     <r>
       <rPr>
@@ -1064,7 +1064,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">. W1</t>
     </r>
     <r>
       <rPr>
@@ -1072,7 +1072,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">제출일</t>
+      <t xml:space="preserve">만 </t>
     </r>
     <r>
       <rPr>
@@ -1081,7 +1081,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">10/19 </t>
     </r>
     <r>
       <rPr>
@@ -1089,7 +1089,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">워드</t>
+      <t xml:space="preserve">배포</t>
     </r>
     <r>
       <rPr>
@@ -1098,7 +1098,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -1106,7 +1106,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">시트</t>
+      <t xml:space="preserve">첫 모임 </t>
     </r>
     <r>
       <rPr>
@@ -1115,7 +1115,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">10/28. </t>
     </r>
     <r>
       <rPr>
@@ -1123,7 +1123,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">접수</t>
+      <t xml:space="preserve">노란 칸</t>
     </r>
     <r>
       <rPr>
@@ -1132,7 +1132,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -1140,7 +1140,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">반려사유</t>
+      <t xml:space="preserve">원문 배포</t>
     </r>
     <r>
       <rPr>
@@ -1149,7 +1149,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -1157,7 +1157,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">을 원석이 채운다</t>
+      <t xml:space="preserve">제출일</t>
     </r>
     <r>
       <rPr>
@@ -1166,7 +1166,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -1174,7 +1174,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">맨 위 회색 </t>
+      <t xml:space="preserve">워드</t>
     </r>
     <r>
       <rPr>
@@ -1183,7 +1183,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">'</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -1191,7 +1191,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">예시</t>
+      <t xml:space="preserve">시트</t>
     </r>
     <r>
       <rPr>
@@ -1200,7 +1200,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">' </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -1208,7 +1208,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">행을 따라 쓴다</t>
+      <t xml:space="preserve">접수</t>
     </r>
     <r>
       <rPr>
@@ -1217,17 +1217,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">·</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">진행현황</t>
+      <t xml:space="preserve">반려사유</t>
     </r>
     <r>
       <rPr>
@@ -1236,7 +1234,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: </t>
+      <t xml:space="preserve">)</t>
     </r>
     <r>
       <rPr>
@@ -1244,7 +1242,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">주차별배정의 노란 칸을 채우면 자동으로 계산된다</t>
+      <t xml:space="preserve">을 원석이 채운다</t>
     </r>
     <r>
       <rPr>
@@ -1253,7 +1251,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -1261,7 +1259,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">수식</t>
+      <t xml:space="preserve">맨 위 회색 </t>
     </r>
     <r>
       <rPr>
@@ -1270,7 +1268,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">). </t>
+      <t xml:space="preserve">'</t>
     </r>
     <r>
       <rPr>
@@ -1278,7 +1276,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">매주 수요일 보고에 이 숫자를 쓴다</t>
+      <t xml:space="preserve">예시</t>
     </r>
     <r>
       <rPr>
@@ -1287,17 +1285,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">' </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">분류틀</t>
+      <t xml:space="preserve">행을 따라 쓴다</t>
     </r>
     <r>
       <rPr>
@@ -1306,15 +1302,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">단계</t>
+      <t xml:space="preserve">진행현황</t>
     </r>
     <r>
       <rPr>
@@ -1323,7 +1321,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
@@ -1331,7 +1329,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">기능</t>
+      <t xml:space="preserve">주차별배정의 노란 칸을 채우면 자동으로 계산된다</t>
     </r>
     <r>
       <rPr>
@@ -1340,7 +1338,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -1348,7 +1346,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">시장 코드의 뜻과 </t>
+      <t xml:space="preserve">수식</t>
     </r>
     <r>
       <rPr>
@@ -1357,7 +1355,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">148</t>
+      <t xml:space="preserve">). </t>
     </r>
     <r>
       <rPr>
@@ -1365,7 +1363,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">편의 교차표</t>
+      <t xml:space="preserve">매주 수요일 보고에 이 숫자를 쓴다</t>
     </r>
     <r>
       <rPr>
@@ -1374,15 +1372,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">수식</t>
+      <t xml:space="preserve">분류틀</t>
     </r>
     <r>
       <rPr>
@@ -1391,17 +1391,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">).</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">: </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">선별과정</t>
+      <t xml:space="preserve">단계</t>
     </r>
     <r>
       <rPr>
@@ -1410,7 +1408,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: 52,006</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -1418,7 +1416,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">건에서 </t>
+      <t xml:space="preserve">기능</t>
     </r>
     <r>
       <rPr>
@@ -1427,7 +1425,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">148</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -1435,7 +1433,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">편이 되기까지</t>
+      <t xml:space="preserve">시장 코드의 뜻과 </t>
     </r>
     <r>
       <rPr>
@@ -1444,7 +1442,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(PRISMA). </t>
+      <t xml:space="preserve">148</t>
     </r>
     <r>
       <rPr>
@@ -1452,7 +1450,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">논문 </t>
+      <t xml:space="preserve">편의 교차표</t>
     </r>
     <r>
       <rPr>
@@ -1461,7 +1459,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -1469,7 +1467,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">장의 숫자</t>
+      <t xml:space="preserve">수식</t>
     </r>
     <r>
       <rPr>
@@ -1478,7 +1476,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
+      <t xml:space="preserve">).</t>
     </r>
   </si>
   <si>
@@ -1488,7 +1486,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">전체</t>
+      <t xml:space="preserve">선별과정</t>
     </r>
     <r>
       <rPr>
@@ -1497,7 +1495,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">438: </t>
+      <t xml:space="preserve">: 52,006</t>
     </r>
     <r>
       <rPr>
@@ -1505,7 +1503,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">제목</t>
+      <t xml:space="preserve">건에서 </t>
     </r>
     <r>
       <rPr>
@@ -1514,7 +1512,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">148</t>
     </r>
     <r>
       <rPr>
@@ -1522,7 +1520,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">초록 선별을 통과한 </t>
+      <t xml:space="preserve">편이 되기까지</t>
     </r>
     <r>
       <rPr>
@@ -1531,7 +1529,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">438</t>
+      <t xml:space="preserve">(PRISMA). </t>
     </r>
     <r>
       <rPr>
@@ -1539,7 +1537,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">편과 각 편이 종합</t>
+      <t xml:space="preserve">논문 </t>
     </r>
     <r>
       <rPr>
@@ -1548,7 +1546,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
+      <t xml:space="preserve">3</t>
     </r>
     <r>
       <rPr>
@@ -1556,7 +1554,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">배경</t>
+      <t xml:space="preserve">장의 숫자</t>
     </r>
     <r>
       <rPr>
@@ -1565,15 +1563,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">증거지도 중 어디로 갔는지</t>
+      <t xml:space="preserve">전체</t>
     </r>
     <r>
       <rPr>
@@ -1582,20 +1582,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">노란 칸 입력 규칙</t>
-  </si>
-  <si>
+      <t xml:space="preserve">438: </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원문 배포</t>
+      <t xml:space="preserve">제목</t>
     </r>
     <r>
       <rPr>
@@ -1604,7 +1599,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: O. </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -1612,7 +1607,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">워드</t>
+      <t xml:space="preserve">초록 선별을 통과한 </t>
     </r>
     <r>
       <rPr>
@@ -1621,7 +1616,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">438</t>
     </r>
     <r>
       <rPr>
@@ -1629,7 +1624,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">시트</t>
+      <t xml:space="preserve">편과 각 편이 종합</t>
     </r>
     <r>
       <rPr>
@@ -1638,7 +1633,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: O(</t>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
@@ -1646,7 +1641,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">냈음</t>
+      <t xml:space="preserve">배경</t>
     </r>
     <r>
       <rPr>
@@ -1655,7 +1650,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) / X. </t>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
@@ -1663,7 +1658,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">접수</t>
+      <t xml:space="preserve">증거지도 중 어디로 갔는지</t>
     </r>
     <r>
       <rPr>
@@ -1672,15 +1667,20 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: O(</t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">노란 칸 입력 규칙</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">통과</t>
+      <t xml:space="preserve">원문 배포</t>
     </r>
     <r>
       <rPr>
@@ -1689,7 +1689,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) / </t>
+      <t xml:space="preserve">: O. </t>
     </r>
     <r>
       <rPr>
@@ -1697,7 +1697,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">반려 </t>
+      <t xml:space="preserve">워드</t>
     </r>
     <r>
       <rPr>
@@ -1706,7 +1706,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/ </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -1714,7 +1714,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">미제출</t>
+      <t xml:space="preserve">시트</t>
     </r>
     <r>
       <rPr>
@@ -1723,7 +1723,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">: O(</t>
     </r>
     <r>
       <rPr>
@@ -1731,7 +1731,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">반려는 빈칸이 있거나 쪽수가 없을 때만</t>
+      <t xml:space="preserve">냈음</t>
     </r>
     <r>
       <rPr>
@@ -1740,7 +1740,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">) / X. </t>
     </r>
     <r>
       <rPr>
@@ -1748,7 +1748,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">반려사유는 짧게</t>
+      <t xml:space="preserve">접수</t>
     </r>
     <r>
       <rPr>
@@ -1757,7 +1757,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">: O(</t>
     </r>
     <r>
       <rPr>
@@ -1765,7 +1765,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">예</t>
+      <t xml:space="preserve">통과</t>
     </r>
     <r>
       <rPr>
@@ -1774,7 +1774,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: </t>
+      <t xml:space="preserve">) / </t>
     </r>
     <r>
       <rPr>
@@ -1782,7 +1782,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">정의 칸 쪽수 없음</t>
+      <t xml:space="preserve">반려 </t>
     </r>
     <r>
       <rPr>
@@ -1791,17 +1791,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">).</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">/ </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원문 상태 </t>
+      <t xml:space="preserve">미제출</t>
     </r>
     <r>
       <rPr>
@@ -1810,7 +1808,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">'</t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -1818,7 +1816,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">도서관 전자저널</t>
+      <t xml:space="preserve">반려는 빈칸이 있거나 쪽수가 없을 때만</t>
     </r>
     <r>
       <rPr>
@@ -1827,7 +1825,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">'</t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -1835,7 +1833,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">은 학교 도서관 로그인 후 </t>
+      <t xml:space="preserve">반려사유는 짧게</t>
     </r>
     <r>
       <rPr>
@@ -1844,7 +1842,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DOI </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -1852,7 +1850,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">링크로 받는다</t>
+      <t xml:space="preserve">예</t>
     </r>
     <r>
       <rPr>
@@ -1861,7 +1859,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
@@ -1869,7 +1867,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">안 되면 상호대차</t>
+      <t xml:space="preserve">정의 칸 쪽수 없음</t>
     </r>
     <r>
       <rPr>
@@ -1878,7 +1876,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
+      <t xml:space="preserve">).</t>
     </r>
   </si>
   <si>
@@ -1905,7 +1903,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">한국 학술지</t>
+      <t xml:space="preserve">도서관 전자저널</t>
     </r>
     <r>
       <rPr>
@@ -1922,7 +1920,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">는 </t>
+      <t xml:space="preserve">은 학교 도서관 로그인 후 </t>
     </r>
     <r>
       <rPr>
@@ -1931,7 +1929,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">KCI</t>
+      <t xml:space="preserve">DOI </t>
     </r>
     <r>
       <rPr>
@@ -1939,7 +1937,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">에서 논문명 검색 → 원문보기</t>
+      <t xml:space="preserve">링크로 받는다</t>
     </r>
     <r>
       <rPr>
@@ -1956,7 +1954,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">안 되면 </t>
+      <t xml:space="preserve">안 되면 상호대차</t>
     </r>
     <r>
       <rPr>
@@ -1965,7 +1963,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">RISS·DBpia.</t>
+      <t xml:space="preserve">.</t>
     </r>
   </si>
   <si>
@@ -1992,7 +1990,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">받음</t>
+      <t xml:space="preserve">한국 학술지</t>
     </r>
     <r>
       <rPr>
@@ -2009,7 +2007,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">은 저장소 </t>
+      <t xml:space="preserve">는 </t>
     </r>
     <r>
       <rPr>
@@ -2018,7 +2016,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">papers/ </t>
+      <t xml:space="preserve">KCI</t>
     </r>
     <r>
       <rPr>
@@ -2026,7 +2024,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">폴더에 </t>
+      <t xml:space="preserve">에서 논문명 검색 → 원문보기</t>
     </r>
     <r>
       <rPr>
@@ -2035,7 +2033,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PDF</t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -2043,7 +2041,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가 있다</t>
+      <t xml:space="preserve">안 되면 </t>
     </r>
     <r>
       <rPr>
@@ -2052,15 +2050,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(pid </t>
-    </r>
+      <t xml:space="preserve">RISS·DBpia.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이름</t>
+      <t xml:space="preserve">원문 상태 </t>
     </r>
     <r>
       <rPr>
@@ -2069,20 +2069,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">).</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">숫자 출처</t>
-  </si>
-  <si>
+      <t xml:space="preserve">'</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">선별과정 시트의 수치는 저장소 </t>
+      <t xml:space="preserve">받음</t>
     </r>
     <r>
       <rPr>
@@ -2091,7 +2086,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">review/prisma_flow.md(2026-10-10 </t>
+      <t xml:space="preserve">'</t>
     </r>
     <r>
       <rPr>
@@ -2099,7 +2094,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">검색 실행 결과</t>
+      <t xml:space="preserve">은 저장소 </t>
     </r>
     <r>
       <rPr>
@@ -2108,7 +2103,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">papers/ </t>
     </r>
     <r>
       <rPr>
@@ -2116,7 +2111,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">에서 옮긴 값이다</t>
+      <t xml:space="preserve">폴더에 </t>
     </r>
     <r>
       <rPr>
@@ -2125,98 +2120,91 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">PDF</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">사람별 주간 논문 — 수요일에 받아 다음 주 화요일 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">가 있다</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">18:00</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">(pid </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">까지 워드 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">이름</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">숫자 출처</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">쪽 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">선별과정 시트의 수치는 저장소 </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">review/prisma_flow.md(2026-10-10 </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">구글시트 행을 낸다</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">검색 실행 결과</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">날짜는 배정일</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">에서 옮긴 값이다</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
@@ -2226,616 +2214,355 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">이름</t>
-  </si>
-  <si>
-    <t xml:space="preserve">구분</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W01 (10-21)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W02 (10-28)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W03 (11-04)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W04 (11-11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W05 (11-18)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W06 (11-25)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W07 (12-02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W08 (12-09)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W09 (12-16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W10 (12-23)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W11 (12-30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W12 (01-06)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전우성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">박사</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p023 Factors Affecting the Days on Market of Resid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p099 Intervention Analysis of Apartment Trading Vo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p108 Behavioral Economic Analysis of Housing Trans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p109 Big Data Time Series Analysis of the Relation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p105 The Repeat Time-On-The-Market Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p015 Days on market and home sales
-p021 A Spatiotemporal Solution for the Simultaneou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p046 Comparing alternative house price indices: ev
-p052 A More Timely House Price Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p024 Liquidity Imbalance in the Residential Real E
-p039 Bargaining over residential real estate: evid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p040 Estimating House Price Indexes in the Presenc
-p064 Dynamic hierarchical network-based framework </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p073 Transaction Volume and Price Dispersion in th
-p082 Price and transaction volume in the Dutch hou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p132 Housing Prices and Transaction Volumes in Tai
-p141 Segmented Housing Search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p143 Local Experiences, Search, and Spillovers in 
-p145 Housing search activity and quantiles-based p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">손수연</t>
-  </si>
-  <si>
-    <t xml:space="preserve">석사</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p025 The Effect of Apartment Housing Characteristi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p077 Do Housing Trading Volume Explain Housing Pri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p117 A Study on the Monthly Effect of Apartment Pr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p119 Effects of Consumer Sentiment, Interest Rate,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p019 Marketing Time and Sales Price of Residential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p007 The Probability of Sale for Residential Real 
-p022 Measuring the influence of space and time eff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p051 The Effect of Listing Price Changes on the Se
-p054 House price index based on online listing inf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p070 The Inventory–Sales Relationship in the Marke
-p111 Liquidity and prices: a cluster analysis of t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p050 House prices at different stages of the buyin
-p118 Time‐varying impacts of expectations on housi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p075 Housing Price Dynamics in Time and Space: Pre
-p083 The Relationship between Trading Volume and P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p013 House Search Duration in Hot and Cold Residen
-p116 Housing market spillovers through the lens of</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p136 Sentiment-based predictions of housing market
-p146 From digital search to deed: forecasting UK h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">최찬미</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p035 Determinants of Time to Close in Housing Tran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p093 The Relationship between Asymmetric Volatilit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p122 A Study on the Causality of Housing Price and</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p148 Real Estate News Data by Living District in S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p027 A hybrid neural network for predicting Days o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p008 Spatial Heterogeneity in Listing Duration: Th
-p029 Solving Old Puzzles with New Tricks: Addressi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p026 The influence of house, seller, and locationa
-p112 A Housing Supply Absorption Rate Equation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p053 Can list prices accurately capture housing pr
-p124 Local Constant-Quality Housing Market Liquidi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p097 Home Sales Pair Counts: The&lt;i&gt;Organic&lt;/i&gt;Metr
-p131 Frozen Markets, Falling Prices: Illiquidity a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p042 List price and sale price variation across th
-p085 Ripple effect in house prices and trading vol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p120 House price seasonality, market activity, and
-p138 Home is where the ad is: online interest prox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p137 Internet Search Behavior, Liquidity and Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이원석</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">학부 </t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">사람별 주간 논문 — 수요일 모임에서 받아 다음 모임 전날 화요일 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3·</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">18:00</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">담당</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p058 A Study on the Impact of Asking Price and Sal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p095 Causality and Predictability of Price-Volume </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p123 Dynamic Relationship between Housing Sales Pr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p002 The Duration of Marketing Time of Residential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p028 Key determinants of time on the market: an an</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p011 Are homes hot or cold potatoes? The distribut
-p031 Time on the Market and Probability of Sale Us</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p030 Average time to sell a property and credit co
-p056 Early Real Estate Indicators during the COVID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p062 List prices and “hot” real estate markets
-p079 Integrating Real Estate Market Conditions int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p059 Interpretation and measurement of the spread 
-p065 Incorporating the Number of Existing Home Sal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p076 Could We Have Predicted the Recent Downturn i
-p086 Anticipated vs. unanticipated house price mov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p121 Sale to list ratio, for-sale inventory, sale 
-p147 House hunting high and low: Constructing a Ho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p104 Forecasting Short-Term Housing Transaction Vo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이다윤</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">학부 </t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">까지 워드 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p063 Does Online Apartment Listing Volume Lead Pri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p096 Empirical Analyses of Factors Shaping the Rel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p089 A study on the impact of changes in consumer </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p003 Measuring Residential Real Estate Liquidity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p032 The Impacts of Property Features on Time on M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p016 The Probability of Sale and Price Premiums in
-p037 Understanding Housing Market Dynamics through</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p057 Signaling effects of recurrent list‐price red
-p060 Web-scraping housing prices in real-time: The</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p001 An Investigation of the Major Influences of R
-p087 Can Tightness in the Housing Market Help Pred</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p066 Price spreads and residential housing market 
-p067 Forecasting Connecticut home sales in a BVAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p078 The Economic Impact of Anticipated House Pric
-p098 INFORMATION CONTENT OF TRANSACTION VOLUME: TH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p125 Spatial and temporal diffusion of property pr
-p133 Forecasting Residential Real Estate Price Cha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p139 &lt;i&gt;FEAR Index&lt;/i&gt;, city characteristics, and </t>
-  </si>
-  <si>
-    <t xml:space="preserve">오건</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">학부 </t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">쪽 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p128 A Study on the Typology of the Busan Housing </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p102 A Study on the Impact of the Trading Volume o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p092 Relationship Among News Coverage, Consumers’ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p009 Liquidating Real Estate Assets Quickly: What </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p004 Censored Sample Bias, Macroeconomic Factors, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p017 Does Time-on-Market Measurement Matter?
-p038 Listing Price, Time on Market, and Ultimate S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p034 Apartment prices, the business cycle and time
-p043 Bidding Conventions and the Degree of Overpri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p071 Running hot and cold in the urban home-owners
-p088 Expectation, volatility and liquidity in the </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p045 Bidding Wars for Houses
-p068 Using Leading Indicators to Forecast U.S. Hom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p080 Trading Volume-Induced Spatial Autocorrelatio
-p101 The cause and outcomes of the ripple effect: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p126 From Causes to Forecasts: Granger Causality a
-p134 Intercity Information Diffusion and Price Dis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p140 Google Search Queries, Foreclosures, and Hous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이지은</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p129 Apartment Transaction Volume and Price Volati</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p106 A Study on the Dynamic Causal Relationship be</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p094 A Study on the Effects of News Big Data and G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p012 Cross sectional Analysis of time on Market in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p005 Exploring Spatial Effects on Urban Housing Du</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p010 "Fire Sales" in Housing Market: Is the House-
-p018 For sale… but for how long? a methodological </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p036 Liquidity in housing markets: the effect of n
-p048 The Comparative Analysis Of Asking And Traded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p084 To Sell or Not to Sell: Measuring the Heat of
-p090 Does liquidity affect housing market performa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p055 Properties that Sell at or above Listing Pric
-p069 Testing Alternative Theories of the Property </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p047 List price and sales prices of residential pr
-p113 Features of the ripple effect in the US regio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p127 Housing Market Spillovers in China via Tradin
-p135 Online Information Search, Market Fundamental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p142 Use of Google Trends to Predict the Real Esta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">홍다연</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p074 Applications and Improvements of Real Estate </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p107 A Study on the Interaction of Apartment Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p103 Consumer Sentiment in On-line Community and t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p014 Modelling a property's time to sale by inflat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p006 Submarket Dynamics of Time to Sale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p020 The Effect of Relisting on House Selling Pric
-p044 Asymmetric information and list-price reducti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p041 Measuring price expectations
-p049 Dynamic and Static Asking Prices in the Sydne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p100 Market depth in the UK housing market
-p110 Hot and cold seasons in Texas housing markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p061 Machine Learning Insights: Exploring Key Fact
-p072 Trading Volume and Price Dispersion in Housin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p081 Housing prices and transaction volume
-p114 Forecasting trading volume in local housing m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p091 Fundamentals and Market Sentiment in Housing 
-p130 From prediction to explanation for price–volu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p144 Predicting Housing Price Trends in Poland: On</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">주차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">담당</t>
-  </si>
-  <si>
-    <t xml:space="preserve">연도</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제목</t>
-  </si>
-  <si>
-    <t xml:space="preserve">학술지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">단계</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기능</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시장</t>
-  </si>
-  <si>
-    <t xml:space="preserve">한국</t>
-  </si>
-  <si>
-    <t xml:space="preserve">원문 상태</t>
-  </si>
-  <si>
-    <t xml:space="preserve">원문 받는 법</t>
-  </si>
-  <si>
-    <t xml:space="preserve">비고</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">예시</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구글시트 행</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Claude(</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">. W1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">예시</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">만 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Modeling home property listings’ time-on-market duration and listing outcome using copula-based competing risk method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Transport and Land Use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.5198/jtlu.2024.2447</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t xml:space="preserve">10/19 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배포</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S3 </t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">매칭</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">첫 모임 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">10/28. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">매물 시간</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">날짜는 배정일</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">이름</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구분</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W01 (10-19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W02 (10-28)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W03 (11-04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W04 (11-11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W05 (11-18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W06 (11-25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W07 (12-02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W08 (12-09)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W09 (12-16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W10 (12-23)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W11 (12-30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W12 (01-06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전우성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">박사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p023 Factors Affecting the Days on Market of Resid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p099 Intervention Analysis of Apartment Trading Vo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p108 Behavioral Economic Analysis of Housing Trans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p109 Big Data Time Series Analysis of the Relation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p105 The Repeat Time-On-The-Market Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p015 Days on market and home sales
+p021 A Spatiotemporal Solution for the Simultaneou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p046 Comparing alternative house price indices: ev
+p052 A More Timely House Price Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p024 Liquidity Imbalance in the Residential Real E
+p039 Bargaining over residential real estate: evid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p040 Estimating House Price Indexes in the Presenc
+p064 Dynamic hierarchical network-based framework </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p073 Transaction Volume and Price Dispersion in th
+p082 Price and transaction volume in the Dutch hou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p132 Housing Prices and Transaction Volumes in Tai
+p141 Segmented Housing Search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p143 Local Experiences, Search, and Spillovers in 
+p145 Housing search activity and quantiles-based p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">손수연</t>
+  </si>
+  <si>
+    <t xml:space="preserve">석사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p025 The Effect of Apartment Housing Characteristi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p077 Do Housing Trading Volume Explain Housing Pri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p117 A Study on the Monthly Effect of Apartment Pr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p119 Effects of Consumer Sentiment, Interest Rate,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p019 Marketing Time and Sales Price of Residential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p007 The Probability of Sale for Residential Real 
+p022 Measuring the influence of space and time eff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p051 The Effect of Listing Price Changes on the Se
+p054 House price index based on online listing inf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p070 The Inventory–Sales Relationship in the Marke
+p111 Liquidity and prices: a cluster analysis of t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p050 House prices at different stages of the buyin
+p118 Time‐varying impacts of expectations on housi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p075 Housing Price Dynamics in Time and Space: Pre
+p083 The Relationship between Trading Volume and P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p013 House Search Duration in Hot and Cold Residen
+p116 Housing market spillovers through the lens of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p136 Sentiment-based predictions of housing market
+p146 From digital search to deed: forecasting UK h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">최찬미</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p035 Determinants of Time to Close in Housing Tran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p093 The Relationship between Asymmetric Volatilit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p122 A Study on the Causality of Housing Price and</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p148 Real Estate News Data by Living District in S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p027 A hybrid neural network for predicting Days o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p008 Spatial Heterogeneity in Listing Duration: Th
+p029 Solving Old Puzzles with New Tricks: Addressi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p026 The influence of house, seller, and locationa
+p112 A Housing Supply Absorption Rate Equation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p053 Can list prices accurately capture housing pr
+p124 Local Constant-Quality Housing Market Liquidi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p097 Home Sales Pair Counts: The&lt;i&gt;Organic&lt;/i&gt;Metr
+p131 Frozen Markets, Falling Prices: Illiquidity a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p042 List price and sale price variation across th
+p085 Ripple effect in house prices and trading vol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p120 House price seasonality, market activity, and
+p138 Home is where the ad is: online interest prox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p137 Internet Search Behavior, Liquidity and Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이원석</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">호가 조정</t>
+      <t xml:space="preserve">학부 </t>
     </r>
     <r>
       <rPr>
@@ -2844,10 +2571,71 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">3·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">담당</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p058 A Study on the Impact of Asking Price and Sal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p095 Causality and Predictability of Price-Volume </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p123 Dynamic Relationship between Housing Sales Pr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p002 The Duration of Marketing Time of Residential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p028 Key determinants of time on the market: an an</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p011 Are homes hot or cold potatoes? The distribut
+p031 Time on the Market and Probability of Sale Us</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p030 Average time to sell a property and credit co
+p056 Early Real Estate Indicators during the COVID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p062 List prices and “hot” real estate markets
+p079 Integrating Real Estate Market Conditions int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p059 Interpretation and measurement of the spread 
+p065 Incorporating the Number of Existing Home Sal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p076 Could We Have Predicted the Recent Downturn i
+p086 Anticipated vs. unanticipated house price mov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p121 Sale to list ratio, for-sale inventory, sale 
+p147 House hunting high and low: Constructing a Ho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p104 Forecasting Short-Term Housing Transaction Vo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이다윤</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">학부 </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2855,18 +2643,63 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">F2 </t>
-    </r>
+      <t xml:space="preserve">3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p063 Does Online Apartment Listing Volume Lead Pri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p096 Empirical Analyses of Factors Shaping the Rel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p089 A study on the impact of changes in consumer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p003 Measuring Residential Real Estate Liquidity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p032 The Impacts of Property Features on Time on M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p016 The Probability of Sale and Price Premiums in
+p037 Understanding Housing Market Dynamics through</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p057 Signaling effects of recurrent list‐price red
+p060 Web-scraping housing prices in real-time: The</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p001 An Investigation of the Major Influences of R
+p087 Can Tightness in the Housing Market Help Pred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p066 Price spreads and residential housing market 
+p067 Forecasting Connecticut home sales in a BVAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p078 The Economic Impact of Anticipated House Pric
+p098 INFORMATION CONTENT OF TRANSACTION VOLUME: TH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p125 Spatial and temporal diffusion of property pr
+p133 Forecasting Residential Real Estate Price Cha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p139 &lt;i&gt;FEAR Index&lt;/i&gt;, city characteristics, and </t>
+  </si>
+  <si>
+    <t xml:space="preserve">오건</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">측정 쟁점</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">학부 </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2874,16 +2707,190 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MLS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시장 </t>
-    </r>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p128 A Study on the Typology of the Busan Housing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p102 A Study on the Impact of the Trading Volume o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p092 Relationship Among News Coverage, Consumers’ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p009 Liquidating Real Estate Assets Quickly: What </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p004 Censored Sample Bias, Macroeconomic Factors, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p017 Does Time-on-Market Measurement Matter?
+p038 Listing Price, Time on Market, and Ultimate S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p034 Apartment prices, the business cycle and time
+p043 Bidding Conventions and the Degree of Overpri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p071 Running hot and cold in the urban home-owners
+p088 Expectation, volatility and liquidity in the </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p045 Bidding Wars for Houses
+p068 Using Leading Indicators to Forecast U.S. Hom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p080 Trading Volume-Induced Spatial Autocorrelatio
+p101 The cause and outcomes of the ripple effect: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p126 From Causes to Forecasts: Granger Causality a
+p134 Intercity Information Diffusion and Price Dis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p140 Google Search Queries, Foreclosures, and Hous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이지은</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p129 Apartment Transaction Volume and Price Volati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p106 A Study on the Dynamic Causal Relationship be</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p094 A Study on the Effects of News Big Data and G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p012 Cross sectional Analysis of time on Market in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p005 Exploring Spatial Effects on Urban Housing Du</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p010 "Fire Sales" in Housing Market: Is the House-
+p018 For sale… but for how long? a methodological </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p036 Liquidity in housing markets: the effect of n
+p048 The Comparative Analysis Of Asking And Traded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p084 To Sell or Not to Sell: Measuring the Heat of
+p090 Does liquidity affect housing market performa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p055 Properties that Sell at or above Listing Pric
+p069 Testing Alternative Theories of the Property </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p047 List price and sales prices of residential pr
+p113 Features of the ripple effect in the US regio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p127 Housing Market Spillovers in China via Tradin
+p135 Online Information Search, Market Fundamental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p142 Use of Google Trends to Predict the Real Esta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">홍다연</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p074 Applications and Improvements of Real Estate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p107 A Study on the Interaction of Apartment Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p103 Consumer Sentiment in On-line Community and t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p014 Modelling a property's time to sale by inflat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p006 Submarket Dynamics of Time to Sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p020 The Effect of Relisting on House Selling Pric
+p044 Asymmetric information and list-price reducti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p041 Measuring price expectations
+p049 Dynamic and Static Asking Prices in the Sydne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p100 Market depth in the UK housing market
+p110 Hot and cold seasons in Texas housing markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p061 Machine Learning Insights: Exploring Key Fact
+p072 Trading Volume and Price Dispersion in Housin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p081 Housing prices and transaction volume
+p114 Forecasting trading volume in local housing m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p091 Fundamentals and Market Sentiment in Housing 
+p130 From prediction to explanation for price–volu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p144 Predicting Housing Price Trends in Poland: On</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">담당</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연도</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">학술지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">단계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기능</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한국</t>
+  </si>
+  <si>
+    <t xml:space="preserve">원문 상태</t>
+  </si>
+  <si>
+    <t xml:space="preserve">원문 받는 법</t>
+  </si>
+  <si>
+    <t xml:space="preserve">비고</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">예시</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2891,7 +2898,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">Claude(</t>
     </r>
     <r>
       <rPr>
@@ -2899,7 +2906,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">확인</t>
+      <t xml:space="preserve">예시</t>
     </r>
     <r>
       <rPr>
@@ -2912,22 +2919,13 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">받음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p033.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frequency domain analysis to detect common cycle in housing price and trading volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Housing and Urban Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.38100/jhuf.2021.6.2.53</t>
+    <t xml:space="preserve">Modeling home property listings’ time-on-market duration and listing outcome using copula-based competing risk method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Transport and Land Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.5198/jtlu.2024.2447</t>
   </si>
   <si>
     <r>
@@ -2937,7 +2935,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S4 </t>
+      <t xml:space="preserve">S3 </t>
     </r>
     <r>
       <rPr>
@@ -2945,7 +2943,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">체결</t>
+      <t xml:space="preserve">매칭</t>
     </r>
     <r>
       <rPr>
@@ -2962,7 +2960,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">거래량</t>
+      <t xml:space="preserve">매물 시간</t>
     </r>
     <r>
       <rPr>
@@ -2979,7 +2977,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가격 발견</t>
+      <t xml:space="preserve">호가 조정</t>
     </r>
     <r>
       <rPr>
@@ -2999,7 +2997,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">F3 </t>
+      <t xml:space="preserve">F2 </t>
     </r>
     <r>
       <rPr>
@@ -3007,8 +3005,10 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">선행성</t>
-    </r>
+      <t xml:space="preserve">측정 쟁점</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3016,7 +3016,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">MLS </t>
     </r>
     <r>
       <rPr>
@@ -3024,17 +3024,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">관계</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">비</t>
+      <t xml:space="preserve">시장 </t>
     </r>
     <r>
       <rPr>
@@ -3043,7 +3033,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MLS </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -3051,7 +3041,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">포털</t>
+      <t xml:space="preserve">확인</t>
     </r>
     <r>
       <rPr>
@@ -3060,32 +3050,28 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">중개</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p115.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정리 예시 완료</t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">받음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p033.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frequency domain analysis to detect common cycle in housing price and trading volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Housing and Urban Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.38100/jhuf.2021.6.2.53</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3093,7 +3079,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(examples/example_Ma2021_p115.md). </t>
+      <t xml:space="preserve">S4 </t>
     </r>
     <r>
       <rPr>
@@ -3101,25 +3087,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원석이 원문 대조 검증</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Factors Affecting the Days on Market of Residential Real Estate in Seoul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korean Association for Housing Policy Studies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.24957/hsr.2019.27.1.05</t>
-  </si>
-  <si>
+      <t xml:space="preserve">체결</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3127,7 +3096,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">F1 </t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -3135,7 +3104,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">정의</t>
+      <t xml:space="preserve">거래량</t>
     </r>
     <r>
       <rPr>
@@ -3152,13 +3121,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">구축</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p023.pdf</t>
-  </si>
-  <si>
+      <t xml:space="preserve">가격 발견</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3166,16 +3130,10 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">W1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">파일럿 논문</t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3183,7 +3141,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(KCI </t>
+      <t xml:space="preserve">F3 </t>
     </r>
     <r>
       <rPr>
@@ -3191,7 +3149,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원문</t>
+      <t xml:space="preserve">선행성</t>
     </r>
     <r>
       <rPr>
@@ -3200,29 +3158,25 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Effect of Apartment Housing Characteristics on the Days On Market(DOM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Korean Association of Urban Policies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.21447/jup.2019.10.3.101</t>
-  </si>
-  <si>
+      <t xml:space="preserve">·</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">한국 학술지</t>
+      <t xml:space="preserve">관계</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비</t>
     </r>
     <r>
       <rPr>
@@ -3231,10 +3185,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(KCI·RISS·DBpia)</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">MLS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">포털</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3242,7 +3202,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">KCI</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -3250,7 +3210,23 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">에 원문 없음 → </t>
+      <t xml:space="preserve">중개</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p115.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정리 예시 완료</t>
     </r>
     <r>
       <rPr>
@@ -3259,7 +3235,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DBpia·RISS(</t>
+      <t xml:space="preserve">(examples/example_Ma2021_p115.md). </t>
     </r>
     <r>
       <rPr>
@@ -3267,8 +3243,25 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">학교 계정</t>
-    </r>
+      <t xml:space="preserve">원석이 원문 대조 검증</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factors Affecting the Days on Market of Residential Real Estate in Seoul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korean Association for Housing Policy Studies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.24957/hsr.2019.27.1.05</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3276,7 +3269,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) </t>
+      <t xml:space="preserve">F1 </t>
     </r>
     <r>
       <rPr>
@@ -3284,31 +3277,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">또는 학회 홈페이지</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Determinants of Time to Close in Housing Transactions: Evidence from Survival Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.24957/hsr.2026.34.2.101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Impact of Asking Price and Sales Volume on the Real Transaction Price of Apartment using Machine Learning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Journal of Korean Institute of Information Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.14801/jkiit.2023.21.10.37</t>
-  </si>
-  <si>
+      <t xml:space="preserve">정의</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3316,7 +3286,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S2 </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -3324,8 +3294,13 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">공급</t>
-    </r>
+      <t xml:space="preserve">구축</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p023.pdf</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3333,7 +3308,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">W1 </t>
     </r>
     <r>
       <rPr>
@@ -3341,46 +3316,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">호가 설정</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does Online Apartment Listing Volume Lead Price Changes?: The Role of Transaction Volume and a Comparison of Sale and Jeonse Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.24957/hsr.2026.34.3.267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applications and Improvements of Real Estate Transaction Volume Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">국토연구</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.15793/kspr.2009.62..006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p074.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Typology of the Busan Housing Market Considering Price Differentiation and Transaction Liquidity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korea Real Estate Society</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.37407/kres.2026.44.3.315</t>
-  </si>
-  <si>
+      <t xml:space="preserve">파일럿 논문</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3388,7 +3325,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S5 </t>
+      <t xml:space="preserve">(KCI </t>
     </r>
     <r>
       <rPr>
@@ -3396,7 +3333,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">집계 상태</t>
+      <t xml:space="preserve">원문</t>
     </r>
     <r>
       <rPr>
@@ -3405,153 +3342,30 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Effect of Apartment Housing Characteristics on the Days On Market(DOM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Korean Association of Urban Policies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.21447/jup.2019.10.3.101</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">지수</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apartment Transaction Volume and Price Volatility: Construction and Application of a Transaction-Volume-Based Price Uncertainty Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Housing Finance Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.52344/hfr.2026.10.1.133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p129.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do Housing Trading Volume Explain Housing Prices or the Converse?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.15793/kspr.2011.69..001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p077.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Relationship between Asymmetric Volatility and Trading Volume in the Korean Housing Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">대한경영학회지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.18032/kaaba.2017.30.11.1935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Causality and Predictability of Price-Volume in Housing Market - Evidence from Seoul and Busan Housing Markets -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH Urban Research &amp; Insight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.26700/shuri.2018.12.8.3.51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empirical Analyses of Factors Shaping the Relationship between Housing Price and Trading Volume based on Bounded Rationality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.15793/kspr.2018.97..001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p096.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intervention Analysis of Apartment Trading Volume in Seoul, Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Real Estate Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.30902/jrea.2018.4.1.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p099.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Impact of the Trading Volume on Prices &amp; Prices Volatility of Housing Market in Seoul and the Whole Country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공공정책연구</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.37103/kapp.21.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Dynamic Causal Relationship between Housing Price and Housing Trading Volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential Environment Institute Of Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.22313/reik.2020.18.1.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p106.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Interaction of Apartment Price and Transaction Volumein Seoul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부동산학보</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.31303/krear.2020.83.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A study on the impact of changes in consumer sentiment on the housing market in Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Journal of Urban Sciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/12265934.2016.1239548</t>
-  </si>
-  <si>
+      <t xml:space="preserve">한국 학술지</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3559,16 +3373,10 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수요</t>
-    </r>
+      <t xml:space="preserve">(KCI·RISS·DBpia)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3576,7 +3384,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">KCI</t>
     </r>
     <r>
       <rPr>
@@ -3584,109 +3392,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">관심</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relationship Among News Coverage, Consumers’ Sentiment, Prices, and Trading Volume in Housing Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.24957/hsr.2017.25.3.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p092.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Effects of News Big Data and Google Information Search on Apartment Transaction Volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.22313/reik.2018.16.2.411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p094.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer Sentiment in On-line Community and the Variation of Real Estate Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.22313/reik.2019.17.4.31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p103.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Behavioral Economic Analysis of Housing Transaction Volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부동산학연구</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.19172/kreaa.26.3.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Monthly Effect of Apartment Price and Transaction Volume: Focusing on New Cities in the Metropolitan Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of the Korea Academia-Industrial cooperation Society</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.5762/kais.2022.23.3.273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Study on the Causality of Housing Price and Trading by Cyclical Variation: Focused on Housing market of Seoul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">대한부동산학회지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.37407/kres.2024.42.1.211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic Relationship between Housing Sales Price and Transaction Volume by Housing Type in the Metropolitan Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Journal of the Korea Contents Association</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.5392/jkca.2024.24.01.621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Duration of Marketing Time of Residential Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00463</t>
-  </si>
-  <si>
+      <t xml:space="preserve">에 원문 없음 → </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3694,7 +3401,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MLS </t>
+      <t xml:space="preserve">DBpia·RISS(</t>
     </r>
     <r>
       <rPr>
@@ -3702,20 +3409,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">시장</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">도서관 전자저널</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가천대 도서관 로그인 후 </t>
+      <t xml:space="preserve">학교 계정</t>
     </r>
     <r>
       <rPr>
@@ -3724,7 +3418,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DOI </t>
+      <t xml:space="preserve">) </t>
     </r>
     <r>
       <rPr>
@@ -3732,8 +3426,31 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">링크로 접속</t>
-    </r>
+      <t xml:space="preserve">또는 학회 홈페이지</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Determinants of Time to Close in Housing Transactions: Evidence from Survival Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.24957/hsr.2026.34.2.101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Impact of Asking Price and Sales Volume on the Real Transaction Price of Apartment using Machine Learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Journal of Korean Institute of Information Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.14801/jkiit.2023.21.10.37</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3741,7 +3458,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">S2 </t>
     </r>
     <r>
       <rPr>
@@ -3749,125 +3466,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">구독 안 되면 상호대차 신청</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Measuring Residential Real Estate Liquidity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquidating Real Estate Assets Quickly: What Affects the Probability of a Quick Sale?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Real Estate Practice and Education</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10835547.2010.12091669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross sectional Analysis of time on Market indicators for an Australian City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacific Rim Property Research Journal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/14445921.2012.11104370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelling a property's time to sale by inflating its previous selling price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of the Operational Research Society</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1057/jors.2011.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Big Data Time Series Analysis of the Relationship Between News Coverage, Apartment Price and Trading Volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korea Association Of Real Estate Law</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.32989/rel.2020.24.2.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effects of Consumer Sentiment, Interest Rate, and Transaction Volume on Housing Price Using the BVAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Journal of Humanities and Social sciences 21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.22143/hss21.14.2.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate News Data by Living District in Seoul Trend Analysis Research Through Topic Modeling and Sentiment Analysis: Focusing on Apartment and Non-Apartment Transaction Volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정보과학회 컴퓨팅의 실제 논문지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.5626/ktcp.2026.32.3.89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Censored Sample Bias, Macroeconomic Factors, and Time on Market of Residential Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Real Estate Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10835547.1994.12090750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exploring Spatial Effects on Urban Housing Duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environment and Planning A Economy and Space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1068/a35170</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">비</t>
+      <t xml:space="preserve">공급</t>
     </r>
     <r>
       <rPr>
@@ -3876,7 +3475,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MLS </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -3884,8 +3483,46 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">포털</t>
-    </r>
+      <t xml:space="preserve">호가 설정</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does Online Apartment Listing Volume Lead Price Changes?: The Role of Transaction Volume and a Comparison of Sale and Jeonse Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.24957/hsr.2026.34.3.267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applications and Improvements of Real Estate Transaction Volume Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">국토연구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.15793/kspr.2009.62..006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p074.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Typology of the Busan Housing Market Considering Price Differentiation and Transaction Liquidity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korea Real Estate Society</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.37407/kres.2026.44.3.315</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3893,7 +3530,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">S5 </t>
     </r>
     <r>
       <rPr>
@@ -3901,7 +3538,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">중개 </t>
+      <t xml:space="preserve">집계 상태</t>
     </r>
     <r>
       <rPr>
@@ -3910,7 +3547,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -3918,8 +3555,145 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">확인</t>
-    </r>
+      <t xml:space="preserve">지수</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartment Transaction Volume and Price Volatility: Construction and Application of a Transaction-Volume-Based Price Uncertainty Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Housing Finance Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.52344/hfr.2026.10.1.133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p129.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do Housing Trading Volume Explain Housing Prices or the Converse?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.15793/kspr.2011.69..001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p077.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Relationship between Asymmetric Volatility and Trading Volume in the Korean Housing Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대한경영학회지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.18032/kaaba.2017.30.11.1935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Causality and Predictability of Price-Volume in Housing Market - Evidence from Seoul and Busan Housing Markets -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH Urban Research &amp; Insight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.26700/shuri.2018.12.8.3.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empirical Analyses of Factors Shaping the Relationship between Housing Price and Trading Volume based on Bounded Rationality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.15793/kspr.2018.97..001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p096.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intervention Analysis of Apartment Trading Volume in Seoul, Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Real Estate Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.30902/jrea.2018.4.1.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p099.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Impact of the Trading Volume on Prices &amp; Prices Volatility of Housing Market in Seoul and the Whole Country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공공정책연구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.37103/kapp.21.3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Dynamic Causal Relationship between Housing Price and Housing Trading Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential Environment Institute Of Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.22313/reik.2020.18.1.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p106.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Interaction of Apartment Price and Transaction Volumein Seoul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부동산학보</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.31303/krear.2020.83.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A study on the impact of changes in consumer sentiment on the housing market in Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Journal of Urban Sciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/12265934.2016.1239548</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3927,125 +3701,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submarket Dynamics of Time to Sale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/j.1540-6229.2006.00171.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marketing Time and Sales Price of Residential Properties in Akure, Nigeria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of economics and sustainable development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A hybrid neural network for predicting Days on Market a measure of liquidity in real estate industry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Knowledge-Based Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.knosys.2020.106417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key determinants of time on the market: an analysis of residential housing market in Sri Lanka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Journal of Housing Markets and Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/ijhma-06-2020-0071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Impacts of Property Features on Time on Market of Real Estate Assets in Lagos Metropolis, Nigeria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIOSUN Journal of Engineering and Environmental Sciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.36108/ujees/2202.40.0210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p032.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Repeat Time-On-The-Market Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Urban Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.jue.2019.04.005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Probability of Sale for Residential Real Estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Housing Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10835547.2007.12091978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spatial Heterogeneity in Listing Duration: The Influence of Relative Location to Marketability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10835547.2009.12092005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Fire Sales" in Housing Market: Is the House-Search Process Similar to a Theme Park Visit?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Real Estate Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.53383/100144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p010.pdf</t>
-  </si>
-  <si>
+      <t xml:space="preserve">S1 </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">제목 정정</t>
+      <t xml:space="preserve">수요</t>
     </r>
     <r>
       <rPr>
@@ -4054,7 +3718,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: Crossref </t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -4062,8 +3726,109 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">제목 결손</t>
-    </r>
+      <t xml:space="preserve">관심</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relationship Among News Coverage, Consumers’ Sentiment, Prices, and Trading Volume in Housing Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.24957/hsr.2017.25.3.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p092.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Effects of News Big Data and Google Information Search on Apartment Transaction Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.22313/reik.2018.16.2.411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p094.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer Sentiment in On-line Community and the Variation of Real Estate Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.22313/reik.2019.17.4.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p103.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behavioral Economic Analysis of Housing Transaction Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부동산학연구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.19172/kreaa.26.3.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Monthly Effect of Apartment Price and Transaction Volume: Focusing on New Cities in the Metropolitan Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of the Korea Academia-Industrial cooperation Society</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.5762/kais.2022.23.3.273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on the Causality of Housing Price and Trading by Cyclical Variation: Focused on Housing market of Seoul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대한부동산학회지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.37407/kres.2024.42.1.211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamic Relationship between Housing Sales Price and Transaction Volume by Housing Type in the Metropolitan Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Journal of the Korea Contents Association</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.5392/jkca.2024.24.01.621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Duration of Marketing Time of Residential Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00463</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -4071,7 +3836,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve">MLS </t>
     </r>
     <r>
       <rPr>
@@ -4079,74 +3844,11 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원문으로 확인</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Are homes hot or cold potatoes? The distribution of marketing time in the housing market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regional Science and Urban Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2011.08.010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days on market and home sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The RAND Journal of Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1756-2171.12022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Probability of Sale and Price Premiums in Withdrawn Auctioned Properties*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urban Studies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1177/0042098014529341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">경매 시장</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p016.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does Time-on-Market Measurement Matter?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Journal of Real Estate Finance and Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-013-9450-z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For sale… but for how long? a methodological proposal for estimating time-on-the-market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Journal of Strategic Property Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.3846/1648715x.2015.1072746</t>
+      <t xml:space="preserve">시장</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">도서관 전자저널</t>
   </si>
   <si>
     <r>
@@ -4172,17 +3874,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">링크</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">무료 링크가 다른 논문</t>
+      <t xml:space="preserve">링크로 접속</t>
     </r>
     <r>
       <rPr>
@@ -4191,7 +3883,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -4199,7 +3891,125 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">임대료 설정 논문</t>
+      <t xml:space="preserve">구독 안 되면 상호대차 신청</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measuring Residential Real Estate Liquidity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidating Real Estate Assets Quickly: What Affects the Probability of a Quick Sale?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Real Estate Practice and Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10835547.2010.12091669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross sectional Analysis of time on Market indicators for an Australian City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacific Rim Property Research Journal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/14445921.2012.11104370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelling a property's time to sale by inflating its previous selling price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of the Operational Research Society</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1057/jors.2011.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big Data Time Series Analysis of the Relationship Between News Coverage, Apartment Price and Trading Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korea Association Of Real Estate Law</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.32989/rel.2020.24.2.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effects of Consumer Sentiment, Interest Rate, and Transaction Volume on Housing Price Using the BVAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Journal of Humanities and Social sciences 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.22143/hss21.14.2.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate News Data by Living District in Seoul Trend Analysis Research Through Topic Modeling and Sentiment Analysis: Focusing on Apartment and Non-Apartment Transaction Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정보과학회 컴퓨팅의 실제 논문지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.5626/ktcp.2026.32.3.89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Censored Sample Bias, Macroeconomic Factors, and Time on Market of Residential Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Real Estate Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10835547.1994.12090750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exploring Spatial Effects on Urban Housing Duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Environment and Planning A Economy and Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1068/a35170</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비</t>
     </r>
     <r>
       <rPr>
@@ -4208,7 +4018,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">MLS </t>
     </r>
     <r>
       <rPr>
@@ -4216,146 +4026,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">으로 연결됨 → 도서관 전자저널로 받을 것</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Effect of Relisting on House Selling Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of real estate finance and economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-015-9503-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Spatiotemporal Solution for the Simultaneous Sale Price and Time‐on‐the‐Market Problem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Measuring the influence of space and time effects on time on the market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1177/0042098015596923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solving Old Puzzles with New Tricks: Addressing Endogeneity and Nonlinearity in Time-on-Market Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/08965803.2020.1844476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time on the Market and Probability of Sale Using a Generalized Geometric Hazard Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Econometric Methods</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1515/jem-2020-0017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Understanding Housing Market Dynamics through a Joint Model of Time-on-Market Duration and Listing Outcome of Residential Property Listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of urban planning and development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1061/jupddm.upeng-5857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Listing Price, Time on Market, and Ultimate Selling Price: Causes and Effects of Listing Price Changes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asymmetric information and list-price reductions in the housing market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2013.03.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The influence of house, seller, and locational factors on the probability of sale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Housing Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2018.09.009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average time to sell a property and credit conditions: Evidence from the Italian housing market survey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulletin of Economic Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/boer.12284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apartment prices, the business cycle and time on market: Evidence from Bucharest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.3846/ijspm.2025.23319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquidity in housing markets: the effect of news sentiment on time on market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of European Real Estate Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/jerer-12-2025-0098</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">무료 원문</t>
+      <t xml:space="preserve">포털</t>
     </r>
     <r>
       <rPr>
@@ -4364,7 +4035,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -4372,7 +4043,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">직접 받기</t>
+      <t xml:space="preserve">중개 </t>
     </r>
     <r>
       <rPr>
@@ -4381,149 +4052,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.emerald.com/jerer/article-pdf/doi/10.1108/JERER-12-2025-0098/11860165/jerer-12-2025-0098en.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Measuring price expectations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/17539260910978481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bidding Conventions and the Degree of Overpricing in the Market for Houses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1177/0042098010363496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparing alternative house price indices: evidence from asking prices in Malta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/17538271311306048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Comparative Analysis Of Asking And Traded Price Indices In Different Floor Area Subsegments Of The Residential Property Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate Management and Valuation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1515/remav-2015-0021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p048.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic and Static Asking Prices in the Sydney Housing Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economic Record</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1475-4932.12242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p049.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Effect of Listing Price Changes on the Selling Price of Single-Family Residential Homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-016-9558-z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A More Timely House Price Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review of Economics and Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1162/rest_a_00634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">House price index based on online listing information: The case of China</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2020.101715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Early Real Estate Indicators during the COVID-19 Crisis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Official Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.2478/jos-2022-0017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p056.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signaling effects of recurrent list‐price reductions on the likelihood of house sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Journal of Financial Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/jfir.12308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/jfir.12308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Web-scraping housing prices in real-time: The Covid-19 crisis in the UK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2022.101906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p060.pdf</t>
-  </si>
-  <si>
+      <t xml:space="preserve">(</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">받은 파일은 워킹페이퍼</t>
+      <t xml:space="preserve">확인</t>
     </r>
     <r>
       <rPr>
@@ -4532,15 +4069,125 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submarket Dynamics of Time to Sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/j.1540-6229.2006.00171.x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing Time and Sales Price of Residential Properties in Akure, Nigeria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of economics and sustainable development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A hybrid neural network for predicting Days on Market a measure of liquidity in real estate industry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knowledge-Based Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.knosys.2020.106417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key determinants of time on the market: an analysis of residential housing market in Sri Lanka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Journal of Housing Markets and Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/ijhma-06-2020-0071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Impacts of Property Features on Time on Market of Real Estate Assets in Lagos Metropolis, Nigeria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIOSUN Journal of Engineering and Environmental Sciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.36108/ujees/2202.40.0210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p032.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Repeat Time-On-The-Market Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Urban Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.jue.2019.04.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Probability of Sale for Residential Real Estate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Housing Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10835547.2007.12091978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spatial Heterogeneity in Listing Duration: The Influence of Relative Location to Marketability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10835547.2009.12092005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Fire Sales" in Housing Market: Is the House-Search Process Similar to a Theme Park Visit?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Real Estate Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.53383/100144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p010.pdf</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">저자 공개본일 수 있음</t>
+      <t xml:space="preserve">제목 정정</t>
     </r>
     <r>
       <rPr>
@@ -4549,7 +4196,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">: Crossref </t>
     </r>
     <r>
       <rPr>
@@ -4557,7 +4204,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">인용</t>
+      <t xml:space="preserve">제목 결손</t>
     </r>
     <r>
       <rPr>
@@ -4566,7 +4213,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -4574,359 +4221,74 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">쪽수는 게재본으로 확인</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Housing Supply Absorption Rate Equation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-020-09815-z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p112.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An Investigation of the Major Influences of Residential Liquidity: A Multivariate Approach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquidity Imbalance in the Residential Real Estate Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10527001.2020.1776513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bargaining over residential real estate: evidence from England</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.jue.2004.05.004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p039.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can list prices accurately capture housing price trends? Insights from extreme markets conditions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finance Research Letters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.frl.2018.10.004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List prices and “hot” real estate markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.70013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Inventory–Sales Relationship in the Market for New Single‐Family Homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/j.1080-8620.2004.00106.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Running hot and cold in the urban home-ownership market: The experience of Japan?s major cities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Housing and the Built Environment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s10901-005-6762-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrating Real Estate Market Conditions into Home Price Forecasting Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10835547.2012.12092059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To Sell or Not to Sell: Measuring the Heat of the Housing Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/reec.12003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can Tightness in the Housing Market Help Predict Subsequent Home Price Appreciation? Evidence from the United States and the Netherlands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expectation, volatility and liquidity in the housing market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/00036846.2015.1023943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does liquidity affect housing market performance? An empirical study with spatial panel approach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Land Use Policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.landusepol.2016.05.008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market depth in the UK housing market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economic Research-Ekonomska Istraživanja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/1331677x.2018.1429289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.tandfonline.com/doi/pdf/10.1080/1331677X.2018.1429289?needAccess=true</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hot and cold seasons in Texas housing markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1108/ijhma-02-2020-0017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://scholarsphere.psu.edu/resources/8b45d64c-36f4-4294-a0a6-50926994da05/downloads/15638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquidity and prices: a cluster analysis of the German residential real estate market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Business Economics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11573-020-00990-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p111.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Local Constant-Quality Housing Market Liquidity Indices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2024.103997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimating House Price Indexes in the Presence of Seller Reservation Prices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1162/003465306775565783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bidding Wars for Houses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/reec.12015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">House prices at different stages of the buying/selling process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2016.04.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p050.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Properties that Sell at or above Listing Price: Strategic Pricing, Better Broker or Just Dumb Luck?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s11146-019-09714-y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interpretation and measurement of the spread between asking and selling prices in the Italian residential market [Interpretazione e misura dello spread tra prezzi richiesti e prezzi di vendita nel mercato residenziale italiano]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valori e Valutazioni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.48264/vvsiev-20223102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">papers/p059.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine Learning Insights: Exploring Key Factors Influencing Sale-to-List Ratio—Insights from SVM Classification and Recursive Feature Selection in the US Real Estate Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.3390/buildings14051471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic hierarchical network-based framework for constructing a predictive index of offer–listing price differences in real estate E-commerce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electronic Commerce Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/s10660-026-10107-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incorporating the Number of Existing Home Sales into a Structural Model of the Market for Owner-Occupied Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1006/jhec.1995.1005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price spreads and residential housing market liquidity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/bf01099111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://libres.uncg.edu/ir/uncg/f/D_Winkler_Price_1995.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forecasting Connecticut home sales in a BVAR framework using coincident and leading indexes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1007/bf00217392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Using Leading Indicators to Forecast U.S. Home Sales in a Bayesian Vector Autoregressive Framework</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1023/a:1007718725609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testing Alternative Theories of the Property Price-Trading Volume Correlation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/10835547.2002.12091081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trading Volume and Price Dispersion in Housing Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Property Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1080/09599910802696615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Sales Pair Counts: The&lt;i&gt;Organic&lt;/i&gt;Metric for Trading Volume in Housing Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time‐varying impacts of expectations on housing markets across hot and cold phases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.1111/infi.12408</t>
+      <t xml:space="preserve">원문으로 확인</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are homes hot or cold potatoes? The distribution of marketing time in the housing market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regional Science and Urban Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2011.08.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days on market and home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The RAND Journal of Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1756-2171.12022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Probability of Sale and Price Premiums in Withdrawn Auctioned Properties*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urban Studies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1177/0042098014529341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">경매 시장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p016.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does Time-on-Market Measurement Matter?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Journal of Real Estate Finance and Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-013-9450-z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For sale… but for how long? a methodological proposal for estimating time-on-the-market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Journal of Strategic Property Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.3846/1648715x.2015.1072746</t>
   </si>
   <si>
     <r>
@@ -4935,7 +4297,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">복수</t>
+      <t xml:space="preserve">가천대 도서관 로그인 후 </t>
     </r>
     <r>
       <rPr>
@@ -4944,7 +4306,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
+      <t xml:space="preserve">DOI </t>
     </r>
     <r>
       <rPr>
@@ -4952,7 +4314,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">불명 </t>
+      <t xml:space="preserve">링크</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무료 링크가 다른 논문</t>
     </r>
     <r>
       <rPr>
@@ -4969,7 +4341,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">확인</t>
+      <t xml:space="preserve">임대료 설정 논문</t>
     </r>
     <r>
       <rPr>
@@ -4980,6 +4352,776 @@
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">으로 연결됨 → 도서관 전자저널로 받을 것</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Effect of Relisting on House Selling Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of real estate finance and economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-015-9503-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Spatiotemporal Solution for the Simultaneous Sale Price and Time‐on‐the‐Market Problem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measuring the influence of space and time effects on time on the market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1177/0042098015596923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solving Old Puzzles with New Tricks: Addressing Endogeneity and Nonlinearity in Time-on-Market Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/08965803.2020.1844476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time on the Market and Probability of Sale Using a Generalized Geometric Hazard Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Econometric Methods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1515/jem-2020-0017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Understanding Housing Market Dynamics through a Joint Model of Time-on-Market Duration and Listing Outcome of Residential Property Listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of urban planning and development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1061/jupddm.upeng-5857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listing Price, Time on Market, and Ultimate Selling Price: Causes and Effects of Listing Price Changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asymmetric information and list-price reductions in the housing market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2013.03.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The influence of house, seller, and locational factors on the probability of sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Housing Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2018.09.009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average time to sell a property and credit conditions: Evidence from the Italian housing market survey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulletin of Economic Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/boer.12284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartment prices, the business cycle and time on market: Evidence from Bucharest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.3846/ijspm.2025.23319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidity in housing markets: the effect of news sentiment on time on market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of European Real Estate Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/jerer-12-2025-0098</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무료 원문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직접 받기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.emerald.com/jerer/article-pdf/doi/10.1108/JERER-12-2025-0098/11860165/jerer-12-2025-0098en.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measuring price expectations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/17539260910978481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bidding Conventions and the Degree of Overpricing in the Market for Houses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1177/0042098010363496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparing alternative house price indices: evidence from asking prices in Malta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/17538271311306048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Comparative Analysis Of Asking And Traded Price Indices In Different Floor Area Subsegments Of The Residential Property Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate Management and Valuation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1515/remav-2015-0021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p048.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamic and Static Asking Prices in the Sydney Housing Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economic Record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1475-4932.12242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p049.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Effect of Listing Price Changes on the Selling Price of Single-Family Residential Homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-016-9558-z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A More Timely House Price Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review of Economics and Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1162/rest_a_00634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House price index based on online listing information: The case of China</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2020.101715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Early Real Estate Indicators during the COVID-19 Crisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Official Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.2478/jos-2022-0017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p056.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signaling effects of recurrent list‐price reductions on the likelihood of house sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Journal of Financial Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/jfir.12308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/jfir.12308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web-scraping housing prices in real-time: The Covid-19 crisis in the UK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.jhe.2022.101906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p060.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">받은 파일은 워킹페이퍼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저자 공개본일 수 있음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">쪽수는 게재본으로 확인</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Housing Supply Absorption Rate Equation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-020-09815-z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p112.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An Investigation of the Major Influences of Residential Liquidity: A Multivariate Approach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.00410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidity Imbalance in the Residential Real Estate Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10527001.2020.1776513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bargaining over residential real estate: evidence from England</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.jue.2004.05.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p039.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Can list prices accurately capture housing price trends? Insights from extreme markets conditions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finance Research Letters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.frl.2018.10.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List prices and “hot” real estate markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.70013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Inventory–Sales Relationship in the Market for New Single‐Family Homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/j.1080-8620.2004.00106.x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Running hot and cold in the urban home-ownership market: The experience of Japan?s major cities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Housing and the Built Environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s10901-005-6762-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrating Real Estate Market Conditions into Home Price Forecasting Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10835547.2012.12092059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To Sell or Not to Sell: Measuring the Heat of the Housing Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/reec.12003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Can Tightness in the Housing Market Help Predict Subsequent Home Price Appreciation? Evidence from the United States and the Netherlands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expectation, volatility and liquidity in the housing market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/00036846.2015.1023943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does liquidity affect housing market performance? An empirical study with spatial panel approach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land Use Policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.landusepol.2016.05.008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market depth in the UK housing market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economic Research-Ekonomska Istraživanja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/1331677x.2018.1429289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.tandfonline.com/doi/pdf/10.1080/1331677X.2018.1429289?needAccess=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hot and cold seasons in Texas housing markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1108/ijhma-02-2020-0017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://scholarsphere.psu.edu/resources/8b45d64c-36f4-4294-a0a6-50926994da05/downloads/15638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidity and prices: a cluster analysis of the German residential real estate market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Business Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11573-020-00990-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p111.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local Constant-Quality Housing Market Liquidity Indices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2024.103997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimating House Price Indexes in the Presence of Seller Reservation Prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1162/003465306775565783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bidding Wars for Houses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/reec.12015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House prices at different stages of the buying/selling process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1016/j.regsciurbeco.2016.04.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p050.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Properties that Sell at or above Listing Price: Strategic Pricing, Better Broker or Just Dumb Luck?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s11146-019-09714-y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpretation and measurement of the spread between asking and selling prices in the Italian residential market [Interpretazione e misura dello spread tra prezzi richiesti e prezzi di vendita nel mercato residenziale italiano]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valori e Valutazioni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.48264/vvsiev-20223102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">papers/p059.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machine Learning Insights: Exploring Key Factors Influencing Sale-to-List Ratio—Insights from SVM Classification and Recursive Feature Selection in the US Real Estate Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.3390/buildings14051471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamic hierarchical network-based framework for constructing a predictive index of offer–listing price differences in real estate E-commerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electronic Commerce Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s10660-026-10107-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incorporating the Number of Existing Home Sales into a Structural Model of the Market for Owner-Occupied Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1006/jhec.1995.1005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price spreads and residential housing market liquidity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/bf01099111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://libres.uncg.edu/ir/uncg/f/D_Winkler_Price_1995.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecasting Connecticut home sales in a BVAR framework using coincident and leading indexes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/bf00217392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using Leading Indicators to Forecast U.S. Home Sales in a Bayesian Vector Autoregressive Framework</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1023/a:1007718725609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing Alternative Theories of the Property Price-Trading Volume Correlation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/10835547.2002.12091081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trading Volume and Price Dispersion in Housing Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Property Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1080/09599910802696615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home Sales Pair Counts: The&lt;i&gt;Organic&lt;/i&gt;Metric for Trading Volume in Housing Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/1540-6229.12269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time‐varying impacts of expectations on housing markets across hot and cold phases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1111/infi.12408</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">복수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">p131</t>
@@ -5495,7 +5637,7 @@
     <t xml:space="preserve">반려사유</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-21</t>
+    <t xml:space="preserve">2026-10-19</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-27</t>

--- a/handover/유동성리뷰_담당자파일.xlsx
+++ b/handover/유동성리뷰_담당자파일.xlsx
@@ -2486,28 +2486,28 @@
 p021 A Spatiotemporal Solution for the Simultaneou</t>
   </si>
   <si>
-    <t xml:space="preserve">p046 Comparing alternative house price indices: ev
-p052 A More Timely House Price Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p024 Liquidity Imbalance in the Residential Real E
-p039 Bargaining over residential real estate: evid</t>
+    <t xml:space="preserve">p052 A More Timely House Price Index
+p112 A Housing Supply Absorption Rate Equation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p001 An Investigation of the Major Influences of R
+p087 Can Tightness in the Housing Market Help Pred</t>
   </si>
   <si>
     <t xml:space="preserve">p040 Estimating House Price Indexes in the Presenc
-p064 Dynamic hierarchical network-based framework </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p073 Transaction Volume and Price Dispersion in th
-p082 Price and transaction volume in the Dutch hou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p132 Housing Prices and Transaction Volumes in Tai
+p068 Using Leading Indicators to Forecast U.S. Hom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p047 List price and sales prices of residential pr
+p113 Features of the ripple effect in the US regio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p137 Internet Search Behavior, Liquidity and Price
 p141 Segmented Housing Search</t>
   </si>
   <si>
-    <t xml:space="preserve">p143 Local Experiences, Search, and Spillovers in 
-p145 Housing search activity and quantiles-based p</t>
+    <t xml:space="preserve">p125 Spatial and temporal diffusion of property pr
+p143 Local Experiences, Search, and Spillovers in </t>
   </si>
   <si>
     <t xml:space="preserve">손수연</t>
@@ -2535,28 +2535,28 @@
 p022 Measuring the influence of space and time eff</t>
   </si>
   <si>
-    <t xml:space="preserve">p051 The Effect of Listing Price Changes on the Se
-p054 House price index based on online listing inf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p070 The Inventory–Sales Relationship in the Marke
-p111 Liquidity and prices: a cluster analysis of t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p050 House prices at different stages of the buyin
-p118 Time‐varying impacts of expectations on housi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p075 Housing Price Dynamics in Time and Space: Pre
-p083 The Relationship between Trading Volume and P</t>
+    <t xml:space="preserve">p039 Bargaining over residential real estate: evid
+p056 Early Real Estate Indicators during the COVID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p071 Running hot and cold in the urban home-owners
+p088 Expectation, volatility and liquidity in the </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p055 Properties that Sell at or above Listing Pric
+p069 Testing Alternative Theories of the Property </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p081 Housing prices and transaction volume
+p114 Forecasting trading volume in local housing m</t>
   </si>
   <si>
     <t xml:space="preserve">p013 House Search Duration in Hot and Cold Residen
-p116 Housing market spillovers through the lens of</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p136 Sentiment-based predictions of housing market
-p146 From digital search to deed: forecasting UK h</t>
+p104 Forecasting Short-Term Housing Transaction Vo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p037 Understanding Housing Market Dynamics through
+p136 Sentiment-based predictions of housing market</t>
   </si>
   <si>
     <t xml:space="preserve">최찬미</t>
@@ -2582,26 +2582,27 @@
   </si>
   <si>
     <t xml:space="preserve">p026 The influence of house, seller, and locationa
-p112 A Housing Supply Absorption Rate Equation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p053 Can list prices accurately capture housing pr
-p124 Local Constant-Quality Housing Market Liquidi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p097 Home Sales Pair Counts: The&lt;i&gt;Organic&lt;/i&gt;Metr
-p131 Frozen Markets, Falling Prices: Illiquidity a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p042 List price and sale price variation across th
-p085 Ripple effect in house prices and trading vol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p120 House price seasonality, market activity, and
-p138 Home is where the ad is: online interest prox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p137 Internet Search Behavior, Liquidity and Price</t>
+p060 Web-scraping housing prices in real-time: The</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p084 To Sell or Not to Sell: Measuring the Heat of
+p090 Does liquidity affect housing market performa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p061 Machine Learning Insights: Exploring Key Fact
+p072 Trading Volume and Price Dispersion in Housin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p082 Price and transaction volume in the Dutch hou
+p116 Housing market spillovers through the lens of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p138 Home is where the ad is: online interest prox
+p139 &lt;i&gt;FEAR Index&lt;/i&gt;, city characteristics, and </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p041 Measuring price expectations
+p146 From digital search to deed: forecasting UK h</t>
   </si>
   <si>
     <t xml:space="preserve">이원석</t>
@@ -2654,244 +2655,243 @@
   </si>
   <si>
     <t xml:space="preserve">p030 Average time to sell a property and credit co
-p056 Early Real Estate Indicators during the COVID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p062 List prices and “hot” real estate markets
+p043 Bidding Conventions and the Degree of Overpri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p100 Market depth in the UK housing market
+p118 Time‐varying impacts of expectations on housi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p064 Dynamic hierarchical network-based framework 
+p073 Transaction Volume and Price Dispersion in th</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p083 The Relationship between Trading Volume and P
+p120 House price seasonality, market activity, and</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p140 Google Search Queries, Foreclosures, and Hous
+p147 House hunting high and low: Constructing a Ho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p046 Comparing alternative house price indices: ev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이다윤</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">학부 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p063 Does Online Apartment Listing Volume Lead Pri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p096 Empirical Analyses of Factors Shaping the Rel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p089 A study on the impact of changes in consumer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p003 Measuring Residential Real Estate Liquidity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p032 The Impacts of Property Features on Time on M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p016 The Probability of Sale and Price Premiums in
+p038 Listing Price, Time on Market, and Ultimate S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p048 The Comparative Analysis Of Asking And Traded
+p057 Signaling effects of recurrent list‐price red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p024 Liquidity Imbalance in the Residential Real E
+p131 Frozen Markets, Falling Prices: Illiquidity a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p050 House prices at different stages of the buyin
+p075 Housing Price Dynamics in Time and Space: Pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p085 Ripple effect in house prices and trading vol
+p126 From Causes to Forecasts: Granger Causality a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p133 Forecasting Residential Real Estate Price Cha
+p142 Use of Google Trends to Predict the Real Esta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p062 List prices and “hot” real estate markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">오건</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">학부 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">p128 A Study on the Typology of the Busan Housing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p102 A Study on the Impact of the Trading Volume o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p092 Relationship Among News Coverage, Consumers’ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p009 Liquidating Real Estate Assets Quickly: What </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p004 Censored Sample Bias, Macroeconomic Factors, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p010 "Fire Sales" in Housing Market: Is the House-
+p017 Does Time-on-Market Measurement Matter?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p034 Apartment prices, the business cycle and time
+p049 Dynamic and Static Asking Prices in the Sydne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p065 Incorporating the Number of Existing Home Sal
+p111 Liquidity and prices: a cluster analysis of t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p076 Could We Have Predicted the Recent Downturn i
+p097 Home Sales Pair Counts: The&lt;i&gt;Organic&lt;/i&gt;Metr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p086 Anticipated vs. unanticipated house price mov
+p127 Housing Market Spillovers in China via Tradin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p134 Intercity Information Diffusion and Price Dis
+p144 Predicting Housing Price Trends in Poland: On</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p110 Hot and cold seasons in Texas housing markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이지은</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p129 Apartment Transaction Volume and Price Volati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p106 A Study on the Dynamic Causal Relationship be</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p094 A Study on the Effects of News Big Data and G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p012 Cross sectional Analysis of time on Market in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p005 Exploring Spatial Effects on Urban Housing Du</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p018 For sale… but for how long? a methodological 
+p044 Asymmetric information and list-price reducti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p036 Liquidity in housing markets: the effect of n
+p070 The Inventory–Sales Relationship in the Marke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p066 Price spreads and residential housing market 
+p124 Local Constant-Quality Housing Market Liquidi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p059 Interpretation and measurement of the spread 
+p078 The Economic Impact of Anticipated House Pric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p098 INFORMATION CONTENT OF TRANSACTION VOLUME: TH
+p130 From prediction to explanation for price–volu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p135 Online Information Search, Market Fundamental
+p145 Housing search activity and quantiles-based p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p042 List price and sale price variation across th</t>
+  </si>
+  <si>
+    <t xml:space="preserve">홍다연</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p074 Applications and Improvements of Real Estate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p107 A Study on the Interaction of Apartment Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p103 Consumer Sentiment in On-line Community and t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p014 Modelling a property's time to sale by inflat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p006 Submarket Dynamics of Time to Sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p020 The Effect of Relisting on House Selling Pric
+p051 The Effect of Listing Price Changes on the Se</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p053 Can list prices accurately capture housing pr
+p054 House price index based on online listing inf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p045 Bidding Wars for Houses
 p079 Integrating Real Estate Market Conditions int</t>
   </si>
   <si>
-    <t xml:space="preserve">p059 Interpretation and measurement of the spread 
-p065 Incorporating the Number of Existing Home Sal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p076 Could We Have Predicted the Recent Downturn i
-p086 Anticipated vs. unanticipated house price mov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p121 Sale to list ratio, for-sale inventory, sale 
-p147 House hunting high and low: Constructing a Ho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p104 Forecasting Short-Term Housing Transaction Vo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이다윤</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">학부 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p063 Does Online Apartment Listing Volume Lead Pri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p096 Empirical Analyses of Factors Shaping the Rel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p089 A study on the impact of changes in consumer </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p003 Measuring Residential Real Estate Liquidity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p032 The Impacts of Property Features on Time on M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p016 The Probability of Sale and Price Premiums in
-p037 Understanding Housing Market Dynamics through</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p057 Signaling effects of recurrent list‐price red
-p060 Web-scraping housing prices in real-time: The</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p001 An Investigation of the Major Influences of R
-p087 Can Tightness in the Housing Market Help Pred</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p066 Price spreads and residential housing market 
-p067 Forecasting Connecticut home sales in a BVAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p078 The Economic Impact of Anticipated House Pric
-p098 INFORMATION CONTENT OF TRANSACTION VOLUME: TH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p125 Spatial and temporal diffusion of property pr
-p133 Forecasting Residential Real Estate Price Cha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p139 &lt;i&gt;FEAR Index&lt;/i&gt;, city characteristics, and </t>
-  </si>
-  <si>
-    <t xml:space="preserve">오건</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">학부 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">p128 A Study on the Typology of the Busan Housing </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p102 A Study on the Impact of the Trading Volume o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p092 Relationship Among News Coverage, Consumers’ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p009 Liquidating Real Estate Assets Quickly: What </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p004 Censored Sample Bias, Macroeconomic Factors, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p017 Does Time-on-Market Measurement Matter?
-p038 Listing Price, Time on Market, and Ultimate S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p034 Apartment prices, the business cycle and time
-p043 Bidding Conventions and the Degree of Overpri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p071 Running hot and cold in the urban home-owners
-p088 Expectation, volatility and liquidity in the </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p045 Bidding Wars for Houses
-p068 Using Leading Indicators to Forecast U.S. Hom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p080 Trading Volume-Induced Spatial Autocorrelatio
-p101 The cause and outcomes of the ripple effect: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p126 From Causes to Forecasts: Granger Causality a
-p134 Intercity Information Diffusion and Price Dis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p140 Google Search Queries, Foreclosures, and Hous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이지은</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p129 Apartment Transaction Volume and Price Volati</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p106 A Study on the Dynamic Causal Relationship be</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p094 A Study on the Effects of News Big Data and G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p012 Cross sectional Analysis of time on Market in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p005 Exploring Spatial Effects on Urban Housing Du</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p010 "Fire Sales" in Housing Market: Is the House-
-p018 For sale… but for how long? a methodological </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p036 Liquidity in housing markets: the effect of n
-p048 The Comparative Analysis Of Asking And Traded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p084 To Sell or Not to Sell: Measuring the Heat of
-p090 Does liquidity affect housing market performa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p055 Properties that Sell at or above Listing Pric
-p069 Testing Alternative Theories of the Property </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p047 List price and sales prices of residential pr
-p113 Features of the ripple effect in the US regio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p127 Housing Market Spillovers in China via Tradin
-p135 Online Information Search, Market Fundamental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p142 Use of Google Trends to Predict the Real Esta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">홍다연</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p074 Applications and Improvements of Real Estate </t>
-  </si>
-  <si>
-    <t xml:space="preserve">p107 A Study on the Interaction of Apartment Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p103 Consumer Sentiment in On-line Community and t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p014 Modelling a property's time to sale by inflat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p006 Submarket Dynamics of Time to Sale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p020 The Effect of Relisting on House Selling Pric
-p044 Asymmetric information and list-price reducti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p041 Measuring price expectations
-p049 Dynamic and Static Asking Prices in the Sydne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p100 Market depth in the UK housing market
-p110 Hot and cold seasons in Texas housing markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p061 Machine Learning Insights: Exploring Key Fact
-p072 Trading Volume and Price Dispersion in Housin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p081 Housing prices and transaction volume
-p114 Forecasting trading volume in local housing m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p091 Fundamentals and Market Sentiment in Housing 
-p130 From prediction to explanation for price–volu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p144 Predicting Housing Price Trends in Poland: On</t>
+    <t xml:space="preserve">p067 Forecasting Connecticut home sales in a BVAR 
+p080 Trading Volume-Induced Spatial Autocorrelatio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p101 The cause and outcomes of the ripple effect: 
+p132 Housing Prices and Transaction Volumes in Tai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p091 Fundamentals and Market Sentiment in Housing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p121 Sale to list ratio, for-sale inventory, sale </t>
   </si>
   <si>
     <t xml:space="preserve">pid</t>
@@ -11262,331 +11262,331 @@
     <t xml:space="preserve">10.1177/0042098014529341</t>
   </si>
   <si>
+    <t xml:space="preserve">10.1111/1540-6229.00038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.53383/100144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s11146-013-9450-z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3846/1648715x.2015.1072746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.regsciurbeco.2013.03.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s11146-015-9503-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s11146-016-9558-z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1162/rest_a_00634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s11146-020-09815-z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.jue.2004.05.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2478/jos-2022-0017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.jhe.2018.09.009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.jhe.2022.101906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/boer.12284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1177/0042098010363496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1515/remav-2015-0021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/jfir.12308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3846/ijspm.2025.23319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/1475-4932.12242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1108/jerer-12-2025-0098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/j.1080-8620.2004.00106.x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.frl.2018.10.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.jhe.2020.101715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/1540-6229.00410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/1540-6229.12082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s10901-005-6762-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1080/00036846.2015.1023943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/reec.12003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.landusepol.2016.05.008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1080/1331677x.2018.1429289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/infi.12408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1080/10527001.2020.1776513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s11146-026-10080-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1006/jhec.1995.1005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s11573-020-00990-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/bf01099111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.regsciurbeco.2024.103997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/reec.12015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1080/10835547.2012.12092059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1162/003465306775565783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1023/a:1007718725609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s11146-019-09714-y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1080/10835547.2002.12091081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3390/buildings14051471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1080/09599910802696615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s10660-026-10107-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s11146-008-9161-z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.regsciurbeco.2016.04.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s11146-009-9207-x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1080/10835547.2010.12092026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/1540-6229.12269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.48264/vvsiev-20223102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/j.1540-6229.2010.00292.x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/bf00217392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s11146-012-9375-y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.jhe.2013.01.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1080/12265934.2021.1925142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.jhe.2013.02.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1108/ecam-10-2020-0850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.regsciurbeco.2012.07.002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.jempfin.2021.10.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.17092/jibr.2013.10.1.159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/1540-6229.12463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.econmod.2014.03.026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.26650/istjecon2025-1707729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.jhe.2015.04.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/fire.70004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3846/ijspm.2018.5219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1098/rsfs.2025.0069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s00168-018-0870-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4236/jfrm.2026.152007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-01-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/1540-6229.12187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1257/aer.20141772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/j.1540-6229.2012.00329.x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s12205-019-1926-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1140/epjds/s13688-018-0176-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/1540-6229.12335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s11146-020-09789-y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.jhe.2026.102163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1080/10835547.2013.12091364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.53383/100332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s11146-014-9493-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2478/remav-2023-0032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007/s11146-015-9496-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1108/ijhma-12-2023-0166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1080/14036096.2016.1196240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-01-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-01-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1108/ijhma-09-2023-0118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111/jofi.13208</t>
+  </si>
+  <si>
     <t xml:space="preserve">10.1061/jupddm.upeng-5857</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1007/s11146-013-9450-z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/1540-6229.00038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.53383/100144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3846/1648715x.2015.1072746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s11146-015-9503-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1016/j.regsciurbeco.2013.03.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-12-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-12-08</t>
+    <t xml:space="preserve">10.1108/ijhma-12-2014-0058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1108/17539260910978481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1108/jerer-07-2025-0060</t>
   </si>
   <si>
     <t xml:space="preserve">10.1108/17538271311306048</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1162/rest_a_00634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s11146-016-9558-z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1016/j.jhe.2020.101715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1016/j.jhe.2018.09.009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s11146-020-09815-z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/boer.12284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2478/jos-2022-0017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/jfir.12308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1016/j.jhe.2022.101906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3846/ijspm.2025.23319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1177/0042098010363496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1108/jerer-12-2025-0098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1515/remav-2015-0021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1108/17539260910978481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/1475-4932.12242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-12-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-12-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1080/10527001.2020.1776513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1016/j.jue.2004.05.004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/j.1080-8620.2004.00106.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s11573-020-00990-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1016/j.frl.2018.10.004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1016/j.regsciurbeco.2024.103997</t>
-  </si>
-  <si>
     <t xml:space="preserve">10.1111/1540-6229.70013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1080/10835547.2012.12092059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/1540-6229.00410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/1540-6229.12082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s10901-005-6762-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1080/00036846.2015.1023943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/reec.12003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1016/j.landusepol.2016.05.008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1080/1331677x.2018.1429289</t>
-  </si>
-  <si>
     <t xml:space="preserve">10.1108/ijhma-02-2020-0017</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-12-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-12-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1162/003465306775565783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s10660-026-10107-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1016/j.regsciurbeco.2016.04.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/infi.12408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/1540-6229.12269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s11146-026-10080-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.48264/vvsiev-20223102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1006/jhec.1995.1005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/bf01099111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/bf00217392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/reec.12015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1023/a:1007718725609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s11146-019-09714-y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1080/10835547.2002.12091081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3390/buildings14051471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1080/09599910802696615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-12-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-12-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s11146-008-9161-z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1016/j.regsciurbeco.2012.07.002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s11146-009-9207-x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.17092/jibr.2013.10.1.159</t>
-  </si>
-  <si>
     <t xml:space="preserve">10.1108/17538271011049731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1016/j.econmod.2014.03.026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1080/10835547.2010.12092026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1016/j.jhe.2015.04.003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/j.1540-6229.2010.00292.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3846/ijspm.2018.5219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s11146-012-9375-y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s00168-018-0870-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1016/j.jhe.2013.01.003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1080/12265934.2021.1925142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1016/j.jhe.2013.02.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1108/ecam-10-2020-0850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-12-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-01-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4236/jfrm.2026.152007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1257/aer.20141772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/j.1540-6229.2012.00329.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1016/j.jempfin.2021.10.003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/1540-6229.12463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1140/epjds/s13688-018-0176-2</t>
-  </si>
-  <si>
     <t xml:space="preserve">10.1108/ijhma-08-2023-0113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1016/j.jhe.2026.102163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1108/ijhma-09-2023-0118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1080/10835547.2013.12091364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.26650/istjecon2025-1707729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s11146-014-9493-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/fire.70004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s11146-015-9496-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1080/14036096.2016.1196240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1098/rsfs.2025.0069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-01-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-01-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/jofi.13208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1108/ijhma-12-2023-0166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1108/ijhma-12-2014-0058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1108/jerer-07-2025-0060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/1540-6229.12187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s12205-019-1926-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1111/1540-6229.12335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1007/s11146-020-09789-y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.53383/100332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2478/remav-2023-0032</t>
   </si>
   <si>
     <t xml:space="preserve">배정</t>
@@ -25426,7 +25426,7 @@
       <c r="R51" s="12"/>
       <c r="S51" s="12"/>
     </row>
-    <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
         <v>382</v>
       </c>
@@ -25440,29 +25440,29 @@
         <v>90</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>877</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>888</v>
+        <v>873</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>166</v>
+        <v>305</v>
       </c>
       <c r="I52" s="8"/>
       <c r="J52" s="7" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>448</v>
+        <v>303</v>
       </c>
       <c r="L52" s="7" t="s">
         <v>941</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>450</v>
+        <v>167</v>
       </c>
       <c r="N52" s="12"/>
       <c r="O52" s="12"/>
@@ -25485,23 +25485,23 @@
         <v>104</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>413</v>
+        <v>391</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>877</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>888</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>305</v>
+        <v>873</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>175</v>
       </c>
       <c r="I53" s="8"/>
       <c r="J53" s="7" t="s">
-        <v>414</v>
+        <v>392</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>415</v>
+        <v>393</v>
       </c>
       <c r="L53" s="7" t="s">
         <v>942</v>
@@ -25530,23 +25530,23 @@
         <v>104</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>452</v>
+        <v>413</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>877</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>873</v>
+        <v>888</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>305</v>
       </c>
       <c r="I54" s="8"/>
       <c r="J54" s="7" t="s">
-        <v>453</v>
+        <v>414</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>303</v>
+        <v>415</v>
       </c>
       <c r="L54" s="7" t="s">
         <v>943</v>
@@ -25561,7 +25561,7 @@
       <c r="R54" s="12"/>
       <c r="S54" s="12"/>
     </row>
-    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
         <v>382</v>
       </c>
@@ -25575,23 +25575,23 @@
         <v>118</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>877</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>873</v>
+        <v>888</v>
       </c>
       <c r="H55" s="8" t="s">
         <v>175</v>
       </c>
       <c r="I55" s="8"/>
       <c r="J55" s="7" t="s">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="L55" s="7" t="s">
         <v>944</v>
@@ -25606,7 +25606,7 @@
       <c r="R55" s="12"/>
       <c r="S55" s="12"/>
     </row>
-    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
         <v>382</v>
       </c>
@@ -25620,23 +25620,23 @@
         <v>118</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>418</v>
+        <v>456</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>877</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>888</v>
+        <v>873</v>
       </c>
       <c r="H56" s="8" t="s">
         <v>175</v>
       </c>
       <c r="I56" s="8"/>
       <c r="J56" s="7" t="s">
-        <v>419</v>
+        <v>457</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="L56" s="7" t="s">
         <v>945</v>
@@ -25710,7 +25710,7 @@
         <v>131</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>456</v>
+        <v>503</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>877</v>
@@ -25718,15 +25718,15 @@
       <c r="G58" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H58" s="8" t="s">
-        <v>175</v>
+      <c r="H58" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I58" s="8"/>
       <c r="J58" s="7" t="s">
-        <v>457</v>
+        <v>504</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="L58" s="7" t="s">
         <v>947</v>
@@ -25755,7 +25755,7 @@
         <v>35</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>882</v>
@@ -25763,21 +25763,21 @@
       <c r="G59" s="7" t="s">
         <v>878</v>
       </c>
-      <c r="H59" s="8" t="s">
-        <v>175</v>
+      <c r="H59" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I59" s="8"/>
       <c r="J59" s="7" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>368</v>
+        <v>510</v>
       </c>
       <c r="L59" s="7" t="s">
         <v>950</v>
       </c>
       <c r="M59" s="8" t="s">
-        <v>450</v>
+        <v>167</v>
       </c>
       <c r="N59" s="12"/>
       <c r="O59" s="12"/>
@@ -25800,7 +25800,7 @@
         <v>35</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>508</v>
+        <v>533</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>882</v>
@@ -25813,10 +25813,10 @@
       </c>
       <c r="I60" s="8"/>
       <c r="J60" s="7" t="s">
-        <v>509</v>
+        <v>534</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>510</v>
+        <v>415</v>
       </c>
       <c r="L60" s="7" t="s">
         <v>951</v>
@@ -25831,7 +25831,7 @@
       <c r="R60" s="12"/>
       <c r="S60" s="12"/>
     </row>
-    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
         <v>461</v>
       </c>
@@ -25845,23 +25845,23 @@
         <v>49</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>503</v>
+        <v>546</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H61" s="7" t="s">
-        <v>305</v>
+      <c r="H61" s="8" t="s">
+        <v>175</v>
       </c>
       <c r="I61" s="8"/>
       <c r="J61" s="7" t="s">
-        <v>504</v>
+        <v>547</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>415</v>
+        <v>378</v>
       </c>
       <c r="L61" s="7" t="s">
         <v>952</v>
@@ -25876,7 +25876,7 @@
       <c r="R61" s="12"/>
       <c r="S61" s="12"/>
     </row>
-    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
         <v>461</v>
       </c>
@@ -25890,7 +25890,7 @@
         <v>49</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>882</v>
@@ -25903,10 +25903,10 @@
       </c>
       <c r="I62" s="8"/>
       <c r="J62" s="7" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>463</v>
+        <v>519</v>
       </c>
       <c r="L62" s="7" t="s">
         <v>953</v>
@@ -25980,7 +25980,7 @@
         <v>63</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>882</v>
@@ -25988,15 +25988,15 @@
       <c r="G64" s="7" t="s">
         <v>878</v>
       </c>
-      <c r="H64" s="7" t="s">
-        <v>305</v>
+      <c r="H64" s="8" t="s">
+        <v>175</v>
       </c>
       <c r="I64" s="8"/>
       <c r="J64" s="7" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>415</v>
+        <v>463</v>
       </c>
       <c r="L64" s="7" t="s">
         <v>955</v>
@@ -26056,7 +26056,7 @@
       <c r="R65" s="12"/>
       <c r="S65" s="12"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
         <v>461</v>
       </c>
@@ -26070,23 +26070,23 @@
         <v>76</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>517</v>
+        <v>486</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>882</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>878</v>
+        <v>888</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>175</v>
+        <v>411</v>
       </c>
       <c r="I66" s="8"/>
       <c r="J66" s="7" t="s">
-        <v>518</v>
+        <v>487</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>519</v>
+        <v>409</v>
       </c>
       <c r="L66" s="7" t="s">
         <v>957</v>
@@ -26101,7 +26101,7 @@
       <c r="R66" s="12"/>
       <c r="S66" s="12"/>
     </row>
-    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
         <v>461</v>
       </c>
@@ -26115,23 +26115,23 @@
         <v>90</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>522</v>
+        <v>493</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>873</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>166</v>
+        <v>888</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>175</v>
       </c>
       <c r="I67" s="8"/>
       <c r="J67" s="7" t="s">
-        <v>523</v>
+        <v>494</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>524</v>
+        <v>495</v>
       </c>
       <c r="L67" s="7" t="s">
         <v>958</v>
@@ -26160,23 +26160,23 @@
         <v>90</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>878</v>
-      </c>
-      <c r="H68" s="8" t="s">
-        <v>175</v>
+        <v>873</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="I68" s="8"/>
       <c r="J68" s="7" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>463</v>
+        <v>524</v>
       </c>
       <c r="L68" s="7" t="s">
         <v>959</v>
@@ -26236,7 +26236,7 @@
       <c r="R69" s="12"/>
       <c r="S69" s="12"/>
     </row>
-    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
         <v>461</v>
       </c>
@@ -26250,7 +26250,7 @@
         <v>104</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>882</v>
@@ -26263,10 +26263,10 @@
       </c>
       <c r="I70" s="8"/>
       <c r="J70" s="7" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>409</v>
+        <v>500</v>
       </c>
       <c r="L70" s="7" t="s">
         <v>961</v>
@@ -26326,7 +26326,7 @@
       <c r="R71" s="12"/>
       <c r="S71" s="12"/>
     </row>
-    <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
         <v>461</v>
       </c>
@@ -26340,23 +26340,23 @@
         <v>118</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>493</v>
+        <v>558</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>882</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>888</v>
-      </c>
-      <c r="H72" s="8" t="s">
-        <v>175</v>
+        <v>873</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I72" s="8"/>
       <c r="J72" s="7" t="s">
-        <v>494</v>
+        <v>559</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>495</v>
+        <v>303</v>
       </c>
       <c r="L72" s="7" t="s">
         <v>963</v>
@@ -26371,7 +26371,7 @@
       <c r="R72" s="12"/>
       <c r="S72" s="12"/>
     </row>
-    <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
         <v>461</v>
       </c>
@@ -26385,29 +26385,29 @@
         <v>131</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>481</v>
+        <v>550</v>
       </c>
       <c r="F73" s="7" t="s">
         <v>882</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="H73" s="8" t="s">
         <v>175</v>
       </c>
       <c r="I73" s="8"/>
       <c r="J73" s="7" t="s">
-        <v>482</v>
+        <v>551</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>478</v>
+        <v>552</v>
       </c>
       <c r="L73" s="7" t="s">
         <v>964</v>
       </c>
       <c r="M73" s="8" t="s">
-        <v>484</v>
+        <v>167</v>
       </c>
       <c r="N73" s="12"/>
       <c r="O73" s="12"/>
@@ -26416,7 +26416,7 @@
       <c r="R73" s="12"/>
       <c r="S73" s="12"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
         <v>461</v>
       </c>
@@ -26430,23 +26430,23 @@
         <v>131</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>882</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>888</v>
+        <v>878</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>411</v>
+        <v>175</v>
       </c>
       <c r="I74" s="8"/>
       <c r="J74" s="7" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="L74" s="7" t="s">
         <v>965</v>
@@ -26461,7 +26461,7 @@
       <c r="R74" s="12"/>
       <c r="S74" s="12"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
         <v>538</v>
       </c>
@@ -26475,7 +26475,7 @@
         <v>35</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>885</v>
@@ -26488,10 +26488,10 @@
       </c>
       <c r="I75" s="8"/>
       <c r="J75" s="7" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>384</v>
+        <v>303</v>
       </c>
       <c r="L75" s="7" t="s">
         <v>968</v>
@@ -26506,7 +26506,7 @@
       <c r="R75" s="12"/>
       <c r="S75" s="12"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
         <v>538</v>
       </c>
@@ -26520,23 +26520,23 @@
         <v>35</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>546</v>
+        <v>575</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="G76" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H76" s="8" t="s">
-        <v>175</v>
+      <c r="H76" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I76" s="8"/>
       <c r="J76" s="7" t="s">
-        <v>547</v>
+        <v>576</v>
       </c>
       <c r="K76" s="7" t="s">
-        <v>378</v>
+        <v>303</v>
       </c>
       <c r="L76" s="7" t="s">
         <v>969</v>
@@ -26565,23 +26565,23 @@
         <v>49</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>873</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>305</v>
+        <v>878</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>175</v>
       </c>
       <c r="I77" s="8"/>
       <c r="J77" s="7" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>303</v>
+        <v>564</v>
       </c>
       <c r="L77" s="7" t="s">
         <v>970</v>
@@ -26596,7 +26596,7 @@
       <c r="R77" s="12"/>
       <c r="S77" s="12"/>
     </row>
-    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
         <v>538</v>
       </c>
@@ -26610,23 +26610,23 @@
         <v>49</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>598</v>
+        <v>579</v>
       </c>
       <c r="F78" s="7" t="s">
         <v>885</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="H78" s="8" t="s">
         <v>175</v>
       </c>
       <c r="I78" s="8"/>
       <c r="J78" s="7" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>600</v>
+        <v>581</v>
       </c>
       <c r="L78" s="7" t="s">
         <v>971</v>
@@ -26641,7 +26641,7 @@
       <c r="R78" s="12"/>
       <c r="S78" s="12"/>
     </row>
-    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
         <v>538</v>
       </c>
@@ -26655,23 +26655,23 @@
         <v>63</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>550</v>
+        <v>571</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>873</v>
-      </c>
-      <c r="H79" s="8" t="s">
-        <v>175</v>
+        <v>878</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I79" s="8"/>
       <c r="J79" s="7" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>552</v>
+        <v>303</v>
       </c>
       <c r="L79" s="7" t="s">
         <v>972</v>
@@ -26700,23 +26700,23 @@
         <v>63</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>603</v>
+        <v>584</v>
       </c>
       <c r="F80" s="7" t="s">
         <v>885</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="H80" s="8" t="s">
         <v>175</v>
       </c>
       <c r="I80" s="8"/>
       <c r="J80" s="7" t="s">
-        <v>604</v>
+        <v>585</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>399</v>
+        <v>586</v>
       </c>
       <c r="L80" s="7" t="s">
         <v>973</v>
@@ -26731,7 +26731,7 @@
       <c r="R80" s="12"/>
       <c r="S80" s="12"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
         <v>538</v>
       </c>
@@ -26745,29 +26745,29 @@
         <v>76</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>555</v>
+        <v>589</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>873</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>305</v>
+        <v>878</v>
+      </c>
+      <c r="H81" s="8" t="s">
+        <v>175</v>
       </c>
       <c r="I81" s="8"/>
       <c r="J81" s="7" t="s">
-        <v>556</v>
+        <v>590</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>303</v>
+        <v>591</v>
       </c>
       <c r="L81" s="7" t="s">
         <v>974</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>450</v>
+        <v>167</v>
       </c>
       <c r="N81" s="12"/>
       <c r="O81" s="12"/>
@@ -26790,7 +26790,7 @@
         <v>76</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>567</v>
+        <v>669</v>
       </c>
       <c r="F82" s="7" t="s">
         <v>885</v>
@@ -26798,15 +26798,15 @@
       <c r="G82" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H82" s="7" t="s">
-        <v>305</v>
+      <c r="H82" s="8" t="s">
+        <v>673</v>
       </c>
       <c r="I82" s="8"/>
       <c r="J82" s="7" t="s">
-        <v>568</v>
+        <v>670</v>
       </c>
       <c r="K82" s="7" t="s">
-        <v>384</v>
+        <v>671</v>
       </c>
       <c r="L82" s="7" t="s">
         <v>975</v>
@@ -26821,7 +26821,7 @@
       <c r="R82" s="12"/>
       <c r="S82" s="12"/>
     </row>
-    <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
         <v>538</v>
       </c>
@@ -26835,7 +26835,7 @@
         <v>90</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>885</v>
@@ -26848,10 +26848,10 @@
       </c>
       <c r="I83" s="8"/>
       <c r="J83" s="7" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>303</v>
+        <v>384</v>
       </c>
       <c r="L83" s="7" t="s">
         <v>976</v>
@@ -26866,7 +26866,7 @@
       <c r="R83" s="12"/>
       <c r="S83" s="12"/>
     </row>
-    <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
         <v>538</v>
       </c>
@@ -26880,7 +26880,7 @@
         <v>90</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>575</v>
+        <v>675</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>885</v>
@@ -26893,10 +26893,10 @@
       </c>
       <c r="I84" s="8"/>
       <c r="J84" s="7" t="s">
-        <v>576</v>
+        <v>676</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>303</v>
+        <v>415</v>
       </c>
       <c r="L84" s="7" t="s">
         <v>977</v>
@@ -26925,23 +26925,23 @@
         <v>104</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>562</v>
+        <v>639</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="G85" s="7" t="s">
         <v>878</v>
       </c>
-      <c r="H85" s="8" t="s">
-        <v>175</v>
+      <c r="H85" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I85" s="8"/>
       <c r="J85" s="7" t="s">
-        <v>563</v>
+        <v>640</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>564</v>
+        <v>463</v>
       </c>
       <c r="L85" s="7" t="s">
         <v>978</v>
@@ -26956,7 +26956,7 @@
       <c r="R85" s="12"/>
       <c r="S85" s="12"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
         <v>538</v>
       </c>
@@ -26970,23 +26970,23 @@
         <v>104</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>579</v>
+        <v>598</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>885</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="H86" s="8" t="s">
         <v>175</v>
       </c>
       <c r="I86" s="8"/>
       <c r="J86" s="7" t="s">
-        <v>580</v>
+        <v>599</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>581</v>
+        <v>600</v>
       </c>
       <c r="L86" s="7" t="s">
         <v>979</v>
@@ -27001,7 +27001,7 @@
       <c r="R86" s="12"/>
       <c r="S86" s="12"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
         <v>538</v>
       </c>
@@ -27015,10 +27015,10 @@
         <v>118</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>571</v>
+        <v>643</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="G87" s="7" t="s">
         <v>878</v>
@@ -27028,10 +27028,10 @@
       </c>
       <c r="I87" s="8"/>
       <c r="J87" s="7" t="s">
-        <v>572</v>
+        <v>644</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>303</v>
+        <v>415</v>
       </c>
       <c r="L87" s="7" t="s">
         <v>980</v>
@@ -27060,23 +27060,23 @@
         <v>118</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>584</v>
+        <v>603</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>885</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="H88" s="8" t="s">
         <v>175</v>
       </c>
       <c r="I88" s="8"/>
       <c r="J88" s="7" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>586</v>
+        <v>399</v>
       </c>
       <c r="L88" s="7" t="s">
         <v>981</v>
@@ -27091,7 +27091,7 @@
       <c r="R88" s="12"/>
       <c r="S88" s="12"/>
     </row>
-    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
         <v>538</v>
       </c>
@@ -27105,23 +27105,23 @@
         <v>131</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="G89" s="7" t="s">
         <v>878</v>
       </c>
-      <c r="H89" s="8" t="s">
-        <v>175</v>
+      <c r="H89" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I89" s="8"/>
       <c r="J89" s="7" t="s">
-        <v>590</v>
+        <v>613</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>591</v>
+        <v>303</v>
       </c>
       <c r="L89" s="7" t="s">
         <v>982</v>
@@ -27136,7 +27136,7 @@
       <c r="R89" s="12"/>
       <c r="S89" s="12"/>
     </row>
-    <row r="90" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
         <v>538</v>
       </c>
@@ -27150,7 +27150,7 @@
         <v>131</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>594</v>
+        <v>567</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>885</v>
@@ -27163,16 +27163,16 @@
       </c>
       <c r="I90" s="8"/>
       <c r="J90" s="7" t="s">
-        <v>595</v>
+        <v>568</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="L90" s="7" t="s">
         <v>983</v>
       </c>
       <c r="M90" s="8" t="s">
-        <v>484</v>
+        <v>167</v>
       </c>
       <c r="N90" s="12"/>
       <c r="O90" s="12"/>
@@ -27226,7 +27226,7 @@
       <c r="R91" s="12"/>
       <c r="S91" s="12"/>
     </row>
-    <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
         <v>608</v>
       </c>
@@ -27240,23 +27240,23 @@
         <v>35</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>634</v>
+        <v>651</v>
       </c>
       <c r="F92" s="7" t="s">
         <v>872</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>878</v>
-      </c>
-      <c r="H92" s="8" t="s">
-        <v>175</v>
+        <v>873</v>
+      </c>
+      <c r="H92" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I92" s="8"/>
       <c r="J92" s="7" t="s">
-        <v>635</v>
+        <v>652</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>636</v>
+        <v>415</v>
       </c>
       <c r="L92" s="7" t="s">
         <v>987</v>
@@ -27271,7 +27271,7 @@
       <c r="R92" s="12"/>
       <c r="S92" s="12"/>
     </row>
-    <row r="93" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
         <v>608</v>
       </c>
@@ -27285,23 +27285,23 @@
         <v>49</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>872</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>888</v>
-      </c>
-      <c r="H93" s="8" t="s">
-        <v>351</v>
+        <v>878</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I93" s="8"/>
       <c r="J93" s="7" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="L93" s="7" t="s">
         <v>988</v>
@@ -27330,23 +27330,23 @@
         <v>49</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="G94" s="7" t="s">
         <v>873</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>673</v>
+        <v>175</v>
       </c>
       <c r="I94" s="8"/>
       <c r="J94" s="7" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>671</v>
+        <v>344</v>
       </c>
       <c r="L94" s="7" t="s">
         <v>989</v>
@@ -27361,7 +27361,7 @@
       <c r="R94" s="12"/>
       <c r="S94" s="12"/>
     </row>
-    <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
         <v>608</v>
       </c>
@@ -27375,23 +27375,23 @@
         <v>63</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>664</v>
+        <v>629</v>
       </c>
       <c r="F95" s="7" t="s">
         <v>872</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>888</v>
+        <v>878</v>
       </c>
       <c r="H95" s="7" t="s">
         <v>305</v>
       </c>
       <c r="I95" s="8"/>
       <c r="J95" s="7" t="s">
-        <v>665</v>
+        <v>630</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>303</v>
+        <v>631</v>
       </c>
       <c r="L95" s="7" t="s">
         <v>990</v>
@@ -27406,7 +27406,7 @@
       <c r="R95" s="12"/>
       <c r="S95" s="12"/>
     </row>
-    <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
         <v>608</v>
       </c>
@@ -27420,23 +27420,23 @@
         <v>63</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="G96" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H96" s="7" t="s">
-        <v>305</v>
+      <c r="H96" s="8" t="s">
+        <v>175</v>
       </c>
       <c r="I96" s="8"/>
       <c r="J96" s="7" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>415</v>
+        <v>661</v>
       </c>
       <c r="L96" s="7" t="s">
         <v>991</v>
@@ -27451,7 +27451,7 @@
       <c r="R96" s="12"/>
       <c r="S96" s="12"/>
     </row>
-    <row r="97" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
         <v>608</v>
       </c>
@@ -27465,23 +27465,23 @@
         <v>76</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>624</v>
+        <v>634</v>
       </c>
       <c r="F97" s="7" t="s">
         <v>872</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>888</v>
+        <v>878</v>
       </c>
       <c r="H97" s="8" t="s">
         <v>175</v>
       </c>
       <c r="I97" s="8"/>
       <c r="J97" s="7" t="s">
-        <v>625</v>
+        <v>635</v>
       </c>
       <c r="K97" s="7" t="s">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="L97" s="7" t="s">
         <v>992</v>
@@ -27510,23 +27510,23 @@
         <v>76</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>639</v>
+        <v>687</v>
       </c>
       <c r="F98" s="7" t="s">
         <v>872</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>878</v>
-      </c>
-      <c r="H98" s="7" t="s">
-        <v>305</v>
+        <v>873</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>175</v>
       </c>
       <c r="I98" s="8"/>
       <c r="J98" s="7" t="s">
-        <v>640</v>
+        <v>688</v>
       </c>
       <c r="K98" s="7" t="s">
-        <v>463</v>
+        <v>415</v>
       </c>
       <c r="L98" s="7" t="s">
         <v>993</v>
@@ -27541,7 +27541,7 @@
       <c r="R98" s="12"/>
       <c r="S98" s="12"/>
     </row>
-    <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
         <v>608</v>
       </c>
@@ -27555,23 +27555,23 @@
         <v>90</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>643</v>
+        <v>616</v>
       </c>
       <c r="F99" s="7" t="s">
         <v>872</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>878</v>
-      </c>
-      <c r="H99" s="7" t="s">
-        <v>305</v>
+        <v>888</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>351</v>
       </c>
       <c r="I99" s="8"/>
       <c r="J99" s="7" t="s">
-        <v>644</v>
+        <v>617</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="L99" s="7" t="s">
         <v>994</v>
@@ -27586,7 +27586,7 @@
       <c r="R99" s="12"/>
       <c r="S99" s="12"/>
     </row>
-    <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="s">
         <v>608</v>
       </c>
@@ -27600,7 +27600,7 @@
         <v>90</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>647</v>
+        <v>691</v>
       </c>
       <c r="F100" s="7" t="s">
         <v>872</v>
@@ -27608,12 +27608,12 @@
       <c r="G100" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H100" s="7" t="s">
-        <v>305</v>
+      <c r="H100" s="8" t="s">
+        <v>351</v>
       </c>
       <c r="I100" s="8"/>
       <c r="J100" s="7" t="s">
-        <v>648</v>
+        <v>692</v>
       </c>
       <c r="K100" s="7" t="s">
         <v>415</v>
@@ -27631,7 +27631,7 @@
       <c r="R100" s="12"/>
       <c r="S100" s="12"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="s">
         <v>608</v>
       </c>
@@ -27645,23 +27645,23 @@
         <v>104</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>612</v>
+        <v>695</v>
       </c>
       <c r="F101" s="7" t="s">
         <v>872</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="H101" s="7" t="s">
         <v>305</v>
       </c>
       <c r="I101" s="8"/>
       <c r="J101" s="7" t="s">
-        <v>613</v>
+        <v>696</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>303</v>
+        <v>384</v>
       </c>
       <c r="L101" s="7" t="s">
         <v>996</v>
@@ -27690,23 +27690,23 @@
         <v>104</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>651</v>
+        <v>664</v>
       </c>
       <c r="F102" s="7" t="s">
         <v>872</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>873</v>
+        <v>888</v>
       </c>
       <c r="H102" s="7" t="s">
         <v>305</v>
       </c>
       <c r="I102" s="8"/>
       <c r="J102" s="7" t="s">
-        <v>652</v>
+        <v>665</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>415</v>
+        <v>303</v>
       </c>
       <c r="L102" s="7" t="s">
         <v>997</v>
@@ -27721,7 +27721,7 @@
       <c r="R102" s="12"/>
       <c r="S102" s="12"/>
     </row>
-    <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="s">
         <v>608</v>
       </c>
@@ -27735,23 +27735,23 @@
         <v>118</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="F103" s="7" t="s">
         <v>872</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>878</v>
-      </c>
-      <c r="H103" s="7" t="s">
-        <v>305</v>
+        <v>888</v>
+      </c>
+      <c r="H103" s="8" t="s">
+        <v>175</v>
       </c>
       <c r="I103" s="8"/>
       <c r="J103" s="7" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>415</v>
+        <v>626</v>
       </c>
       <c r="L103" s="7" t="s">
         <v>998</v>
@@ -27780,7 +27780,7 @@
         <v>118</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>655</v>
+        <v>699</v>
       </c>
       <c r="F104" s="7" t="s">
         <v>872</v>
@@ -27788,15 +27788,15 @@
       <c r="G104" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H104" s="8" t="s">
-        <v>175</v>
+      <c r="H104" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I104" s="8"/>
       <c r="J104" s="7" t="s">
-        <v>656</v>
+        <v>700</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>344</v>
+        <v>303</v>
       </c>
       <c r="L104" s="7" t="s">
         <v>999</v>
@@ -27811,7 +27811,7 @@
       <c r="R104" s="12"/>
       <c r="S104" s="12"/>
     </row>
-    <row r="105" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
         <v>608</v>
       </c>
@@ -27825,23 +27825,23 @@
         <v>131</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="F105" s="7" t="s">
         <v>872</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="H105" s="7" t="s">
         <v>305</v>
       </c>
       <c r="I105" s="8"/>
       <c r="J105" s="7" t="s">
-        <v>630</v>
+        <v>648</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>631</v>
+        <v>415</v>
       </c>
       <c r="L105" s="7" t="s">
         <v>1000</v>
@@ -27856,7 +27856,7 @@
       <c r="R105" s="12"/>
       <c r="S105" s="12"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
         <v>608</v>
       </c>
@@ -27870,7 +27870,7 @@
         <v>131</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>659</v>
+        <v>703</v>
       </c>
       <c r="F106" s="7" t="s">
         <v>872</v>
@@ -27879,14 +27879,14 @@
         <v>873</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="I106" s="8"/>
       <c r="J106" s="7" t="s">
-        <v>660</v>
+        <v>704</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>661</v>
+        <v>415</v>
       </c>
       <c r="L106" s="7" t="s">
         <v>1001</v>
@@ -27915,7 +27915,7 @@
         <v>35</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="F107" s="7" t="s">
         <v>872</v>
@@ -27928,10 +27928,10 @@
       </c>
       <c r="I107" s="8"/>
       <c r="J107" s="7" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>415</v>
+        <v>463</v>
       </c>
       <c r="L107" s="7" t="s">
         <v>1004</v>
@@ -27960,7 +27960,7 @@
         <v>35</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>711</v>
+        <v>738</v>
       </c>
       <c r="F108" s="7" t="s">
         <v>872</v>
@@ -27968,15 +27968,15 @@
       <c r="G108" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H108" s="8" t="s">
-        <v>175</v>
+      <c r="H108" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I108" s="8"/>
       <c r="J108" s="7" t="s">
-        <v>712</v>
+        <v>739</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>399</v>
+        <v>264</v>
       </c>
       <c r="L108" s="7" t="s">
         <v>1005</v>
@@ -27991,7 +27991,7 @@
       <c r="R108" s="12"/>
       <c r="S108" s="12"/>
     </row>
-    <row r="109" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
         <v>680</v>
       </c>
@@ -28005,7 +28005,7 @@
         <v>49</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>691</v>
+        <v>707</v>
       </c>
       <c r="F109" s="7" t="s">
         <v>872</v>
@@ -28013,15 +28013,15 @@
       <c r="G109" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H109" s="8" t="s">
-        <v>351</v>
+      <c r="H109" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I109" s="8"/>
       <c r="J109" s="7" t="s">
-        <v>692</v>
+        <v>708</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>415</v>
+        <v>463</v>
       </c>
       <c r="L109" s="7" t="s">
         <v>1006</v>
@@ -28036,7 +28036,7 @@
       <c r="R109" s="12"/>
       <c r="S109" s="12"/>
     </row>
-    <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
         <v>680</v>
       </c>
@@ -28050,7 +28050,7 @@
         <v>49</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>715</v>
+        <v>742</v>
       </c>
       <c r="F110" s="7" t="s">
         <v>872</v>
@@ -28059,14 +28059,14 @@
         <v>873</v>
       </c>
       <c r="H110" s="8" t="s">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="I110" s="8"/>
       <c r="J110" s="7" t="s">
-        <v>716</v>
+        <v>743</v>
       </c>
       <c r="K110" s="7" t="s">
-        <v>717</v>
+        <v>744</v>
       </c>
       <c r="L110" s="7" t="s">
         <v>1007</v>
@@ -28095,7 +28095,7 @@
         <v>63</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>679</v>
+        <v>711</v>
       </c>
       <c r="F111" s="7" t="s">
         <v>872</v>
@@ -28108,16 +28108,16 @@
       </c>
       <c r="I111" s="8"/>
       <c r="J111" s="7" t="s">
-        <v>681</v>
+        <v>712</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>368</v>
+        <v>399</v>
       </c>
       <c r="L111" s="7" t="s">
         <v>1008</v>
       </c>
       <c r="M111" s="8" t="s">
-        <v>450</v>
+        <v>167</v>
       </c>
       <c r="N111" s="12"/>
       <c r="O111" s="12"/>
@@ -28140,7 +28140,7 @@
         <v>63</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>720</v>
+        <v>757</v>
       </c>
       <c r="F112" s="7" t="s">
         <v>872</v>
@@ -28149,14 +28149,14 @@
         <v>873</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>175</v>
+        <v>673</v>
       </c>
       <c r="I112" s="8"/>
       <c r="J112" s="7" t="s">
-        <v>721</v>
+        <v>758</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>722</v>
+        <v>759</v>
       </c>
       <c r="L112" s="7" t="s">
         <v>1009</v>
@@ -28185,7 +28185,7 @@
         <v>76</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>695</v>
+        <v>715</v>
       </c>
       <c r="F113" s="7" t="s">
         <v>872</v>
@@ -28193,15 +28193,15 @@
       <c r="G113" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H113" s="7" t="s">
-        <v>305</v>
+      <c r="H113" s="8" t="s">
+        <v>175</v>
       </c>
       <c r="I113" s="8"/>
       <c r="J113" s="7" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>384</v>
+        <v>717</v>
       </c>
       <c r="L113" s="7" t="s">
         <v>1010</v>
@@ -28230,7 +28230,7 @@
         <v>76</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="F114" s="7" t="s">
         <v>872</v>
@@ -28238,15 +28238,15 @@
       <c r="G114" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H114" s="7" t="s">
-        <v>305</v>
+      <c r="H114" s="8" t="s">
+        <v>175</v>
       </c>
       <c r="I114" s="8"/>
       <c r="J114" s="7" t="s">
-        <v>726</v>
+        <v>763</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>463</v>
+        <v>303</v>
       </c>
       <c r="L114" s="7" t="s">
         <v>1011</v>
@@ -28275,7 +28275,7 @@
         <v>90</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>699</v>
+        <v>720</v>
       </c>
       <c r="F115" s="7" t="s">
         <v>872</v>
@@ -28283,15 +28283,15 @@
       <c r="G115" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H115" s="7" t="s">
-        <v>305</v>
+      <c r="H115" s="8" t="s">
+        <v>175</v>
       </c>
       <c r="I115" s="8"/>
       <c r="J115" s="7" t="s">
-        <v>700</v>
+        <v>721</v>
       </c>
       <c r="K115" s="7" t="s">
-        <v>303</v>
+        <v>722</v>
       </c>
       <c r="L115" s="7" t="s">
         <v>1012</v>
@@ -28306,7 +28306,7 @@
       <c r="R115" s="12"/>
       <c r="S115" s="12"/>
     </row>
-    <row r="116" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
         <v>680</v>
       </c>
@@ -28320,7 +28320,7 @@
         <v>90</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>729</v>
+        <v>772</v>
       </c>
       <c r="F116" s="7" t="s">
         <v>872</v>
@@ -28333,10 +28333,10 @@
       </c>
       <c r="I116" s="8"/>
       <c r="J116" s="7" t="s">
-        <v>730</v>
+        <v>773</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>420</v>
+        <v>774</v>
       </c>
       <c r="L116" s="7" t="s">
         <v>1013</v>
@@ -28351,7 +28351,7 @@
       <c r="R116" s="12"/>
       <c r="S116" s="12"/>
     </row>
-    <row r="117" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
         <v>680</v>
       </c>
@@ -28365,7 +28365,7 @@
         <v>104</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>703</v>
+        <v>725</v>
       </c>
       <c r="F117" s="7" t="s">
         <v>872</v>
@@ -28373,15 +28373,15 @@
       <c r="G117" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H117" s="8" t="s">
-        <v>351</v>
+      <c r="H117" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I117" s="8"/>
       <c r="J117" s="7" t="s">
-        <v>704</v>
+        <v>726</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>415</v>
+        <v>463</v>
       </c>
       <c r="L117" s="7" t="s">
         <v>1014</v>
@@ -28396,7 +28396,7 @@
       <c r="R117" s="12"/>
       <c r="S117" s="12"/>
     </row>
-    <row r="118" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
         <v>680</v>
       </c>
@@ -28410,7 +28410,7 @@
         <v>104</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>733</v>
+        <v>777</v>
       </c>
       <c r="F118" s="7" t="s">
         <v>872</v>
@@ -28419,14 +28419,14 @@
         <v>873</v>
       </c>
       <c r="H118" s="8" t="s">
-        <v>351</v>
+        <v>175</v>
       </c>
       <c r="I118" s="8"/>
       <c r="J118" s="7" t="s">
-        <v>734</v>
+        <v>778</v>
       </c>
       <c r="K118" s="7" t="s">
-        <v>735</v>
+        <v>779</v>
       </c>
       <c r="L118" s="7" t="s">
         <v>1015</v>
@@ -28441,7 +28441,7 @@
       <c r="R118" s="12"/>
       <c r="S118" s="12"/>
     </row>
-    <row r="119" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
         <v>680</v>
       </c>
@@ -28455,7 +28455,7 @@
         <v>118</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>683</v>
+        <v>729</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>872</v>
@@ -28468,10 +28468,10 @@
       </c>
       <c r="I119" s="8"/>
       <c r="J119" s="7" t="s">
-        <v>684</v>
+        <v>730</v>
       </c>
       <c r="K119" s="7" t="s">
-        <v>463</v>
+        <v>420</v>
       </c>
       <c r="L119" s="7" t="s">
         <v>1016</v>
@@ -28500,7 +28500,7 @@
         <v>118</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>738</v>
+        <v>782</v>
       </c>
       <c r="F120" s="7" t="s">
         <v>872</v>
@@ -28508,15 +28508,15 @@
       <c r="G120" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H120" s="7" t="s">
-        <v>305</v>
+      <c r="H120" s="8" t="s">
+        <v>673</v>
       </c>
       <c r="I120" s="8"/>
       <c r="J120" s="7" t="s">
-        <v>739</v>
+        <v>783</v>
       </c>
       <c r="K120" s="7" t="s">
-        <v>264</v>
+        <v>784</v>
       </c>
       <c r="L120" s="7" t="s">
         <v>1017</v>
@@ -28531,7 +28531,7 @@
       <c r="R120" s="12"/>
       <c r="S120" s="12"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
         <v>680</v>
       </c>
@@ -28545,7 +28545,7 @@
         <v>131</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>707</v>
+        <v>733</v>
       </c>
       <c r="F121" s="7" t="s">
         <v>872</v>
@@ -28553,15 +28553,15 @@
       <c r="G121" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H121" s="7" t="s">
-        <v>305</v>
+      <c r="H121" s="8" t="s">
+        <v>351</v>
       </c>
       <c r="I121" s="8"/>
       <c r="J121" s="7" t="s">
-        <v>708</v>
+        <v>734</v>
       </c>
       <c r="K121" s="7" t="s">
-        <v>463</v>
+        <v>735</v>
       </c>
       <c r="L121" s="7" t="s">
         <v>1018</v>
@@ -28576,7 +28576,7 @@
       <c r="R121" s="12"/>
       <c r="S121" s="12"/>
     </row>
-    <row r="122" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
         <v>680</v>
       </c>
@@ -28590,7 +28590,7 @@
         <v>131</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>742</v>
+        <v>787</v>
       </c>
       <c r="F122" s="7" t="s">
         <v>872</v>
@@ -28599,14 +28599,14 @@
         <v>873</v>
       </c>
       <c r="H122" s="8" t="s">
-        <v>351</v>
+        <v>175</v>
       </c>
       <c r="I122" s="8"/>
       <c r="J122" s="7" t="s">
-        <v>743</v>
+        <v>788</v>
       </c>
       <c r="K122" s="7" t="s">
-        <v>744</v>
+        <v>789</v>
       </c>
       <c r="L122" s="7" t="s">
         <v>1019</v>
@@ -28635,10 +28635,10 @@
         <v>35</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>787</v>
+        <v>827</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>872</v>
+        <v>906</v>
       </c>
       <c r="G123" s="7" t="s">
         <v>873</v>
@@ -28648,10 +28648,10 @@
       </c>
       <c r="I123" s="8"/>
       <c r="J123" s="7" t="s">
-        <v>788</v>
+        <v>828</v>
       </c>
       <c r="K123" s="7" t="s">
-        <v>789</v>
+        <v>303</v>
       </c>
       <c r="L123" s="7" t="s">
         <v>1022</v>
@@ -28770,23 +28770,23 @@
         <v>49</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>757</v>
+        <v>818</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>872</v>
+        <v>906</v>
       </c>
       <c r="G126" s="7" t="s">
         <v>873</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>673</v>
+        <v>175</v>
       </c>
       <c r="I126" s="8"/>
       <c r="J126" s="7" t="s">
-        <v>758</v>
+        <v>820</v>
       </c>
       <c r="K126" s="7" t="s">
-        <v>759</v>
+        <v>821</v>
       </c>
       <c r="L126" s="7" t="s">
         <v>1025</v>
@@ -28815,23 +28815,23 @@
         <v>63</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>762</v>
+        <v>804</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>872</v>
+        <v>906</v>
       </c>
       <c r="G127" s="7" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="H127" s="8" t="s">
         <v>175</v>
       </c>
       <c r="I127" s="8"/>
       <c r="J127" s="7" t="s">
-        <v>763</v>
+        <v>805</v>
       </c>
       <c r="K127" s="7" t="s">
-        <v>303</v>
+        <v>806</v>
       </c>
       <c r="L127" s="7" t="s">
         <v>1026</v>
@@ -28846,7 +28846,7 @@
       <c r="R127" s="12"/>
       <c r="S127" s="12"/>
     </row>
-    <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
         <v>748</v>
       </c>
@@ -28860,23 +28860,23 @@
         <v>63</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>804</v>
+        <v>831</v>
       </c>
       <c r="F128" s="7" t="s">
         <v>906</v>
       </c>
       <c r="G128" s="7" t="s">
-        <v>878</v>
-      </c>
-      <c r="H128" s="8" t="s">
-        <v>175</v>
+        <v>873</v>
+      </c>
+      <c r="H128" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I128" s="8"/>
       <c r="J128" s="7" t="s">
-        <v>805</v>
+        <v>832</v>
       </c>
       <c r="K128" s="7" t="s">
-        <v>806</v>
+        <v>303</v>
       </c>
       <c r="L128" s="7" t="s">
         <v>1027</v>
@@ -28905,10 +28905,10 @@
         <v>76</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>766</v>
+        <v>836</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>872</v>
+        <v>906</v>
       </c>
       <c r="G129" s="7" t="s">
         <v>873</v>
@@ -28918,16 +28918,16 @@
       </c>
       <c r="I129" s="8"/>
       <c r="J129" s="7" t="s">
-        <v>767</v>
+        <v>837</v>
       </c>
       <c r="K129" s="7" t="s">
-        <v>368</v>
+        <v>415</v>
       </c>
       <c r="L129" s="7" t="s">
         <v>1028</v>
       </c>
       <c r="M129" s="8" t="s">
-        <v>450</v>
+        <v>167</v>
       </c>
       <c r="N129" s="12"/>
       <c r="O129" s="12"/>
@@ -28995,29 +28995,29 @@
         <v>90</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>769</v>
+        <v>792</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>872</v>
+        <v>906</v>
       </c>
       <c r="G131" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H131" s="8" t="s">
-        <v>175</v>
+      <c r="H131" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I131" s="8"/>
       <c r="J131" s="7" t="s">
-        <v>770</v>
+        <v>793</v>
       </c>
       <c r="K131" s="7" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="L131" s="7" t="s">
         <v>1030</v>
       </c>
       <c r="M131" s="8" t="s">
-        <v>450</v>
+        <v>167</v>
       </c>
       <c r="N131" s="12"/>
       <c r="O131" s="12"/>
@@ -29040,7 +29040,7 @@
         <v>90</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>792</v>
+        <v>840</v>
       </c>
       <c r="F132" s="7" t="s">
         <v>906</v>
@@ -29048,15 +29048,15 @@
       <c r="G132" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H132" s="7" t="s">
-        <v>305</v>
+      <c r="H132" s="8" t="s">
+        <v>175</v>
       </c>
       <c r="I132" s="8"/>
       <c r="J132" s="7" t="s">
-        <v>793</v>
+        <v>841</v>
       </c>
       <c r="K132" s="7" t="s">
-        <v>344</v>
+        <v>393</v>
       </c>
       <c r="L132" s="7" t="s">
         <v>1031</v>
@@ -29085,23 +29085,23 @@
         <v>104</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>772</v>
+        <v>796</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>872</v>
+        <v>906</v>
       </c>
       <c r="G133" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H133" s="8" t="s">
-        <v>175</v>
+      <c r="H133" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I133" s="8"/>
       <c r="J133" s="7" t="s">
-        <v>773</v>
+        <v>797</v>
       </c>
       <c r="K133" s="7" t="s">
-        <v>774</v>
+        <v>415</v>
       </c>
       <c r="L133" s="7" t="s">
         <v>1032</v>
@@ -29130,7 +29130,7 @@
         <v>104</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>796</v>
+        <v>849</v>
       </c>
       <c r="F134" s="7" t="s">
         <v>906</v>
@@ -29138,15 +29138,15 @@
       <c r="G134" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H134" s="7" t="s">
-        <v>305</v>
+      <c r="H134" s="8" t="s">
+        <v>175</v>
       </c>
       <c r="I134" s="8"/>
       <c r="J134" s="7" t="s">
-        <v>797</v>
+        <v>850</v>
       </c>
       <c r="K134" s="7" t="s">
-        <v>415</v>
+        <v>495</v>
       </c>
       <c r="L134" s="7" t="s">
         <v>1033</v>
@@ -29161,7 +29161,7 @@
       <c r="R134" s="12"/>
       <c r="S134" s="12"/>
     </row>
-    <row r="135" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
         <v>748</v>
       </c>
@@ -29175,23 +29175,23 @@
         <v>118</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>777</v>
+        <v>800</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>872</v>
+        <v>906</v>
       </c>
       <c r="G135" s="7" t="s">
         <v>873</v>
       </c>
       <c r="H135" s="8" t="s">
-        <v>175</v>
+        <v>351</v>
       </c>
       <c r="I135" s="8"/>
       <c r="J135" s="7" t="s">
-        <v>778</v>
+        <v>801</v>
       </c>
       <c r="K135" s="7" t="s">
-        <v>779</v>
+        <v>415</v>
       </c>
       <c r="L135" s="7" t="s">
         <v>1034</v>
@@ -29206,7 +29206,7 @@
       <c r="R135" s="12"/>
       <c r="S135" s="12"/>
     </row>
-    <row r="136" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
         <v>748</v>
       </c>
@@ -29220,7 +29220,7 @@
         <v>118</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>800</v>
+        <v>853</v>
       </c>
       <c r="F136" s="7" t="s">
         <v>906</v>
@@ -29228,15 +29228,15 @@
       <c r="G136" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H136" s="8" t="s">
-        <v>351</v>
+      <c r="H136" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I136" s="8"/>
       <c r="J136" s="7" t="s">
-        <v>801</v>
+        <v>854</v>
       </c>
       <c r="K136" s="7" t="s">
-        <v>415</v>
+        <v>368</v>
       </c>
       <c r="L136" s="7" t="s">
         <v>1035</v>
@@ -29298,19 +29298,19 @@
     </row>
     <row r="138" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>748</v>
+        <v>819</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>1020</v>
+        <v>1037</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>1021</v>
+        <v>1038</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="F138" s="7" t="s">
         <v>872</v>
@@ -29319,20 +29319,20 @@
         <v>873</v>
       </c>
       <c r="H138" s="8" t="s">
-        <v>673</v>
+        <v>175</v>
       </c>
       <c r="I138" s="8"/>
       <c r="J138" s="7" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="K138" s="7" t="s">
-        <v>784</v>
+        <v>368</v>
       </c>
       <c r="L138" s="7" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="M138" s="8" t="s">
-        <v>167</v>
+        <v>450</v>
       </c>
       <c r="N138" s="12"/>
       <c r="O138" s="12"/>
@@ -29346,10 +29346,10 @@
         <v>819</v>
       </c>
       <c r="B139" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C139" s="7" t="s">
         <v>1038</v>
-      </c>
-      <c r="C139" s="7" t="s">
-        <v>1039</v>
       </c>
       <c r="D139" s="8" t="s">
         <v>35</v>
@@ -29386,43 +29386,43 @@
       <c r="R139" s="12"/>
       <c r="S139" s="12"/>
     </row>
-    <row r="140" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
         <v>819</v>
       </c>
       <c r="B140" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C140" s="7" t="s">
         <v>1038</v>
       </c>
-      <c r="C140" s="7" t="s">
-        <v>1039</v>
-      </c>
       <c r="D140" s="8" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>853</v>
+        <v>446</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>906</v>
+        <v>877</v>
       </c>
       <c r="G140" s="7" t="s">
-        <v>873</v>
+        <v>888</v>
       </c>
       <c r="H140" s="7" t="s">
-        <v>305</v>
+        <v>166</v>
       </c>
       <c r="I140" s="8"/>
       <c r="J140" s="7" t="s">
-        <v>854</v>
+        <v>447</v>
       </c>
       <c r="K140" s="7" t="s">
-        <v>368</v>
+        <v>448</v>
       </c>
       <c r="L140" s="7" t="s">
         <v>1041</v>
       </c>
       <c r="M140" s="8" t="s">
-        <v>167</v>
+        <v>450</v>
       </c>
       <c r="N140" s="12"/>
       <c r="O140" s="12"/>
@@ -29436,10 +29436,10 @@
         <v>819</v>
       </c>
       <c r="B141" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C141" s="7" t="s">
         <v>1038</v>
-      </c>
-      <c r="C141" s="7" t="s">
-        <v>1039</v>
       </c>
       <c r="D141" s="8" t="s">
         <v>49</v>
@@ -29481,29 +29481,29 @@
         <v>819</v>
       </c>
       <c r="B142" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C142" s="7" t="s">
         <v>1038</v>
       </c>
-      <c r="C142" s="7" t="s">
-        <v>1039</v>
-      </c>
       <c r="D142" s="8" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>857</v>
+        <v>481</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>906</v>
+        <v>882</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="H142" s="8" t="s">
         <v>175</v>
       </c>
       <c r="I142" s="8"/>
       <c r="J142" s="7" t="s">
-        <v>858</v>
+        <v>482</v>
       </c>
       <c r="K142" s="7" t="s">
         <v>478</v>
@@ -29521,21 +29521,21 @@
       <c r="R142" s="12"/>
       <c r="S142" s="12"/>
     </row>
-    <row r="143" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
         <v>819</v>
       </c>
       <c r="B143" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C143" s="7" t="s">
         <v>1038</v>
-      </c>
-      <c r="C143" s="7" t="s">
-        <v>1039</v>
       </c>
       <c r="D143" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>827</v>
+        <v>857</v>
       </c>
       <c r="F143" s="7" t="s">
         <v>906</v>
@@ -29548,16 +29548,16 @@
       </c>
       <c r="I143" s="8"/>
       <c r="J143" s="7" t="s">
-        <v>828</v>
+        <v>858</v>
       </c>
       <c r="K143" s="7" t="s">
-        <v>303</v>
+        <v>478</v>
       </c>
       <c r="L143" s="7" t="s">
         <v>1044</v>
       </c>
       <c r="M143" s="8" t="s">
-        <v>167</v>
+        <v>484</v>
       </c>
       <c r="N143" s="12"/>
       <c r="O143" s="12"/>
@@ -29571,38 +29571,38 @@
         <v>819</v>
       </c>
       <c r="B144" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C144" s="7" t="s">
         <v>1038</v>
-      </c>
-      <c r="C144" s="7" t="s">
-        <v>1039</v>
       </c>
       <c r="D144" s="8" t="s">
         <v>76</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>818</v>
+        <v>490</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>906</v>
+        <v>882</v>
       </c>
       <c r="G144" s="7" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="H144" s="8" t="s">
         <v>175</v>
       </c>
       <c r="I144" s="8"/>
       <c r="J144" s="7" t="s">
-        <v>820</v>
+        <v>491</v>
       </c>
       <c r="K144" s="7" t="s">
-        <v>821</v>
+        <v>368</v>
       </c>
       <c r="L144" s="7" t="s">
         <v>1045</v>
       </c>
       <c r="M144" s="8" t="s">
-        <v>167</v>
+        <v>450</v>
       </c>
       <c r="N144" s="12"/>
       <c r="O144" s="12"/>
@@ -29616,19 +29616,19 @@
         <v>819</v>
       </c>
       <c r="B145" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C145" s="7" t="s">
         <v>1038</v>
-      </c>
-      <c r="C145" s="7" t="s">
-        <v>1039</v>
       </c>
       <c r="D145" s="8" t="s">
         <v>90</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>831</v>
+        <v>555</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>906</v>
+        <v>882</v>
       </c>
       <c r="G145" s="7" t="s">
         <v>873</v>
@@ -29638,7 +29638,7 @@
       </c>
       <c r="I145" s="8"/>
       <c r="J145" s="7" t="s">
-        <v>832</v>
+        <v>556</v>
       </c>
       <c r="K145" s="7" t="s">
         <v>303</v>
@@ -29647,7 +29647,7 @@
         <v>1046</v>
       </c>
       <c r="M145" s="8" t="s">
-        <v>167</v>
+        <v>450</v>
       </c>
       <c r="N145" s="12"/>
       <c r="O145" s="12"/>
@@ -29656,24 +29656,24 @@
       <c r="R145" s="12"/>
       <c r="S145" s="12"/>
     </row>
-    <row r="146" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="7" t="s">
         <v>819</v>
       </c>
       <c r="B146" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C146" s="7" t="s">
         <v>1038</v>
-      </c>
-      <c r="C146" s="7" t="s">
-        <v>1039</v>
       </c>
       <c r="D146" s="8" t="s">
         <v>104</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>836</v>
+        <v>594</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>906</v>
+        <v>885</v>
       </c>
       <c r="G146" s="7" t="s">
         <v>873</v>
@@ -29683,16 +29683,16 @@
       </c>
       <c r="I146" s="8"/>
       <c r="J146" s="7" t="s">
-        <v>837</v>
+        <v>595</v>
       </c>
       <c r="K146" s="7" t="s">
-        <v>415</v>
+        <v>368</v>
       </c>
       <c r="L146" s="7" t="s">
         <v>1047</v>
       </c>
       <c r="M146" s="8" t="s">
-        <v>167</v>
+        <v>484</v>
       </c>
       <c r="N146" s="12"/>
       <c r="O146" s="12"/>
@@ -29706,19 +29706,19 @@
         <v>819</v>
       </c>
       <c r="B147" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C147" s="7" t="s">
         <v>1038</v>
-      </c>
-      <c r="C147" s="7" t="s">
-        <v>1039</v>
       </c>
       <c r="D147" s="8" t="s">
         <v>118</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>840</v>
+        <v>679</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>906</v>
+        <v>872</v>
       </c>
       <c r="G147" s="7" t="s">
         <v>873</v>
@@ -29728,16 +29728,16 @@
       </c>
       <c r="I147" s="8"/>
       <c r="J147" s="7" t="s">
-        <v>841</v>
+        <v>681</v>
       </c>
       <c r="K147" s="7" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="L147" s="7" t="s">
         <v>1048</v>
       </c>
       <c r="M147" s="8" t="s">
-        <v>167</v>
+        <v>450</v>
       </c>
       <c r="N147" s="12"/>
       <c r="O147" s="12"/>
@@ -29751,38 +29751,38 @@
         <v>819</v>
       </c>
       <c r="B148" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C148" s="7" t="s">
         <v>1038</v>
-      </c>
-      <c r="C148" s="7" t="s">
-        <v>1039</v>
       </c>
       <c r="D148" s="8" t="s">
         <v>131</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>849</v>
+        <v>766</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>906</v>
+        <v>872</v>
       </c>
       <c r="G148" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="H148" s="8" t="s">
-        <v>175</v>
+      <c r="H148" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="I148" s="8"/>
       <c r="J148" s="7" t="s">
-        <v>850</v>
+        <v>767</v>
       </c>
       <c r="K148" s="7" t="s">
-        <v>495</v>
+        <v>368</v>
       </c>
       <c r="L148" s="7" t="s">
         <v>1049</v>
       </c>
       <c r="M148" s="8" t="s">
-        <v>167</v>
+        <v>450</v>
       </c>
       <c r="N148" s="12"/>
       <c r="O148" s="12"/>
@@ -30149,7 +30149,7 @@
       </c>
       <c r="B12" s="6" t="n">
         <f aca="false">COUNTIF(주차별배정!$A$3:$A$148,A12)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" s="6" t="n">
         <f aca="false">COUNTIFS(주차별배정!$A$3:$A$148,A12,주차별배정!$N$3:$N$148,"O")</f>
@@ -30178,7 +30178,7 @@
       </c>
       <c r="B13" s="6" t="n">
         <f aca="false">COUNTIF(주차별배정!$A$3:$A$148,A13)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="6" t="n">
         <f aca="false">COUNTIFS(주차별배정!$A$3:$A$148,A13,주차별배정!$N$3:$N$148,"O")</f>
@@ -30892,7 +30892,7 @@
         <v>303</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>1116</v>
@@ -31126,7 +31126,7 @@
         <v>393</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>1116</v>
@@ -31308,7 +31308,7 @@
         <v>415</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>1118</v>
@@ -31334,7 +31334,7 @@
         <v>420</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>1118</v>
@@ -31488,7 +31488,7 @@
         <v>384</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>1116</v>
@@ -31826,7 +31826,7 @@
         <v>448</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>941</v>
+        <v>1041</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>1118</v>
@@ -31852,7 +31852,7 @@
         <v>303</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>1121</v>
@@ -31878,7 +31878,7 @@
         <v>378</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>969</v>
+        <v>952</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>1121</v>
@@ -31930,7 +31930,7 @@
         <v>478</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>964</v>
+        <v>1043</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>1121</v>
@@ -31956,7 +31956,7 @@
         <v>368</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>1008</v>
+        <v>1048</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>1121</v>
@@ -31982,7 +31982,7 @@
         <v>409</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>1121</v>
@@ -32008,7 +32008,7 @@
         <v>399</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>1121</v>
@@ -32034,7 +32034,7 @@
         <v>303</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>996</v>
+        <v>982</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>1122</v>
@@ -32060,7 +32060,7 @@
         <v>368</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>950</v>
+        <v>1045</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>1121</v>
@@ -32086,7 +32086,7 @@
         <v>463</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>1016</v>
+        <v>1004</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>1121</v>
@@ -32112,7 +32112,7 @@
         <v>495</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>1121</v>
@@ -32138,7 +32138,7 @@
         <v>500</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>1121</v>
@@ -32164,7 +32164,7 @@
         <v>399</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>1121</v>
@@ -32190,7 +32190,7 @@
         <v>415</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>1121</v>
@@ -32216,7 +32216,7 @@
         <v>510</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>1123</v>
@@ -32242,7 +32242,7 @@
         <v>552</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>1121</v>
@@ -32268,7 +32268,7 @@
         <v>463</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>953</v>
+        <v>965</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>1123</v>
@@ -32294,7 +32294,7 @@
         <v>415</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>998</v>
+        <v>988</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>1121</v>
@@ -32320,7 +32320,7 @@
         <v>519</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>1123</v>
@@ -32346,7 +32346,7 @@
         <v>524</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>1121</v>
@@ -32398,7 +32398,7 @@
         <v>626</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>1121</v>
@@ -32424,7 +32424,7 @@
         <v>463</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>1123</v>
@@ -32450,7 +32450,7 @@
         <v>631</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>1122</v>
@@ -32476,7 +32476,7 @@
         <v>303</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>974</v>
+        <v>1046</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>1121</v>
@@ -32528,7 +32528,7 @@
         <v>636</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="G65" s="7" t="s">
         <v>1123</v>
@@ -32554,7 +32554,7 @@
         <v>463</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>993</v>
+        <v>978</v>
       </c>
       <c r="G66" s="7" t="s">
         <v>1125</v>
@@ -32580,7 +32580,7 @@
         <v>415</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>994</v>
+        <v>980</v>
       </c>
       <c r="G67" s="7" t="s">
         <v>1125</v>
@@ -32606,7 +32606,7 @@
         <v>415</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="G68" s="7" t="s">
         <v>1125</v>
@@ -32632,7 +32632,7 @@
         <v>415</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>997</v>
+        <v>987</v>
       </c>
       <c r="G69" s="7" t="s">
         <v>1125</v>
@@ -32658,7 +32658,7 @@
         <v>344</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>999</v>
+        <v>989</v>
       </c>
       <c r="G70" s="7" t="s">
         <v>1125</v>
@@ -32684,7 +32684,7 @@
         <v>303</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="G71" s="7" t="s">
         <v>1125</v>
@@ -32710,7 +32710,7 @@
         <v>564</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="G72" s="7" t="s">
         <v>1125</v>
@@ -32736,7 +32736,7 @@
         <v>661</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>1001</v>
+        <v>991</v>
       </c>
       <c r="G73" s="7" t="s">
         <v>1125</v>
@@ -32762,7 +32762,7 @@
         <v>415</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>1004</v>
+        <v>993</v>
       </c>
       <c r="G74" s="7" t="s">
         <v>1126</v>
@@ -32814,7 +32814,7 @@
         <v>415</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>1006</v>
+        <v>995</v>
       </c>
       <c r="G76" s="7" t="s">
         <v>1125</v>
@@ -32840,7 +32840,7 @@
         <v>384</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>1010</v>
+        <v>996</v>
       </c>
       <c r="G77" s="7" t="s">
         <v>1125</v>
@@ -32892,7 +32892,7 @@
         <v>303</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>1012</v>
+        <v>999</v>
       </c>
       <c r="G79" s="7" t="s">
         <v>1125</v>
@@ -32918,7 +32918,7 @@
         <v>384</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="G80" s="7" t="s">
         <v>1125</v>
@@ -32944,7 +32944,7 @@
         <v>415</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>1014</v>
+        <v>1001</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>1125</v>
@@ -32970,7 +32970,7 @@
         <v>463</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>1018</v>
+        <v>1006</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>1125</v>
@@ -32996,7 +32996,7 @@
         <v>399</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="G83" s="7" t="s">
         <v>1125</v>
@@ -33022,7 +33022,7 @@
         <v>717</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="G84" s="7" t="s">
         <v>1125</v>
@@ -33048,7 +33048,7 @@
         <v>303</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="G85" s="7" t="s">
         <v>1125</v>
@@ -33074,7 +33074,7 @@
         <v>722</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="G86" s="7" t="s">
         <v>1125</v>
@@ -33100,7 +33100,7 @@
         <v>463</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="G87" s="7" t="s">
         <v>1125</v>
@@ -33126,7 +33126,7 @@
         <v>303</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="G88" s="7" t="s">
         <v>1125</v>
@@ -33152,7 +33152,7 @@
         <v>581</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="G89" s="7" t="s">
         <v>1125</v>
@@ -33204,7 +33204,7 @@
         <v>586</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
       <c r="G91" s="7" t="s">
         <v>1125</v>
@@ -33386,7 +33386,7 @@
         <v>303</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="G98" s="7" t="s">
         <v>1125</v>
@@ -33412,7 +33412,7 @@
         <v>420</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="G99" s="7" t="s">
         <v>1125</v>
@@ -33464,7 +33464,7 @@
         <v>591</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="G101" s="7" t="s">
         <v>1125</v>
@@ -33490,7 +33490,7 @@
         <v>735</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="G102" s="7" t="s">
         <v>1125</v>
@@ -33568,7 +33568,7 @@
         <v>821</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>1045</v>
+        <v>1025</v>
       </c>
       <c r="G105" s="7" t="s">
         <v>1128</v>
@@ -33724,7 +33724,7 @@
         <v>368</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>983</v>
+        <v>1047</v>
       </c>
       <c r="G111" s="7" t="s">
         <v>1125</v>
@@ -33750,7 +33750,7 @@
         <v>600</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="G112" s="7" t="s">
         <v>1125</v>
@@ -33776,7 +33776,7 @@
         <v>415</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="G113" s="7" t="s">
         <v>1125</v>
@@ -33802,7 +33802,7 @@
         <v>264</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>1017</v>
+        <v>1005</v>
       </c>
       <c r="G114" s="7" t="s">
         <v>1125</v>
@@ -33828,7 +33828,7 @@
         <v>744</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>1019</v>
+        <v>1007</v>
       </c>
       <c r="G115" s="7" t="s">
         <v>1125</v>
@@ -33880,7 +33880,7 @@
         <v>759</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>1025</v>
+        <v>1009</v>
       </c>
       <c r="G117" s="7" t="s">
         <v>1125</v>
@@ -33932,7 +33932,7 @@
         <v>671</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>989</v>
+        <v>975</v>
       </c>
       <c r="G119" s="7" t="s">
         <v>1125</v>
@@ -33984,7 +33984,7 @@
         <v>303</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>1026</v>
+        <v>1011</v>
       </c>
       <c r="G121" s="7" t="s">
         <v>1125</v>
@@ -34010,7 +34010,7 @@
         <v>368</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>1028</v>
+        <v>1049</v>
       </c>
       <c r="G122" s="7" t="s">
         <v>1125</v>
@@ -34088,7 +34088,7 @@
         <v>399</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="G125" s="7" t="s">
         <v>1125</v>
@@ -34114,7 +34114,7 @@
         <v>368</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>1030</v>
+        <v>1039</v>
       </c>
       <c r="G126" s="7" t="s">
         <v>1125</v>
@@ -34140,7 +34140,7 @@
         <v>774</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>1032</v>
+        <v>1013</v>
       </c>
       <c r="G127" s="7" t="s">
         <v>1125</v>
@@ -34166,7 +34166,7 @@
         <v>779</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>1034</v>
+        <v>1015</v>
       </c>
       <c r="G128" s="7" t="s">
         <v>1125</v>
@@ -34244,7 +34244,7 @@
         <v>784</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>1037</v>
+        <v>1017</v>
       </c>
       <c r="G131" s="7" t="s">
         <v>1125</v>
@@ -34270,7 +34270,7 @@
         <v>415</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>991</v>
+        <v>977</v>
       </c>
       <c r="G132" s="7" t="s">
         <v>1125</v>
@@ -34296,7 +34296,7 @@
         <v>789</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="G133" s="7" t="s">
         <v>1125</v>
@@ -34322,7 +34322,7 @@
         <v>344</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="G134" s="7" t="s">
         <v>1129</v>
@@ -34348,7 +34348,7 @@
         <v>415</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="G135" s="7" t="s">
         <v>1129</v>
@@ -34374,7 +34374,7 @@
         <v>415</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="G136" s="7" t="s">
         <v>1129</v>
@@ -34426,7 +34426,7 @@
         <v>303</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>1044</v>
+        <v>1022</v>
       </c>
       <c r="G138" s="7" t="s">
         <v>1129</v>
@@ -34452,7 +34452,7 @@
         <v>806</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G139" s="7" t="s">
         <v>1129</v>
@@ -34478,7 +34478,7 @@
         <v>303</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>1046</v>
+        <v>1027</v>
       </c>
       <c r="G140" s="7" t="s">
         <v>1129</v>
@@ -34504,7 +34504,7 @@
         <v>415</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>1047</v>
+        <v>1028</v>
       </c>
       <c r="G141" s="7" t="s">
         <v>1129</v>
@@ -34556,7 +34556,7 @@
         <v>393</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>1048</v>
+        <v>1031</v>
       </c>
       <c r="G143" s="7" t="s">
         <v>1129</v>
@@ -34608,7 +34608,7 @@
         <v>495</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>1049</v>
+        <v>1033</v>
       </c>
       <c r="G145" s="7" t="s">
         <v>1129</v>
@@ -34634,7 +34634,7 @@
         <v>368</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="G146" s="7" t="s">
         <v>1129</v>
@@ -34660,7 +34660,7 @@
         <v>478</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G147" s="7" t="s">
         <v>1129</v>
